--- a/Ulshoefer-Preisliste-Angebotsrechner.xlsx
+++ b/Ulshoefer-Preisliste-Angebotsrechner.xlsx
@@ -27,12 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="277">
   <si>
     <t xml:space="preserve">Preisliste für den Online-Angebotsrechner</t>
   </si>
   <si>
-    <t xml:space="preserve">Elektrotechnik Ulshöfer GmbH · Stand: Website-Version v0.5.5 · alle Preise sind Beispielwerte</t>
+    <t xml:space="preserve">Elektrotechnik Ulshöfer GmbH · Stand: Website-Version v0.6.0 · alle Preise sind Beispielwerte</t>
   </si>
   <si>
     <t xml:space="preserve">Wozu dient diese Tabelle?</t>
@@ -177,6 +177,9 @@
   </si>
   <si>
     <t xml:space="preserve">Elektroinstallation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chat-Assistent „Fragen?“</t>
   </si>
   <si>
     <t xml:space="preserve">Gelbe Zellen ändern. Bruttopreise und Arbeitslohn werden mit Stundensatz und MwSt. aus „Allgemein“ berechnet.</t>
@@ -1532,7 +1535,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
@@ -1751,9 +1754,17 @@
         <v>45</v>
       </c>
     </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B23:B27" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B23:B28" type="list">
       <formula1>"Ja,Nein"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -1791,51 +1802,51 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C7" s="18" t="n">
         <v>2.5</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>990</v>
@@ -1847,16 +1858,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C8" s="18" t="n">
         <v>3.3</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>1120</v>
@@ -1868,16 +1879,16 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C9" s="18" t="n">
         <v>4.2</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>1390</v>
@@ -1889,16 +1900,16 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C10" s="18" t="n">
         <v>5</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>1590</v>
@@ -1910,16 +1921,16 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C11" s="18" t="n">
         <v>6.5</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>2090</v>
@@ -1931,16 +1942,16 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C12" s="18" t="n">
         <v>2.5</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1390</v>
@@ -1952,16 +1963,16 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C13" s="18" t="n">
         <v>3.5</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E13" s="12" t="n">
         <v>1550</v>
@@ -1973,16 +1984,16 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C14" s="18" t="n">
         <v>4.6</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E14" s="12" t="n">
         <v>1790</v>
@@ -1994,16 +2005,16 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C15" s="18" t="n">
         <v>5</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E15" s="12" t="n">
         <v>1990</v>
@@ -2015,16 +2026,16 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C16" s="18" t="n">
         <v>3.5</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E16" s="12" t="n">
         <v>2390</v>
@@ -2036,16 +2047,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C17" s="18" t="n">
         <v>2.5</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E17" s="12" t="n">
         <v>1090</v>
@@ -2057,16 +2068,16 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C18" s="18" t="n">
         <v>3.5</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E18" s="12" t="n">
         <v>1240</v>
@@ -2078,16 +2089,16 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C19" s="18" t="n">
         <v>5</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E19" s="12" t="n">
         <v>1690</v>
@@ -2099,16 +2110,16 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C20" s="18" t="n">
         <v>2.5</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E20" s="12" t="n">
         <v>1490</v>
@@ -2120,16 +2131,16 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C21" s="18" t="n">
         <v>3.5</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E21" s="12" t="n">
         <v>1690</v>
@@ -2141,16 +2152,16 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C22" s="18" t="n">
         <v>5</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E22" s="12" t="n">
         <v>2190</v>
@@ -2162,16 +2173,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C23" s="18" t="n">
         <v>2.5</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E23" s="12" t="n">
         <v>1150</v>
@@ -2183,16 +2194,16 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C24" s="18" t="n">
         <v>3.5</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E24" s="12" t="n">
         <v>1290</v>
@@ -2204,16 +2215,16 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C25" s="18" t="n">
         <v>5</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E25" s="12" t="n">
         <v>1750</v>
@@ -2225,16 +2236,16 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C26" s="18" t="n">
         <v>7.1</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E26" s="12" t="n">
         <v>2390</v>
@@ -2246,46 +2257,46 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C31" s="18" t="n">
         <v>2.5</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E31" s="12" t="n">
         <v>420</v>
@@ -2297,16 +2308,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C32" s="18" t="n">
         <v>3.3</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E32" s="12" t="n">
         <v>470</v>
@@ -2318,16 +2329,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C33" s="18" t="n">
         <v>4.2</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E33" s="12" t="n">
         <v>560</v>
@@ -2339,16 +2350,16 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C34" s="18" t="n">
         <v>2.5</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E34" s="12" t="n">
         <v>590</v>
@@ -2360,16 +2371,16 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C35" s="18" t="n">
         <v>3.5</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E35" s="12" t="n">
         <v>660</v>
@@ -2381,16 +2392,16 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C36" s="18" t="n">
         <v>4.6</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E36" s="12" t="n">
         <v>760</v>
@@ -2402,16 +2413,16 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C37" s="18" t="n">
         <v>2</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E37" s="12" t="n">
         <v>560</v>
@@ -2423,16 +2434,16 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C38" s="18" t="n">
         <v>2.5</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E38" s="12" t="n">
         <v>600</v>
@@ -2444,16 +2455,16 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C39" s="18" t="n">
         <v>3.5</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E39" s="12" t="n">
         <v>680</v>
@@ -2465,16 +2476,16 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C40" s="18" t="n">
         <v>5</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E40" s="12" t="n">
         <v>860</v>
@@ -2486,16 +2497,16 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C41" s="18" t="n">
         <v>2.5</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E41" s="12" t="n">
         <v>430</v>
@@ -2507,16 +2518,16 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B42" s="17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C42" s="18" t="n">
         <v>3.5</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E42" s="12" t="n">
         <v>490</v>
@@ -2528,16 +2539,16 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C43" s="18" t="n">
         <v>5</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E43" s="12" t="n">
         <v>640</v>
@@ -2549,40 +2560,40 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B48" s="17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C48" s="18" t="n">
         <v>2</v>
@@ -2600,10 +2611,10 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B49" s="17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C49" s="18" t="n">
         <v>3</v>
@@ -2621,10 +2632,10 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B50" s="17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C50" s="18" t="n">
         <v>3</v>
@@ -2642,10 +2653,10 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B51" s="17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C51" s="18" t="n">
         <v>4</v>
@@ -2663,10 +2674,10 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B52" s="17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C52" s="18" t="n">
         <v>5</v>
@@ -2684,10 +2695,10 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B53" s="17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C53" s="18" t="n">
         <v>2</v>
@@ -2705,10 +2716,10 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B54" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C54" s="18" t="n">
         <v>3</v>
@@ -2726,10 +2737,10 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B55" s="17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C55" s="18" t="n">
         <v>4</v>
@@ -2747,10 +2758,10 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B56" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C56" s="18" t="n">
         <v>5</v>
@@ -2768,17 +2779,17 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B60" s="10" t="s">
         <v>22</v>
@@ -2787,21 +2798,21 @@
         <v>23</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B61" s="18" t="n">
         <v>6</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D61" s="19" t="n">
         <f aca="false">B61*Allgemein!$B$6</f>
@@ -2814,13 +2825,13 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B62" s="18" t="n">
         <v>7</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D62" s="19" t="n">
         <f aca="false">B62*Allgemein!$B$6</f>
@@ -2833,13 +2844,13 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B63" s="18" t="n">
         <v>4</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D63" s="19" t="n">
         <f aca="false">B63*Allgemein!$B$6</f>
@@ -2852,13 +2863,13 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B64" s="18" t="n">
         <v>0.25</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D64" s="19" t="n">
         <f aca="false">B64*Allgemein!$B$6</f>
@@ -2871,13 +2882,13 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B65" s="18" t="n">
         <v>0.75</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D65" s="19" t="n">
         <f aca="false">B65*Allgemein!$B$6</f>
@@ -2890,13 +2901,13 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B66" s="18" t="n">
         <v>0.5</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D66" s="19" t="n">
         <f aca="false">B66*Allgemein!$B$6</f>
@@ -2909,13 +2920,13 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B67" s="18" t="n">
         <v>2</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D67" s="19" t="n">
         <f aca="false">B67*Allgemein!$B$6</f>
@@ -2928,13 +2939,13 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B68" s="18" t="n">
         <v>1</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D68" s="19" t="n">
         <f aca="false">B68*Allgemein!$B$6</f>
@@ -2947,12 +2958,12 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="15" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B71" s="10" t="s">
         <v>22</v>
@@ -2961,15 +2972,15 @@
         <v>23</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B72" s="12" t="n">
         <v>190</v>
@@ -2984,7 +2995,7 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B73" s="12" t="n">
         <v>150</v>
@@ -2999,7 +3010,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B74" s="12" t="n">
         <v>26</v>
@@ -3014,7 +3025,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B75" s="12" t="n">
         <v>110</v>
@@ -3029,7 +3040,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B76" s="12" t="n">
         <v>360</v>
@@ -3044,7 +3055,7 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B77" s="12" t="n">
         <v>55</v>
@@ -3059,7 +3070,7 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B78" s="12" t="n">
         <v>135</v>
@@ -3074,7 +3085,7 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B79" s="12" t="n">
         <v>170</v>
@@ -3089,12 +3100,12 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="15" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B82" s="10" t="s">
         <v>22</v>
@@ -3103,15 +3114,15 @@
         <v>23</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B83" s="12" t="n">
         <v>149</v>
@@ -3122,13 +3133,13 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B84" s="18" t="n">
         <v>0.1</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -3171,42 +3182,42 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C7" s="18" t="n">
         <v>6</v>
@@ -3221,10 +3232,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C8" s="18" t="n">
         <v>9</v>
@@ -3239,10 +3250,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C9" s="18" t="n">
         <v>12</v>
@@ -3257,10 +3268,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C10" s="18" t="n">
         <v>16</v>
@@ -3275,10 +3286,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C11" s="18" t="n">
         <v>18</v>
@@ -3293,17 +3304,17 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>22</v>
@@ -3312,21 +3323,21 @@
         <v>23</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B16" s="18" t="n">
         <v>30</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D16" s="19" t="n">
         <f aca="false">B16*Allgemein!$B$6</f>
@@ -3339,13 +3350,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B17" s="18" t="n">
         <v>12</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D17" s="19" t="n">
         <f aca="false">B17*Allgemein!$B$6</f>
@@ -3358,13 +3369,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B18" s="18" t="n">
         <v>6</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D18" s="19" t="n">
         <f aca="false">B18*Allgemein!$B$6</f>
@@ -3377,13 +3388,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B19" s="18" t="n">
         <v>10</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D19" s="19" t="n">
         <f aca="false">B19*Allgemein!$B$6</f>
@@ -3396,13 +3407,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B20" s="18" t="n">
         <v>2.5</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D20" s="19" t="n">
         <f aca="false">B20*Allgemein!$B$6</f>
@@ -3415,13 +3426,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B21" s="18" t="n">
         <v>6</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D21" s="19" t="n">
         <f aca="false">B21*Allgemein!$B$6</f>
@@ -3434,12 +3445,12 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B24" s="10" t="s">
         <v>22</v>
@@ -3448,15 +3459,15 @@
         <v>23</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B25" s="12" t="n">
         <v>4200</v>
@@ -3471,7 +3482,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B26" s="12" t="n">
         <v>900</v>
@@ -3486,7 +3497,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B27" s="12" t="n">
         <v>150</v>
@@ -3501,7 +3512,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B28" s="12" t="n">
         <v>350</v>
@@ -3516,7 +3527,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B29" s="12" t="n">
         <v>380</v>
@@ -3531,7 +3542,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B30" s="12" t="n">
         <v>650</v>
@@ -3546,12 +3557,12 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>22</v>
@@ -3560,21 +3571,21 @@
         <v>23</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B34" s="18" t="n">
         <v>0.25</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -3611,42 +3622,42 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C7" s="18" t="n">
         <v>450</v>
@@ -3661,10 +3672,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C8" s="18" t="n">
         <v>400</v>
@@ -3679,42 +3690,42 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C14" s="18" t="n">
         <v>4</v>
@@ -3729,10 +3740,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C15" s="18" t="n">
         <v>6</v>
@@ -3747,10 +3758,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C16" s="18" t="n">
         <v>8</v>
@@ -3765,10 +3776,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C17" s="18" t="n">
         <v>10</v>
@@ -3783,10 +3794,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C18" s="18" t="n">
         <v>15</v>
@@ -3801,42 +3812,42 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="17" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C24" s="18" t="n">
         <v>5.1</v>
@@ -3851,10 +3862,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="17" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C25" s="18" t="n">
         <v>7.7</v>
@@ -3869,10 +3880,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="17" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C26" s="18" t="n">
         <v>10.2</v>
@@ -3887,17 +3898,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B30" s="10" t="s">
         <v>22</v>
@@ -3906,33 +3917,33 @@
         <v>23</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B31" s="20" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C31" s="11"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C32" s="11"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B33" s="12" t="n">
         <v>890</v>
@@ -3947,13 +3958,13 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B34" s="18" t="n">
         <v>5</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D34" s="19" t="n">
         <f aca="false">B34*Allgemein!$B$6</f>
@@ -3966,12 +3977,12 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B37" s="10" t="s">
         <v>22</v>
@@ -3980,21 +3991,21 @@
         <v>23</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B38" s="18" t="n">
         <v>8</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D38" s="19" t="n">
         <f aca="false">B38*Allgemein!$B$6</f>
@@ -4007,13 +4018,13 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B39" s="18" t="n">
         <v>0.6</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D39" s="19" t="n">
         <f aca="false">B39*Allgemein!$B$6</f>
@@ -4026,13 +4037,13 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B40" s="18" t="n">
         <v>4</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D40" s="19" t="n">
         <f aca="false">B40*Allgemein!$B$6</f>
@@ -4045,13 +4056,13 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B41" s="18" t="n">
         <v>4</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D41" s="19" t="n">
         <f aca="false">B41*Allgemein!$B$6</f>
@@ -4064,12 +4075,12 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B44" s="10" t="s">
         <v>22</v>
@@ -4078,15 +4089,15 @@
         <v>23</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="11" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B45" s="12" t="n">
         <v>48</v>
@@ -4101,7 +4112,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B46" s="12" t="n">
         <v>480</v>
@@ -4116,7 +4127,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="11" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B47" s="12" t="n">
         <v>650</v>
@@ -4131,7 +4142,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="11" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B48" s="12" t="n">
         <v>450</v>
@@ -4146,7 +4157,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="11" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B49" s="12" t="n">
         <v>250</v>
@@ -4161,7 +4172,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="11" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B50" s="12" t="n">
         <v>450</v>
@@ -4176,12 +4187,12 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="15" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B53" s="10" t="s">
         <v>22</v>
@@ -4190,43 +4201,43 @@
         <v>23</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="11" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B54" s="18" t="n">
         <v>950</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="11" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B55" s="21" t="n">
         <v>0.35</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B56" s="21" t="n">
         <v>0.077</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -4263,17 +4274,17 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>22</v>
@@ -4282,24 +4293,24 @@
         <v>23</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C6" s="11"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B7" s="12" t="n">
         <v>900</v>
@@ -4314,13 +4325,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B8" s="18" t="n">
         <v>12</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D8" s="19" t="n">
         <f aca="false">B8*Allgemein!$B$6</f>
@@ -4333,7 +4344,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B9" s="12" t="n">
         <v>160</v>
@@ -4348,13 +4359,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B10" s="18" t="n">
         <v>1.5</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D10" s="19" t="n">
         <f aca="false">B10*Allgemein!$B$6</f>
@@ -4367,7 +4378,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B11" s="12" t="n">
         <v>120</v>
@@ -4382,13 +4393,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B12" s="18" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D12" s="19" t="n">
         <f aca="false">B12*Allgemein!$B$6</f>
@@ -4401,7 +4412,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B13" s="12" t="n">
         <v>140</v>
@@ -4416,13 +4427,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B14" s="18" t="n">
         <v>1.5</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D14" s="19" t="n">
         <f aca="false">B14*Allgemein!$B$6</f>
@@ -4435,7 +4446,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B15" s="12" t="n">
         <v>600</v>
@@ -4450,13 +4461,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B16" s="18" t="n">
         <v>5</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D16" s="19" t="n">
         <f aca="false">B16*Allgemein!$B$6</f>
@@ -4469,12 +4480,12 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B19" s="10" t="s">
         <v>22</v>
@@ -4483,24 +4494,24 @@
         <v>23</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C20" s="11"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B21" s="12" t="n">
         <v>180</v>
@@ -4515,13 +4526,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B22" s="18" t="n">
         <v>3</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D22" s="19" t="n">
         <f aca="false">B22*Allgemein!$B$6</f>
@@ -4534,7 +4545,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B23" s="12" t="n">
         <v>75</v>
@@ -4549,13 +4560,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B24" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D24" s="19" t="n">
         <f aca="false">B24*Allgemein!$B$6</f>
@@ -4568,7 +4579,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B25" s="12" t="n">
         <v>65</v>
@@ -4583,13 +4594,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B26" s="18" t="n">
         <v>0.75</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D26" s="19" t="n">
         <f aca="false">B26*Allgemein!$B$6</f>
@@ -4602,7 +4613,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B27" s="12" t="n">
         <v>70</v>
@@ -4617,13 +4628,13 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B28" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D28" s="19" t="n">
         <f aca="false">B28*Allgemein!$B$6</f>
@@ -4636,7 +4647,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B29" s="12" t="n">
         <v>450</v>
@@ -4651,13 +4662,13 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B30" s="18" t="n">
         <v>4</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D30" s="19" t="n">
         <f aca="false">B30*Allgemein!$B$6</f>
@@ -4670,12 +4681,12 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>22</v>
@@ -4684,24 +4695,24 @@
         <v>23</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C34" s="11"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B35" s="12" t="n">
         <v>1300</v>
@@ -4716,13 +4727,13 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B36" s="18" t="n">
         <v>14</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D36" s="19" t="n">
         <f aca="false">B36*Allgemein!$B$6</f>
@@ -4735,7 +4746,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B37" s="12" t="n">
         <v>180</v>
@@ -4750,13 +4761,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B38" s="18" t="n">
         <v>2</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D38" s="19" t="n">
         <f aca="false">B38*Allgemein!$B$6</f>
@@ -4769,7 +4780,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B39" s="12" t="n">
         <v>140</v>
@@ -4784,13 +4795,13 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B40" s="18" t="n">
         <v>1.5</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D40" s="19" t="n">
         <f aca="false">B40*Allgemein!$B$6</f>
@@ -4803,7 +4814,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B41" s="12" t="n">
         <v>150</v>
@@ -4818,13 +4829,13 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="11" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B42" s="18" t="n">
         <v>1.75</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D42" s="19" t="n">
         <f aca="false">B42*Allgemein!$B$6</f>
@@ -4837,7 +4848,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B43" s="12" t="n">
         <v>700</v>
@@ -4852,13 +4863,13 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B44" s="18" t="n">
         <v>7</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D44" s="19" t="n">
         <f aca="false">B44*Allgemein!$B$6</f>
@@ -4871,12 +4882,12 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B47" s="10" t="s">
         <v>22</v>
@@ -4885,15 +4896,15 @@
         <v>23</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="11" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B48" s="12" t="n">
         <v>0</v>
@@ -4904,13 +4915,13 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="11" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B49" s="18" t="n">
         <v>4</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D49" s="19" t="n">
         <f aca="false">B49*Allgemein!$B$6</f>
@@ -4955,17 +4966,17 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>22</v>
@@ -4974,15 +4985,15 @@
         <v>23</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B6" s="12" t="n">
         <v>42</v>
@@ -4997,13 +5008,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B7" s="18" t="n">
         <v>0.75</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D7" s="19" t="n">
         <f aca="false">B7*Allgemein!$B$6</f>
@@ -5016,7 +5027,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B8" s="12" t="n">
         <v>52</v>
@@ -5031,13 +5042,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B9" s="18" t="n">
         <v>1.2</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D9" s="19" t="n">
         <f aca="false">B9*Allgemein!$B$6</f>
@@ -5050,7 +5061,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B10" s="12" t="n">
         <v>30</v>
@@ -5065,13 +5076,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B11" s="18" t="n">
         <v>0.6</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D11" s="19" t="n">
         <f aca="false">B11*Allgemein!$B$6</f>
@@ -5084,12 +5095,12 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B14" s="10" t="s">
         <v>22</v>
@@ -5098,15 +5109,15 @@
         <v>23</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B15" s="12" t="n">
         <v>1650</v>
@@ -5121,13 +5132,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B16" s="18" t="n">
         <v>18</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D16" s="19" t="n">
         <f aca="false">B16*Allgemein!$B$6</f>
@@ -5140,7 +5151,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B17" s="12" t="n">
         <v>55</v>
@@ -5155,13 +5166,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B18" s="18" t="n">
         <v>1.4</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D18" s="19" t="n">
         <f aca="false">B18*Allgemein!$B$6</f>
@@ -5174,7 +5185,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B19" s="12" t="n">
         <v>330</v>
@@ -5189,13 +5200,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B20" s="18" t="n">
         <v>2.5</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D20" s="19" t="n">
         <f aca="false">B20*Allgemein!$B$6</f>
@@ -5208,7 +5219,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B21" s="12" t="n">
         <v>0</v>
@@ -5223,13 +5234,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B22" s="18" t="n">
         <v>2.75</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D22" s="19" t="n">
         <f aca="false">B22*Allgemein!$B$6</f>
@@ -5242,12 +5253,12 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B25" s="10" t="s">
         <v>22</v>
@@ -5256,33 +5267,33 @@
         <v>23</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C26" s="11"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C27" s="11"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B28" s="12" t="n">
         <v>890</v>
@@ -5297,13 +5308,13 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B29" s="18" t="n">
         <v>7</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D29" s="19" t="n">
         <f aca="false">B29*Allgemein!$B$6</f>
@@ -5341,250 +5352,250 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="22" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="23" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="24" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B4" s="24" t="s">
         <v>42</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="25" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="25" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="25" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="25" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D14" s="26" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="25" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="25" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="25" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D17" s="26" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="25" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="25" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="25" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>

--- a/Ulshoefer-Preisliste-Angebotsrechner.xlsx
+++ b/Ulshoefer-Preisliste-Angebotsrechner.xlsx
@@ -14,8 +14,9 @@
     <sheet name="Wärmepumpe" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Photovoltaik" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Smart Home" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Elektroinstallation" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Partner" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Hausgeräte" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Elektroinstallation" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Partner" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,12 +28,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="320">
   <si>
     <t xml:space="preserve">Preisliste für den Online-Angebotsrechner</t>
   </si>
   <si>
-    <t xml:space="preserve">Elektrotechnik Ulshöfer GmbH · Stand: Website-Version v0.6.0 · alle Preise sind Beispielwerte</t>
+    <t xml:space="preserve">Elektrotechnik Ulshöfer GmbH · Stand: Website-Version v0.7.0 · alle Preise sind Beispielwerte</t>
   </si>
   <si>
     <t xml:space="preserve">Wozu dient diese Tabelle?</t>
@@ -71,6 +72,12 @@
     <t xml:space="preserve">• Der Kunde sieht einen Richtpreis mit Spanne (± Preisspanne). Der verbindliche Festpreis folgt nach der Besichtigung.</t>
   </si>
   <si>
+    <t xml:space="preserve">• Spalte „Aktiv“: „Nein“ = das Modell bleibt gespeichert, wird Kunden aber nicht angeboten.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Hausgeräte: Hier sind alle Preise BRUTTO (inkl. MwSt.), wie im Laden. Produktbilder werden in der Preisverwaltung hochgeladen.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Legende</t>
   </si>
   <si>
@@ -179,6 +186,9 @@
     <t xml:space="preserve">Elektroinstallation</t>
   </si>
   <si>
+    <t xml:space="preserve">Hausgeräte (Online-Bestellung)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Chat-Assistent „Fragen?“</t>
   </si>
   <si>
@@ -191,6 +201,9 @@
     <t xml:space="preserve">Die Website wählt das kleinste Gerät, das für den Raum reicht, in der vom Kunden gewählten Klasse; bei gleicher Leistung das günstigste.</t>
   </si>
   <si>
+    <t xml:space="preserve">Aktiv</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hersteller</t>
   </si>
   <si>
@@ -572,169 +585,292 @@
     <t xml:space="preserve">Wallbox</t>
   </si>
   <si>
+    <t xml:space="preserve">Die Wallbox-Modelle werden im Reiter „Elektroinstallation“ gepflegt (gemeinsame Liste).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montagestunden Wallbox mit PV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montage: Grundpauschale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">… je Modul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montage Speicher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notstromfunktion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unterkonstruktion, pro Modul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC/AC-Verkabelung, Schutzeinrichtungen, Kleinmaterial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gerüst / Absturzsicherung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anpassung Zählerschrank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anmeldung Netzbetreiber und MaStR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notstrom-Umschalter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ertragsberechnung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jahresertrag pro kWp (Südausrichtung)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kWh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strompreis des Kunden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">€/kWh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Einspeisevergütung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Loxone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bezeichnung im Angebot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loxone (Miniserver, Tree/Air)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zentrale / Grundausstattung – Material</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zentrale / Grundausstattung – Stunden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Licht, pro Raum – Material</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Licht, pro Raum – Stunden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heizung, pro Raum – Material</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heizung, pro Raum – Stunden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rollladen, pro Stück – Material</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rollladen, pro Stück – Stunden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sicherheitspaket – Material</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sicherheitspaket – Stunden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Funk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homematic IP (Funk)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System KNX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KNX (Gira / ABB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home Assistant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hardware (0 = keine)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Einrichtung (Stunden)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hausgeräte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partner / Marken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ausgeschaltete Marken verschwinden mitsamt ihren Produkten aus der Online-Bestellung.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siemens Hausgeräte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miele</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liebherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produkte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preise BRUTTO (inkl. MwSt.) wie im Laden. Bild am besten quadratisch mit weißem Hintergrund; es wird automatisch verkleinert.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kategorie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurzbeschreibung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anschluss/Montage brutto (€)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waschmaschine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iQ300 Waschmaschine 8 kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beispielprodukt – Ausstattung und Preis folgen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iQ500 Waschmaschine 9 kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wäschetrockner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iQ500 Wärmepumpentrockner 8 kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geschirrspüler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iQ300 Einbau-Geschirrspüler 60 cm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backofen &amp; Herd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iQ500 Einbau-Backofen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kühlen &amp; Gefrieren</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iQ300 Kühl-Gefrier-Kombination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waschmaschine W1 (Beispiel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kühl-Gefrier-Kombination (Beispiel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leistungen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lieferung pro Gerät (brutto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Altgerät-Mitnahme pro Gerät (brutto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lieferzeit (Text für den Kunden)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In der Regel 3–10 Werktage, Liefertermin nach Absprache.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Installation pro m²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neubau – Material pro m²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neubau – Stunden pro m²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Komplettsanierung – Material pro m²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Komplettsanierung – Stunden pro m²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teilsanierung – Material pro m²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teilsanierung – Stunden pro m²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Einzelpositionen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neuer Zählerschrank – Material</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neuer Zählerschrank – Stunden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netzwerkdose – Material</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netzwerkdose – Stunden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Überspannungsschutz – Material</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Überspannungsschutz – Stunden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-CHECK – Material</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-CHECK – Stunden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wallboxen (für Elektroinstallation und Photovoltaik)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Der Kunde wählt die Wallbox im Rechner. Angeboten werden nur aktive Modelle.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Wattpilot Home 11 J</t>
   </si>
   <si>
-    <t xml:space="preserve">Nettopreis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montagestunden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montage: Grundpauschale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">… je Modul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montage Speicher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notstromfunktion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unterkonstruktion, pro Modul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DC/AC-Verkabelung, Schutzeinrichtungen, Kleinmaterial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gerüst / Absturzsicherung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anpassung Zählerschrank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anmeldung Netzbetreiber und MaStR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notstrom-Umschalter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ertragsberechnung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jahresertrag pro kWp (Südausrichtung)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kWh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strompreis des Kunden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">€/kWh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Einspeisevergütung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Loxone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bezeichnung im Angebot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loxone (Miniserver, Tree/Air)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zentrale / Grundausstattung – Material</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zentrale / Grundausstattung – Stunden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Licht, pro Raum – Material</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Licht, pro Raum – Stunden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heizung, pro Raum – Material</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heizung, pro Raum – Stunden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rollladen, pro Stück – Material</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rollladen, pro Stück – Stunden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sicherheitspaket – Material</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sicherheitspaket – Stunden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Funk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Homematic IP (Funk)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System KNX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KNX (Gira / ABB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home Assistant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hardware (0 = keine)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Einrichtung (Stunden)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Installation pro m²</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neubau – Material pro m²</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neubau – Stunden pro m²</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Komplettsanierung – Material pro m²</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Komplettsanierung – Stunden pro m²</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teilsanierung – Material pro m²</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teilsanierung – Stunden pro m²</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Einzelpositionen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neuer Zählerschrank – Material</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neuer Zählerschrank – Stunden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netzwerkdose – Material</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netzwerkdose – Stunden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Überspannungsschutz – Material</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Überspannungsschutz – Stunden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-CHECK – Material</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-CHECK – Stunden</t>
+    <t xml:space="preserve">ABL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eMH1 11 kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mennekes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMTRON Compact 2.0s 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heidelberg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energy Control</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montage Wallbox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montagestunden (inkl. Zuleitung und Anmeldung)</t>
   </si>
   <si>
     <t xml:space="preserve">Partner</t>
@@ -830,13 +966,7 @@
     <t xml:space="preserve">https://www.krups.de/</t>
   </si>
   <si>
-    <t xml:space="preserve">Liebherr</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://www.liebherr.com/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miele</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.miele.de/</t>
@@ -1138,11 +1268,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1418,7 +1548,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="110"/>
@@ -1499,24 +1629,34 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="6" t="s">
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B19" s="6" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1535,7 +1675,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
@@ -1545,226 +1685,234 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B5" s="12" t="n">
         <v>45</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B6" s="12" t="n">
         <v>68</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B7" s="13" t="n">
         <v>0.08</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B8" s="13" t="n">
         <v>0.19</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B9" s="14" t="n">
         <v>30</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B14" s="13" t="n">
         <v>0.3</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B15" s="13" t="n">
         <v>0.16</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B16" s="13" t="n">
         <v>0.7</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B17" s="13" t="n">
         <v>0.8</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B18" s="16" t="n">
         <v>28000</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>45</v>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B23:B28" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B23:B29" type="list">
       <formula1>"Ja,Nein"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -1784,7 +1932,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F84"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
@@ -1797,1022 +1945,1157 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>59</v>
+        <v>62</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" s="18" t="n">
+        <v>64</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="18" t="n">
         <v>2.5</v>
       </c>
-      <c r="D7" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="F7" s="12" t="n">
         <v>990</v>
       </c>
-      <c r="F7" s="19" t="n">
-        <f aca="false">E7*(1+Allgemein!$B$8)</f>
+      <c r="G7" s="19" t="n">
+        <f aca="false">F7*(1+Allgemein!$B$8)</f>
         <v>1178.1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" s="18" t="n">
+        <v>64</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="18" t="n">
         <v>3.3</v>
       </c>
-      <c r="D8" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="F8" s="12" t="n">
         <v>1120</v>
       </c>
-      <c r="F8" s="19" t="n">
-        <f aca="false">E8*(1+Allgemein!$B$8)</f>
+      <c r="G8" s="19" t="n">
+        <f aca="false">F8*(1+Allgemein!$B$8)</f>
         <v>1332.8</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="B9" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="18" t="n">
+      <c r="C9" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" s="18" t="n">
         <v>4.2</v>
       </c>
-      <c r="D9" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="E9" s="12" t="n">
+      <c r="E9" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="12" t="n">
         <v>1390</v>
       </c>
-      <c r="F9" s="19" t="n">
-        <f aca="false">E9*(1+Allgemein!$B$8)</f>
+      <c r="G9" s="19" t="n">
+        <f aca="false">F9*(1+Allgemein!$B$8)</f>
         <v>1654.1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10" s="18" t="n">
+        <v>64</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="D10" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="F10" s="12" t="n">
         <v>1590</v>
       </c>
-      <c r="F10" s="19" t="n">
-        <f aca="false">E10*(1+Allgemein!$B$8)</f>
+      <c r="G10" s="19" t="n">
+        <f aca="false">F10*(1+Allgemein!$B$8)</f>
         <v>1892.1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="B11" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E11" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C11" s="18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>2090</v>
       </c>
-      <c r="F11" s="19" t="n">
-        <f aca="false">E11*(1+Allgemein!$B$8)</f>
+      <c r="G11" s="19" t="n">
+        <f aca="false">F11*(1+Allgemein!$B$8)</f>
         <v>2487.1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" s="18" t="n">
+        <v>64</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" s="18" t="n">
         <v>2.5</v>
       </c>
-      <c r="D12" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="F12" s="12" t="n">
         <v>1390</v>
       </c>
-      <c r="F12" s="19" t="n">
-        <f aca="false">E12*(1+Allgemein!$B$8)</f>
+      <c r="G12" s="19" t="n">
+        <f aca="false">F12*(1+Allgemein!$B$8)</f>
         <v>1654.1</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" s="18" t="n">
+        <v>64</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" s="18" t="n">
         <v>3.5</v>
       </c>
-      <c r="D13" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="E13" s="12" t="n">
+      <c r="E13" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="F13" s="12" t="n">
         <v>1550</v>
       </c>
-      <c r="F13" s="19" t="n">
-        <f aca="false">E13*(1+Allgemein!$B$8)</f>
+      <c r="G13" s="19" t="n">
+        <f aca="false">F13*(1+Allgemein!$B$8)</f>
         <v>1844.5</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" s="18" t="n">
+        <v>64</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" s="18" t="n">
         <v>4.6</v>
       </c>
-      <c r="D14" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="E14" s="12" t="n">
+      <c r="E14" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="F14" s="12" t="n">
         <v>1790</v>
       </c>
-      <c r="F14" s="19" t="n">
-        <f aca="false">E14*(1+Allgemein!$B$8)</f>
+      <c r="G14" s="19" t="n">
+        <f aca="false">F14*(1+Allgemein!$B$8)</f>
         <v>2130.1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="C15" s="18" t="n">
+        <v>64</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="D15" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="E15" s="12" t="n">
+      <c r="E15" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="F15" s="12" t="n">
         <v>1990</v>
       </c>
-      <c r="F15" s="19" t="n">
-        <f aca="false">E15*(1+Allgemein!$B$8)</f>
+      <c r="G15" s="19" t="n">
+        <f aca="false">F15*(1+Allgemein!$B$8)</f>
         <v>2368.1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="B16" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E16" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>2390</v>
       </c>
-      <c r="F16" s="19" t="n">
-        <f aca="false">E16*(1+Allgemein!$B$8)</f>
+      <c r="G16" s="19" t="n">
+        <f aca="false">F16*(1+Allgemein!$B$8)</f>
         <v>2844.1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" s="18" t="n">
+        <v>77</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" s="18" t="n">
         <v>2.5</v>
       </c>
-      <c r="D17" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="E17" s="12" t="n">
+      <c r="E17" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17" s="12" t="n">
         <v>1090</v>
       </c>
-      <c r="F17" s="19" t="n">
-        <f aca="false">E17*(1+Allgemein!$B$8)</f>
+      <c r="G17" s="19" t="n">
+        <f aca="false">F17*(1+Allgemein!$B$8)</f>
         <v>1297.1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="C18" s="18" t="n">
+        <v>77</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" s="18" t="n">
         <v>3.5</v>
       </c>
-      <c r="D18" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="E18" s="12" t="n">
+      <c r="E18" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="F18" s="12" t="n">
         <v>1240</v>
       </c>
-      <c r="F18" s="19" t="n">
-        <f aca="false">E18*(1+Allgemein!$B$8)</f>
+      <c r="G18" s="19" t="n">
+        <f aca="false">F18*(1+Allgemein!$B$8)</f>
         <v>1475.6</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="17" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" s="18" t="n">
+        <v>77</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="D19" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="E19" s="12" t="n">
+      <c r="E19" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="F19" s="12" t="n">
         <v>1690</v>
       </c>
-      <c r="F19" s="19" t="n">
-        <f aca="false">E19*(1+Allgemein!$B$8)</f>
+      <c r="G19" s="19" t="n">
+        <f aca="false">F19*(1+Allgemein!$B$8)</f>
         <v>2011.1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="17" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="B20" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="C20" s="18" t="n">
+      <c r="C20" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="D20" s="18" t="n">
         <v>2.5</v>
       </c>
-      <c r="D20" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="E20" s="12" t="n">
+      <c r="E20" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="F20" s="12" t="n">
         <v>1490</v>
       </c>
-      <c r="F20" s="19" t="n">
-        <f aca="false">E20*(1+Allgemein!$B$8)</f>
+      <c r="G20" s="19" t="n">
+        <f aca="false">F20*(1+Allgemein!$B$8)</f>
         <v>1773.1</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="17" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="C21" s="18" t="n">
+        <v>77</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D21" s="18" t="n">
         <v>3.5</v>
       </c>
-      <c r="D21" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="E21" s="12" t="n">
+      <c r="E21" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="F21" s="12" t="n">
         <v>1690</v>
       </c>
-      <c r="F21" s="19" t="n">
-        <f aca="false">E21*(1+Allgemein!$B$8)</f>
+      <c r="G21" s="19" t="n">
+        <f aca="false">F21*(1+Allgemein!$B$8)</f>
         <v>2011.1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="17" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="C22" s="18" t="n">
+        <v>77</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="D22" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="E22" s="12" t="n">
+      <c r="E22" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="F22" s="12" t="n">
         <v>2190</v>
       </c>
-      <c r="F22" s="19" t="n">
-        <f aca="false">E22*(1+Allgemein!$B$8)</f>
+      <c r="G22" s="19" t="n">
+        <f aca="false">F22*(1+Allgemein!$B$8)</f>
         <v>2606.1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="17" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="C23" s="18" t="n">
+        <v>84</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="D23" s="18" t="n">
         <v>2.5</v>
       </c>
-      <c r="D23" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="E23" s="12" t="n">
+      <c r="E23" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="F23" s="12" t="n">
         <v>1150</v>
       </c>
-      <c r="F23" s="19" t="n">
-        <f aca="false">E23*(1+Allgemein!$B$8)</f>
+      <c r="G23" s="19" t="n">
+        <f aca="false">F23*(1+Allgemein!$B$8)</f>
         <v>1368.5</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="17" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="C24" s="18" t="n">
+        <v>84</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="D24" s="18" t="n">
         <v>3.5</v>
       </c>
-      <c r="D24" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="E24" s="12" t="n">
+      <c r="E24" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="F24" s="12" t="n">
         <v>1290</v>
       </c>
-      <c r="F24" s="19" t="n">
-        <f aca="false">E24*(1+Allgemein!$B$8)</f>
+      <c r="G24" s="19" t="n">
+        <f aca="false">F24*(1+Allgemein!$B$8)</f>
         <v>1535.1</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="17" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="C25" s="18" t="n">
+        <v>84</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D25" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="D25" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="E25" s="12" t="n">
+      <c r="E25" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="F25" s="12" t="n">
         <v>1750</v>
       </c>
-      <c r="F25" s="19" t="n">
-        <f aca="false">E25*(1+Allgemein!$B$8)</f>
+      <c r="G25" s="19" t="n">
+        <f aca="false">F25*(1+Allgemein!$B$8)</f>
         <v>2082.5</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="17" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="B26" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C26" s="18" t="n">
+      <c r="C26" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="D26" s="18" t="n">
         <v>7.1</v>
       </c>
-      <c r="D26" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="E26" s="12" t="n">
+      <c r="E26" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="F26" s="12" t="n">
         <v>2390</v>
       </c>
-      <c r="F26" s="19" t="n">
-        <f aca="false">E26*(1+Allgemein!$B$8)</f>
+      <c r="G26" s="19" t="n">
+        <f aca="false">F26*(1+Allgemein!$B$8)</f>
         <v>2844.1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>59</v>
+        <v>62</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="17" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="C31" s="18" t="n">
+        <v>64</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D31" s="18" t="n">
         <v>2.5</v>
       </c>
-      <c r="D31" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="E31" s="12" t="n">
+      <c r="E31" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="F31" s="12" t="n">
         <v>420</v>
       </c>
-      <c r="F31" s="19" t="n">
-        <f aca="false">E31*(1+Allgemein!$B$8)</f>
+      <c r="G31" s="19" t="n">
+        <f aca="false">F31*(1+Allgemein!$B$8)</f>
         <v>499.8</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="17" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="C32" s="18" t="n">
+        <v>64</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="D32" s="18" t="n">
         <v>3.3</v>
       </c>
-      <c r="D32" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="E32" s="12" t="n">
+      <c r="E32" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="F32" s="12" t="n">
         <v>470</v>
       </c>
-      <c r="F32" s="19" t="n">
-        <f aca="false">E32*(1+Allgemein!$B$8)</f>
+      <c r="G32" s="19" t="n">
+        <f aca="false">F32*(1+Allgemein!$B$8)</f>
         <v>559.3</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="17" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="C33" s="18" t="n">
+        <v>64</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="D33" s="18" t="n">
         <v>4.2</v>
       </c>
-      <c r="D33" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="E33" s="12" t="n">
+      <c r="E33" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="F33" s="12" t="n">
         <v>560</v>
       </c>
-      <c r="F33" s="19" t="n">
-        <f aca="false">E33*(1+Allgemein!$B$8)</f>
+      <c r="G33" s="19" t="n">
+        <f aca="false">F33*(1+Allgemein!$B$8)</f>
         <v>666.4</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="17" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="C34" s="18" t="n">
+        <v>64</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D34" s="18" t="n">
         <v>2.5</v>
       </c>
-      <c r="D34" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="E34" s="12" t="n">
+      <c r="E34" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="F34" s="12" t="n">
         <v>590</v>
       </c>
-      <c r="F34" s="19" t="n">
-        <f aca="false">E34*(1+Allgemein!$B$8)</f>
+      <c r="G34" s="19" t="n">
+        <f aca="false">F34*(1+Allgemein!$B$8)</f>
         <v>702.1</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="17" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="C35" s="18" t="n">
+        <v>64</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="D35" s="18" t="n">
         <v>3.5</v>
       </c>
-      <c r="D35" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="E35" s="12" t="n">
+      <c r="E35" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="F35" s="12" t="n">
         <v>660</v>
       </c>
-      <c r="F35" s="19" t="n">
-        <f aca="false">E35*(1+Allgemein!$B$8)</f>
+      <c r="G35" s="19" t="n">
+        <f aca="false">F35*(1+Allgemein!$B$8)</f>
         <v>785.4</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="17" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="C36" s="18" t="n">
+        <v>64</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="D36" s="18" t="n">
         <v>4.6</v>
       </c>
-      <c r="D36" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="E36" s="12" t="n">
+      <c r="E36" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="F36" s="12" t="n">
         <v>760</v>
       </c>
-      <c r="F36" s="19" t="n">
-        <f aca="false">E36*(1+Allgemein!$B$8)</f>
+      <c r="G36" s="19" t="n">
+        <f aca="false">F36*(1+Allgemein!$B$8)</f>
         <v>904.4</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="17" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="C37" s="18" t="n">
+        <v>77</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="D37" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="D37" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="E37" s="12" t="n">
+      <c r="E37" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="F37" s="12" t="n">
         <v>560</v>
       </c>
-      <c r="F37" s="19" t="n">
-        <f aca="false">E37*(1+Allgemein!$B$8)</f>
+      <c r="G37" s="19" t="n">
+        <f aca="false">F37*(1+Allgemein!$B$8)</f>
         <v>666.4</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="17" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="C38" s="18" t="n">
+        <v>77</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="D38" s="18" t="n">
         <v>2.5</v>
       </c>
-      <c r="D38" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="E38" s="12" t="n">
+      <c r="E38" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="F38" s="12" t="n">
         <v>600</v>
       </c>
-      <c r="F38" s="19" t="n">
-        <f aca="false">E38*(1+Allgemein!$B$8)</f>
+      <c r="G38" s="19" t="n">
+        <f aca="false">F38*(1+Allgemein!$B$8)</f>
         <v>714</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="17" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="C39" s="18" t="n">
+        <v>77</v>
+      </c>
+      <c r="C39" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="D39" s="18" t="n">
         <v>3.5</v>
       </c>
-      <c r="D39" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="E39" s="12" t="n">
+      <c r="E39" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="F39" s="12" t="n">
         <v>680</v>
       </c>
-      <c r="F39" s="19" t="n">
-        <f aca="false">E39*(1+Allgemein!$B$8)</f>
+      <c r="G39" s="19" t="n">
+        <f aca="false">F39*(1+Allgemein!$B$8)</f>
         <v>809.2</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="17" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="C40" s="18" t="n">
+        <v>77</v>
+      </c>
+      <c r="C40" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="D40" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="D40" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="E40" s="12" t="n">
+      <c r="E40" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="F40" s="12" t="n">
         <v>860</v>
       </c>
-      <c r="F40" s="19" t="n">
-        <f aca="false">E40*(1+Allgemein!$B$8)</f>
+      <c r="G40" s="19" t="n">
+        <f aca="false">F40*(1+Allgemein!$B$8)</f>
         <v>1023.4</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="17" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="C41" s="18" t="n">
+        <v>77</v>
+      </c>
+      <c r="C41" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="D41" s="18" t="n">
         <v>2.5</v>
       </c>
-      <c r="D41" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="E41" s="12" t="n">
+      <c r="E41" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="F41" s="12" t="n">
         <v>430</v>
       </c>
-      <c r="F41" s="19" t="n">
-        <f aca="false">E41*(1+Allgemein!$B$8)</f>
+      <c r="G41" s="19" t="n">
+        <f aca="false">F41*(1+Allgemein!$B$8)</f>
         <v>511.7</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="17" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="B42" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="C42" s="18" t="n">
+        <v>77</v>
+      </c>
+      <c r="C42" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="D42" s="18" t="n">
         <v>3.5</v>
       </c>
-      <c r="D42" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="E42" s="12" t="n">
+      <c r="E42" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="F42" s="12" t="n">
         <v>490</v>
       </c>
-      <c r="F42" s="19" t="n">
-        <f aca="false">E42*(1+Allgemein!$B$8)</f>
+      <c r="G42" s="19" t="n">
+        <f aca="false">F42*(1+Allgemein!$B$8)</f>
         <v>583.1</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="17" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="C43" s="18" t="n">
+        <v>77</v>
+      </c>
+      <c r="C43" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="D43" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="D43" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="E43" s="12" t="n">
+      <c r="E43" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="F43" s="12" t="n">
         <v>640</v>
       </c>
-      <c r="F43" s="19" t="n">
-        <f aca="false">E43*(1+Allgemein!$B$8)</f>
+      <c r="G43" s="19" t="n">
+        <f aca="false">F43*(1+Allgemein!$B$8)</f>
         <v>761.6</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="9" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>101</v>
+        <v>59</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>59</v>
+        <v>62</v>
+      </c>
+      <c r="G47" s="10" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="17" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="B48" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="C48" s="18" t="n">
+        <v>64</v>
+      </c>
+      <c r="C48" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="D48" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="D48" s="18" t="n">
+      <c r="E48" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="F48" s="12" t="n">
         <v>1590</v>
       </c>
-      <c r="F48" s="19" t="n">
-        <f aca="false">E48*(1+Allgemein!$B$8)</f>
+      <c r="G48" s="19" t="n">
+        <f aca="false">F48*(1+Allgemein!$B$8)</f>
         <v>1892.1</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="17" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="B49" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="C49" s="18" t="n">
+        <v>64</v>
+      </c>
+      <c r="C49" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="D49" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="D49" s="18" t="n">
+      <c r="E49" s="18" t="n">
         <v>5.2</v>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="F49" s="12" t="n">
         <v>1990</v>
       </c>
-      <c r="F49" s="19" t="n">
-        <f aca="false">E49*(1+Allgemein!$B$8)</f>
+      <c r="G49" s="19" t="n">
+        <f aca="false">F49*(1+Allgemein!$B$8)</f>
         <v>2368.1</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="17" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="B50" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="C50" s="18" t="n">
+        <v>64</v>
+      </c>
+      <c r="C50" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="D50" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="D50" s="18" t="n">
+      <c r="E50" s="18" t="n">
         <v>7.5</v>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="F50" s="12" t="n">
         <v>2390</v>
       </c>
-      <c r="F50" s="19" t="n">
-        <f aca="false">E50*(1+Allgemein!$B$8)</f>
+      <c r="G50" s="19" t="n">
+        <f aca="false">F50*(1+Allgemein!$B$8)</f>
         <v>2844.1</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="17" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="B51" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="C51" s="18" t="n">
+        <v>64</v>
+      </c>
+      <c r="C51" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="D51" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="D51" s="18" t="n">
+      <c r="E51" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="F51" s="12" t="n">
         <v>2690</v>
       </c>
-      <c r="F51" s="19" t="n">
-        <f aca="false">E51*(1+Allgemein!$B$8)</f>
+      <c r="G51" s="19" t="n">
+        <f aca="false">F51*(1+Allgemein!$B$8)</f>
         <v>3201.1</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="17" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="B52" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="C52" s="18" t="n">
+        <v>64</v>
+      </c>
+      <c r="C52" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="D52" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="D52" s="18" t="n">
+      <c r="E52" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="F52" s="12" t="n">
         <v>3190</v>
       </c>
-      <c r="F52" s="19" t="n">
-        <f aca="false">E52*(1+Allgemein!$B$8)</f>
+      <c r="G52" s="19" t="n">
+        <f aca="false">F52*(1+Allgemein!$B$8)</f>
         <v>3796.1</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="17" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="B53" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="C53" s="18" t="n">
+        <v>77</v>
+      </c>
+      <c r="C53" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="D53" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="D53" s="18" t="n">
+      <c r="E53" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="E53" s="12" t="n">
+      <c r="F53" s="12" t="n">
         <v>1790</v>
       </c>
-      <c r="F53" s="19" t="n">
-        <f aca="false">E53*(1+Allgemein!$B$8)</f>
+      <c r="G53" s="19" t="n">
+        <f aca="false">F53*(1+Allgemein!$B$8)</f>
         <v>2130.1</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="17" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="B54" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="C54" s="18" t="n">
+        <v>77</v>
+      </c>
+      <c r="C54" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="D54" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="D54" s="18" t="n">
+      <c r="E54" s="18" t="n">
         <v>5.2</v>
       </c>
-      <c r="E54" s="12" t="n">
+      <c r="F54" s="12" t="n">
         <v>2190</v>
       </c>
-      <c r="F54" s="19" t="n">
-        <f aca="false">E54*(1+Allgemein!$B$8)</f>
+      <c r="G54" s="19" t="n">
+        <f aca="false">F54*(1+Allgemein!$B$8)</f>
         <v>2606.1</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="17" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="B55" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="C55" s="18" t="n">
+        <v>77</v>
+      </c>
+      <c r="C55" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="D55" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="D55" s="18" t="n">
+      <c r="E55" s="18" t="n">
         <v>6.8</v>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="F55" s="12" t="n">
         <v>2690</v>
       </c>
-      <c r="F55" s="19" t="n">
-        <f aca="false">E55*(1+Allgemein!$B$8)</f>
+      <c r="G55" s="19" t="n">
+        <f aca="false">F55*(1+Allgemein!$B$8)</f>
         <v>3201.1</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="17" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="B56" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="C56" s="18" t="n">
+        <v>77</v>
+      </c>
+      <c r="C56" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="D56" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="D56" s="18" t="n">
+      <c r="E56" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="E56" s="12" t="n">
+      <c r="F56" s="12" t="n">
         <v>3290</v>
       </c>
-      <c r="F56" s="19" t="n">
-        <f aca="false">E56*(1+Allgemein!$B$8)</f>
+      <c r="G56" s="19" t="n">
+        <f aca="false">F56*(1+Allgemein!$B$8)</f>
         <v>3915.1</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="9" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="15" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="10" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="11" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B61" s="18" t="n">
         <v>6</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D61" s="19" t="n">
         <f aca="false">B61*Allgemein!$B$6</f>
@@ -2825,13 +3108,13 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="11" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B62" s="18" t="n">
         <v>7</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D62" s="19" t="n">
         <f aca="false">B62*Allgemein!$B$6</f>
@@ -2844,13 +3127,13 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="11" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B63" s="18" t="n">
         <v>4</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D63" s="19" t="n">
         <f aca="false">B63*Allgemein!$B$6</f>
@@ -2863,13 +3146,13 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="11" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B64" s="18" t="n">
         <v>0.25</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D64" s="19" t="n">
         <f aca="false">B64*Allgemein!$B$6</f>
@@ -2882,13 +3165,13 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="11" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B65" s="18" t="n">
         <v>0.75</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D65" s="19" t="n">
         <f aca="false">B65*Allgemein!$B$6</f>
@@ -2901,13 +3184,13 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="11" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B66" s="18" t="n">
         <v>0.5</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D66" s="19" t="n">
         <f aca="false">B66*Allgemein!$B$6</f>
@@ -2920,13 +3203,13 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="11" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B67" s="18" t="n">
         <v>2</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D67" s="19" t="n">
         <f aca="false">B67*Allgemein!$B$6</f>
@@ -2939,13 +3222,13 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="11" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B68" s="18" t="n">
         <v>1</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D68" s="19" t="n">
         <f aca="false">B68*Allgemein!$B$6</f>
@@ -2958,35 +3241,35 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="15" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="10" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="11" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B72" s="12" t="n">
         <v>190</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E72" s="19" t="n">
         <f aca="false">B72*(1+Allgemein!$B$8)</f>
@@ -2995,13 +3278,13 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="11" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B73" s="12" t="n">
         <v>150</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E73" s="19" t="n">
         <f aca="false">B73*(1+Allgemein!$B$8)</f>
@@ -3010,13 +3293,13 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="11" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B74" s="12" t="n">
         <v>26</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E74" s="19" t="n">
         <f aca="false">B74*(1+Allgemein!$B$8)</f>
@@ -3025,13 +3308,13 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="11" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B75" s="12" t="n">
         <v>110</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E75" s="19" t="n">
         <f aca="false">B75*(1+Allgemein!$B$8)</f>
@@ -3040,13 +3323,13 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="11" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B76" s="12" t="n">
         <v>360</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E76" s="19" t="n">
         <f aca="false">B76*(1+Allgemein!$B$8)</f>
@@ -3055,13 +3338,13 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="11" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B77" s="12" t="n">
         <v>55</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E77" s="19" t="n">
         <f aca="false">B77*(1+Allgemein!$B$8)</f>
@@ -3070,13 +3353,13 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="11" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B78" s="12" t="n">
         <v>135</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E78" s="19" t="n">
         <f aca="false">B78*(1+Allgemein!$B$8)</f>
@@ -3085,13 +3368,13 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="11" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B79" s="12" t="n">
         <v>170</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E79" s="19" t="n">
         <f aca="false">B79*(1+Allgemein!$B$8)</f>
@@ -3100,51 +3383,55 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="15" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="10" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="11" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B83" s="12" t="n">
         <v>149</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="11" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B84" s="18" t="n">
         <v>0.1</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D7:D26 D31:D43" type="list">
+  <dataValidations count="2">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="A7:A26 A31:A43 A48:A56" type="list">
+      <formula1>"Ja,Nein"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E7:E26 E31:E43" type="list">
       <formula1>"Standard,Premium"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -3164,7 +3451,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
@@ -3177,167 +3464,185 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>59</v>
+        <v>62</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>137</v>
+        <v>47</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="C7" s="18" t="n">
+        <v>141</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="D7" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="E7" s="12" t="n">
         <v>8900</v>
       </c>
-      <c r="E7" s="19" t="n">
-        <f aca="false">D7*(1+Allgemein!$B$8)</f>
+      <c r="F7" s="19" t="n">
+        <f aca="false">E7*(1+Allgemein!$B$8)</f>
         <v>10591</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
-        <v>137</v>
+        <v>47</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="C8" s="18" t="n">
+        <v>141</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="D8" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="E8" s="12" t="n">
         <v>10400</v>
       </c>
-      <c r="E8" s="19" t="n">
-        <f aca="false">D8*(1+Allgemein!$B$8)</f>
+      <c r="F8" s="19" t="n">
+        <f aca="false">E8*(1+Allgemein!$B$8)</f>
         <v>12376</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>137</v>
+        <v>47</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="C9" s="18" t="n">
+        <v>141</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="D9" s="18" t="n">
         <v>12</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="E9" s="12" t="n">
         <v>11900</v>
       </c>
-      <c r="E9" s="19" t="n">
-        <f aca="false">D9*(1+Allgemein!$B$8)</f>
+      <c r="F9" s="19" t="n">
+        <f aca="false">E9*(1+Allgemein!$B$8)</f>
         <v>14161</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>137</v>
+        <v>47</v>
       </c>
       <c r="B10" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="C10" s="18" t="n">
+      <c r="C10" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="D10" s="18" t="n">
         <v>16</v>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="E10" s="12" t="n">
         <v>13400</v>
       </c>
-      <c r="E10" s="19" t="n">
-        <f aca="false">D10*(1+Allgemein!$B$8)</f>
+      <c r="F10" s="19" t="n">
+        <f aca="false">E10*(1+Allgemein!$B$8)</f>
         <v>15946</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
-        <v>137</v>
+        <v>47</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="C11" s="18" t="n">
+        <v>141</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="D11" s="18" t="n">
         <v>18</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="E11" s="12" t="n">
         <v>14900</v>
       </c>
-      <c r="E11" s="19" t="n">
-        <f aca="false">D11*(1+Allgemein!$B$8)</f>
+      <c r="F11" s="19" t="n">
+        <f aca="false">E11*(1+Allgemein!$B$8)</f>
         <v>17731</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B16" s="18" t="n">
         <v>30</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D16" s="19" t="n">
         <f aca="false">B16*Allgemein!$B$6</f>
@@ -3350,13 +3655,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B17" s="18" t="n">
         <v>12</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D17" s="19" t="n">
         <f aca="false">B17*Allgemein!$B$6</f>
@@ -3369,13 +3674,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B18" s="18" t="n">
         <v>6</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D18" s="19" t="n">
         <f aca="false">B18*Allgemein!$B$6</f>
@@ -3388,13 +3693,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B19" s="18" t="n">
         <v>10</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D19" s="19" t="n">
         <f aca="false">B19*Allgemein!$B$6</f>
@@ -3407,13 +3712,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B20" s="18" t="n">
         <v>2.5</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D20" s="19" t="n">
         <f aca="false">B20*Allgemein!$B$6</f>
@@ -3426,13 +3731,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B21" s="18" t="n">
         <v>6</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D21" s="19" t="n">
         <f aca="false">B21*Allgemein!$B$6</f>
@@ -3445,35 +3750,35 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B25" s="12" t="n">
         <v>4200</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E25" s="19" t="n">
         <f aca="false">B25*(1+Allgemein!$B$8)</f>
@@ -3482,13 +3787,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B26" s="12" t="n">
         <v>900</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E26" s="19" t="n">
         <f aca="false">B26*(1+Allgemein!$B$8)</f>
@@ -3497,13 +3802,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B27" s="12" t="n">
         <v>150</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E27" s="19" t="n">
         <f aca="false">B27*(1+Allgemein!$B$8)</f>
@@ -3512,13 +3817,13 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B28" s="12" t="n">
         <v>350</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E28" s="19" t="n">
         <f aca="false">B28*(1+Allgemein!$B$8)</f>
@@ -3527,13 +3832,13 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B29" s="12" t="n">
         <v>380</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E29" s="19" t="n">
         <f aca="false">B29*(1+Allgemein!$B$8)</f>
@@ -3542,13 +3847,13 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B30" s="12" t="n">
         <v>650</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E30" s="19" t="n">
         <f aca="false">B30*(1+Allgemein!$B$8)</f>
@@ -3557,38 +3862,44 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B34" s="18" t="n">
         <v>0.25</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="A7:A11" type="list">
+      <formula1>"Ja,Nein"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -3604,7 +3915,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
@@ -3617,630 +3928,647 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>159</v>
+        <v>59</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>59</v>
+        <v>164</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>161</v>
+        <v>47</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>162</v>
-      </c>
-      <c r="C7" s="18" t="n">
+        <v>165</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="D7" s="18" t="n">
         <v>450</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="E7" s="12" t="n">
         <v>118</v>
       </c>
-      <c r="E7" s="19" t="n">
-        <f aca="false">D7*(1+Allgemein!$B$8)</f>
+      <c r="F7" s="19" t="n">
+        <f aca="false">E7*(1+Allgemein!$B$8)</f>
         <v>140.42</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
-        <v>163</v>
+        <v>47</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="C8" s="18" t="n">
+        <v>167</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="D8" s="18" t="n">
         <v>400</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="E8" s="12" t="n">
         <v>175</v>
       </c>
-      <c r="E8" s="19" t="n">
-        <f aca="false">D8*(1+Allgemein!$B$8)</f>
+      <c r="F8" s="19" t="n">
+        <f aca="false">E8*(1+Allgemein!$B$8)</f>
         <v>208.25</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>59</v>
+        <v>62</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
-        <v>167</v>
+        <v>47</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="C14" s="18" t="n">
+        <v>171</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="D14" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="D14" s="12" t="n">
+      <c r="E14" s="12" t="n">
         <v>1750</v>
       </c>
-      <c r="E14" s="19" t="n">
-        <f aca="false">D14*(1+Allgemein!$B$8)</f>
+      <c r="F14" s="19" t="n">
+        <f aca="false">E14*(1+Allgemein!$B$8)</f>
         <v>2082.5</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>167</v>
+        <v>47</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="C15" s="18" t="n">
+        <v>171</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="D15" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="E15" s="12" t="n">
         <v>2050</v>
       </c>
-      <c r="E15" s="19" t="n">
-        <f aca="false">D15*(1+Allgemein!$B$8)</f>
+      <c r="F15" s="19" t="n">
+        <f aca="false">E15*(1+Allgemein!$B$8)</f>
         <v>2439.5</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="17" t="s">
-        <v>167</v>
+        <v>47</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>170</v>
-      </c>
-      <c r="C16" s="18" t="n">
+        <v>171</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="D16" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="E16" s="12" t="n">
         <v>2550</v>
       </c>
-      <c r="E16" s="19" t="n">
-        <f aca="false">D16*(1+Allgemein!$B$8)</f>
+      <c r="F16" s="19" t="n">
+        <f aca="false">E16*(1+Allgemein!$B$8)</f>
         <v>3034.5</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
-        <v>167</v>
+        <v>47</v>
       </c>
       <c r="B17" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="C17" s="18" t="n">
+      <c r="C17" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="D17" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="E17" s="12" t="n">
         <v>2850</v>
       </c>
-      <c r="E17" s="19" t="n">
-        <f aca="false">D17*(1+Allgemein!$B$8)</f>
+      <c r="F17" s="19" t="n">
+        <f aca="false">E17*(1+Allgemein!$B$8)</f>
         <v>3391.5</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>167</v>
+        <v>47</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="C18" s="18" t="n">
+        <v>171</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="D18" s="18" t="n">
         <v>15</v>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="E18" s="12" t="n">
         <v>3600</v>
       </c>
-      <c r="E18" s="19" t="n">
-        <f aca="false">D18*(1+Allgemein!$B$8)</f>
+      <c r="F18" s="19" t="n">
+        <f aca="false">E18*(1+Allgemein!$B$8)</f>
         <v>4284</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>175</v>
+        <v>59</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>59</v>
+        <v>62</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="17" t="s">
-        <v>176</v>
+        <v>47</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>177</v>
-      </c>
-      <c r="C24" s="18" t="n">
+        <v>180</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="D24" s="18" t="n">
         <v>5.1</v>
       </c>
-      <c r="D24" s="12" t="n">
+      <c r="E24" s="12" t="n">
         <v>2950</v>
       </c>
-      <c r="E24" s="19" t="n">
-        <f aca="false">D24*(1+Allgemein!$B$8)</f>
+      <c r="F24" s="19" t="n">
+        <f aca="false">E24*(1+Allgemein!$B$8)</f>
         <v>3510.5</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="17" t="s">
-        <v>176</v>
+        <v>47</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>178</v>
-      </c>
-      <c r="C25" s="18" t="n">
+        <v>180</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="D25" s="18" t="n">
         <v>7.7</v>
       </c>
-      <c r="D25" s="12" t="n">
+      <c r="E25" s="12" t="n">
         <v>4050</v>
       </c>
-      <c r="E25" s="19" t="n">
-        <f aca="false">D25*(1+Allgemein!$B$8)</f>
+      <c r="F25" s="19" t="n">
+        <f aca="false">E25*(1+Allgemein!$B$8)</f>
         <v>4819.5</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="17" t="s">
-        <v>176</v>
+        <v>47</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>179</v>
-      </c>
-      <c r="C26" s="18" t="n">
+        <v>180</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="D26" s="18" t="n">
         <v>10.2</v>
       </c>
-      <c r="D26" s="12" t="n">
+      <c r="E26" s="12" t="n">
         <v>5150</v>
       </c>
-      <c r="E26" s="19" t="n">
-        <f aca="false">D26*(1+Allgemein!$B$8)</f>
+      <c r="F26" s="19" t="n">
+        <f aca="false">E26*(1+Allgemein!$B$8)</f>
         <v>6128.5</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>114</v>
+      <c r="A30" s="9" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="B31" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="C31" s="11"/>
+      <c r="A31" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="B32" s="20" t="s">
-        <v>181</v>
-      </c>
-      <c r="C32" s="11"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="B33" s="12" t="n">
-        <v>890</v>
-      </c>
-      <c r="C33" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="B32" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D32" s="19" t="n">
+        <f aca="false">B32*Allgemein!$B$6</f>
+        <v>340</v>
+      </c>
+      <c r="E32" s="19" t="n">
+        <f aca="false">D32*(1+Allgemein!$B$8)</f>
+        <v>404.6</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="15" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C35" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E33" s="19" t="n">
-        <f aca="false">B33*(1+Allgemein!$B$8)</f>
-        <v>1059.1</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="B34" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="D34" s="19" t="n">
-        <f aca="false">B34*Allgemein!$B$6</f>
-        <v>340</v>
-      </c>
-      <c r="E34" s="19" t="n">
-        <f aca="false">D34*(1+Allgemein!$B$8)</f>
-        <v>404.6</v>
+      <c r="D35" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="15" t="s">
-        <v>111</v>
+      <c r="A36" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B36" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D36" s="19" t="n">
+        <f aca="false">B36*Allgemein!$B$6</f>
+        <v>544</v>
+      </c>
+      <c r="E36" s="19" t="n">
+        <f aca="false">D36*(1+Allgemein!$B$8)</f>
+        <v>647.36</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>114</v>
+      <c r="A37" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="B37" s="18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D37" s="19" t="n">
+        <f aca="false">B37*Allgemein!$B$6</f>
+        <v>40.8</v>
+      </c>
+      <c r="E37" s="19" t="n">
+        <f aca="false">D37*(1+Allgemein!$B$8)</f>
+        <v>48.552</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B38" s="18" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D38" s="19" t="n">
         <f aca="false">B38*Allgemein!$B$6</f>
-        <v>544</v>
+        <v>272</v>
       </c>
       <c r="E38" s="19" t="n">
         <f aca="false">D38*(1+Allgemein!$B$8)</f>
-        <v>647.36</v>
+        <v>323.68</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B39" s="18" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D39" s="19" t="n">
         <f aca="false">B39*Allgemein!$B$6</f>
-        <v>40.8</v>
+        <v>272</v>
       </c>
       <c r="E39" s="19" t="n">
         <f aca="false">D39*(1+Allgemein!$B$8)</f>
-        <v>48.552</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="11" t="s">
-        <v>186</v>
-      </c>
-      <c r="B40" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="C40" s="11" t="s">
+        <v>323.68</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="15" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="D40" s="19" t="n">
-        <f aca="false">B40*Allgemein!$B$6</f>
-        <v>272</v>
-      </c>
-      <c r="E40" s="19" t="n">
-        <f aca="false">D40*(1+Allgemein!$B$8)</f>
-        <v>323.68</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="B41" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="C41" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="D41" s="19" t="n">
-        <f aca="false">B41*Allgemein!$B$6</f>
-        <v>272</v>
-      </c>
-      <c r="E41" s="19" t="n">
-        <f aca="false">D41*(1+Allgemein!$B$8)</f>
-        <v>323.68</v>
+      <c r="B42" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="15" t="s">
-        <v>124</v>
+      <c r="A43" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="B43" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E43" s="19" t="n">
+        <f aca="false">B43*(1+Allgemein!$B$8)</f>
+        <v>57.12</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="B44" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D44" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="E44" s="10" t="s">
-        <v>114</v>
+      <c r="A44" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="B44" s="12" t="n">
+        <v>480</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E44" s="19" t="n">
+        <f aca="false">B44*(1+Allgemein!$B$8)</f>
+        <v>571.2</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="11" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B45" s="12" t="n">
-        <v>48</v>
+        <v>650</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E45" s="19" t="n">
         <f aca="false">B45*(1+Allgemein!$B$8)</f>
-        <v>57.12</v>
+        <v>773.5</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="11" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B46" s="12" t="n">
-        <v>480</v>
+        <v>450</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E46" s="19" t="n">
         <f aca="false">B46*(1+Allgemein!$B$8)</f>
-        <v>571.2</v>
+        <v>535.5</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="11" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B47" s="12" t="n">
-        <v>650</v>
+        <v>250</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E47" s="19" t="n">
         <f aca="false">B47*(1+Allgemein!$B$8)</f>
-        <v>773.5</v>
+        <v>297.5</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="11" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B48" s="12" t="n">
         <v>450</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E48" s="19" t="n">
         <f aca="false">B48*(1+Allgemein!$B$8)</f>
         <v>535.5</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="B49" s="12" t="n">
-        <v>250</v>
-      </c>
-      <c r="C49" s="11" t="s">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="15" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E49" s="19" t="n">
-        <f aca="false">B49*(1+Allgemein!$B$8)</f>
-        <v>297.5</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="B50" s="12" t="n">
-        <v>450</v>
-      </c>
-      <c r="C50" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E50" s="19" t="n">
-        <f aca="false">B50*(1+Allgemein!$B$8)</f>
-        <v>535.5</v>
+      <c r="D51" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="15" t="s">
-        <v>194</v>
+      <c r="A52" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B52" s="18" t="n">
+        <v>950</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="B53" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C53" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D53" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="E53" s="10" t="s">
-        <v>114</v>
+      <c r="A53" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="B53" s="20" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="B54" s="18" t="n">
-        <v>950</v>
+        <v>202</v>
+      </c>
+      <c r="B54" s="20" t="n">
+        <v>0.077</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="11" t="s">
-        <v>197</v>
-      </c>
-      <c r="B55" s="21" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="C55" s="11" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="B56" s="21" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="C56" s="11" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="A7:A8 A14:A18 A24:A26" type="list">
+      <formula1>"Ja,Nein"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -4269,54 +4597,54 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>202</v>
+        <v>204</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>205</v>
       </c>
       <c r="C6" s="11"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B7" s="12" t="n">
         <v>900</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E7" s="19" t="n">
         <f aca="false">B7*(1+Allgemein!$B$8)</f>
@@ -4325,13 +4653,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B8" s="18" t="n">
         <v>12</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D8" s="19" t="n">
         <f aca="false">B8*Allgemein!$B$6</f>
@@ -4344,13 +4672,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B9" s="12" t="n">
         <v>160</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E9" s="19" t="n">
         <f aca="false">B9*(1+Allgemein!$B$8)</f>
@@ -4359,13 +4687,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B10" s="18" t="n">
         <v>1.5</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D10" s="19" t="n">
         <f aca="false">B10*Allgemein!$B$6</f>
@@ -4378,13 +4706,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B11" s="12" t="n">
         <v>120</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E11" s="19" t="n">
         <f aca="false">B11*(1+Allgemein!$B$8)</f>
@@ -4393,13 +4721,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B12" s="18" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D12" s="19" t="n">
         <f aca="false">B12*Allgemein!$B$6</f>
@@ -4412,13 +4740,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B13" s="12" t="n">
         <v>140</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E13" s="19" t="n">
         <f aca="false">B13*(1+Allgemein!$B$8)</f>
@@ -4427,13 +4755,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B14" s="18" t="n">
         <v>1.5</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D14" s="19" t="n">
         <f aca="false">B14*Allgemein!$B$6</f>
@@ -4446,13 +4774,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B15" s="12" t="n">
         <v>600</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E15" s="19" t="n">
         <f aca="false">B15*(1+Allgemein!$B$8)</f>
@@ -4461,13 +4789,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B16" s="18" t="n">
         <v>5</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D16" s="19" t="n">
         <f aca="false">B16*Allgemein!$B$6</f>
@@ -4480,44 +4808,44 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="B20" s="20" t="s">
-        <v>214</v>
+        <v>204</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>217</v>
       </c>
       <c r="C20" s="11"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B21" s="12" t="n">
         <v>180</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E21" s="19" t="n">
         <f aca="false">B21*(1+Allgemein!$B$8)</f>
@@ -4526,13 +4854,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B22" s="18" t="n">
         <v>3</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D22" s="19" t="n">
         <f aca="false">B22*Allgemein!$B$6</f>
@@ -4545,13 +4873,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B23" s="12" t="n">
         <v>75</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E23" s="19" t="n">
         <f aca="false">B23*(1+Allgemein!$B$8)</f>
@@ -4560,13 +4888,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B24" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D24" s="19" t="n">
         <f aca="false">B24*Allgemein!$B$6</f>
@@ -4579,13 +4907,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B25" s="12" t="n">
         <v>65</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E25" s="19" t="n">
         <f aca="false">B25*(1+Allgemein!$B$8)</f>
@@ -4594,13 +4922,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B26" s="18" t="n">
         <v>0.75</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D26" s="19" t="n">
         <f aca="false">B26*Allgemein!$B$6</f>
@@ -4613,13 +4941,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B27" s="12" t="n">
         <v>70</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E27" s="19" t="n">
         <f aca="false">B27*(1+Allgemein!$B$8)</f>
@@ -4628,13 +4956,13 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B28" s="18" t="n">
         <v>1.25</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D28" s="19" t="n">
         <f aca="false">B28*Allgemein!$B$6</f>
@@ -4647,13 +4975,13 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B29" s="12" t="n">
         <v>450</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E29" s="19" t="n">
         <f aca="false">B29*(1+Allgemein!$B$8)</f>
@@ -4662,13 +4990,13 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B30" s="18" t="n">
         <v>4</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D30" s="19" t="n">
         <f aca="false">B30*Allgemein!$B$6</f>
@@ -4681,44 +5009,44 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="B34" s="20" t="s">
-        <v>216</v>
+        <v>204</v>
+      </c>
+      <c r="B34" s="21" t="s">
+        <v>219</v>
       </c>
       <c r="C34" s="11"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="11" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B35" s="12" t="n">
         <v>1300</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E35" s="19" t="n">
         <f aca="false">B35*(1+Allgemein!$B$8)</f>
@@ -4727,13 +5055,13 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B36" s="18" t="n">
         <v>14</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D36" s="19" t="n">
         <f aca="false">B36*Allgemein!$B$6</f>
@@ -4746,13 +5074,13 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B37" s="12" t="n">
         <v>180</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E37" s="19" t="n">
         <f aca="false">B37*(1+Allgemein!$B$8)</f>
@@ -4761,13 +5089,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B38" s="18" t="n">
         <v>2</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D38" s="19" t="n">
         <f aca="false">B38*Allgemein!$B$6</f>
@@ -4780,13 +5108,13 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B39" s="12" t="n">
         <v>140</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E39" s="19" t="n">
         <f aca="false">B39*(1+Allgemein!$B$8)</f>
@@ -4795,13 +5123,13 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B40" s="18" t="n">
         <v>1.5</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D40" s="19" t="n">
         <f aca="false">B40*Allgemein!$B$6</f>
@@ -4814,13 +5142,13 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B41" s="12" t="n">
         <v>150</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E41" s="19" t="n">
         <f aca="false">B41*(1+Allgemein!$B$8)</f>
@@ -4829,13 +5157,13 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="11" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B42" s="18" t="n">
         <v>1.75</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D42" s="19" t="n">
         <f aca="false">B42*Allgemein!$B$6</f>
@@ -4848,13 +5176,13 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="11" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B43" s="12" t="n">
         <v>700</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E43" s="19" t="n">
         <f aca="false">B43*(1+Allgemein!$B$8)</f>
@@ -4863,13 +5191,13 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="11" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B44" s="18" t="n">
         <v>7</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D44" s="19" t="n">
         <f aca="false">B44*Allgemein!$B$6</f>
@@ -4882,46 +5210,46 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="10" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="11" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="11" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B49" s="18" t="n">
         <v>4</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D49" s="19" t="n">
         <f aca="false">B49*Allgemein!$B$6</f>
@@ -4948,7 +5276,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
@@ -4961,371 +5289,343 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>49</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>114</v>
+      <c r="A5" s="9" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="B6" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="C6" s="11" t="s">
+      <c r="A6" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="15" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="9" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>236</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>599</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>799</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>849</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>241</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>649</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>243</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>244</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>699</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>245</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>246</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>749</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>228</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>1199</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>229</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>245</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>999</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="15" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="19" t="n">
-        <f aca="false">B6*(1+Allgemein!$B$8)</f>
-        <v>49.98</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="B7" s="18" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="D7" s="19" t="n">
-        <f aca="false">B7*Allgemein!$B$6</f>
-        <v>51</v>
-      </c>
-      <c r="E7" s="19" t="n">
-        <f aca="false">D7*(1+Allgemein!$B$8)</f>
-        <v>60.69</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="B8" s="12" t="n">
-        <v>52</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="19" t="n">
-        <f aca="false">B8*(1+Allgemein!$B$8)</f>
-        <v>61.88</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="B9" s="18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="D9" s="19" t="n">
-        <f aca="false">B9*Allgemein!$B$6</f>
-        <v>81.6</v>
-      </c>
-      <c r="E9" s="19" t="n">
-        <f aca="false">D9*(1+Allgemein!$B$8)</f>
-        <v>97.104</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="B10" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="19" t="n">
-        <f aca="false">B10*(1+Allgemein!$B$8)</f>
-        <v>35.7</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="B11" s="18" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="D11" s="19" t="n">
-        <f aca="false">B11*Allgemein!$B$6</f>
-        <v>40.8</v>
-      </c>
-      <c r="E11" s="19" t="n">
-        <f aca="false">D11*(1+Allgemein!$B$8)</f>
-        <v>48.552</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="15" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="B15" s="12" t="n">
-        <v>1650</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="19" t="n">
-        <f aca="false">B15*(1+Allgemein!$B$8)</f>
-        <v>1963.5</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="B16" s="18" t="n">
-        <v>18</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="D16" s="19" t="n">
-        <f aca="false">B16*Allgemein!$B$6</f>
-        <v>1224</v>
-      </c>
-      <c r="E16" s="19" t="n">
-        <f aca="false">D16*(1+Allgemein!$B$8)</f>
-        <v>1456.56</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="11" t="s">
-        <v>230</v>
-      </c>
-      <c r="B17" s="12" t="n">
-        <v>55</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="19" t="n">
-        <f aca="false">B17*(1+Allgemein!$B$8)</f>
-        <v>65.45</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="B18" s="18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="D18" s="19" t="n">
-        <f aca="false">B18*Allgemein!$B$6</f>
-        <v>95.2</v>
-      </c>
-      <c r="E18" s="19" t="n">
-        <f aca="false">D18*(1+Allgemein!$B$8)</f>
-        <v>113.288</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="B19" s="12" t="n">
-        <v>330</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19" s="19" t="n">
-        <f aca="false">B19*(1+Allgemein!$B$8)</f>
-        <v>392.7</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="B20" s="18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="D20" s="19" t="n">
-        <f aca="false">B20*Allgemein!$B$6</f>
-        <v>170</v>
-      </c>
-      <c r="E20" s="19" t="n">
-        <f aca="false">D20*(1+Allgemein!$B$8)</f>
-        <v>202.3</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="B21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" s="19" t="n">
-        <f aca="false">B21*(1+Allgemein!$B$8)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="11" t="s">
-        <v>235</v>
-      </c>
-      <c r="B22" s="18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="D22" s="19" t="n">
-        <f aca="false">B22*Allgemein!$B$6</f>
-        <v>187</v>
-      </c>
-      <c r="E22" s="19" t="n">
-        <f aca="false">D22*(1+Allgemein!$B$8)</f>
-        <v>222.53</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="15" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="B26" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="C26" s="11"/>
+      <c r="D26" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="B27" s="20" t="s">
-        <v>181</v>
-      </c>
-      <c r="C27" s="11"/>
+        <v>250</v>
+      </c>
+      <c r="B27" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>182</v>
+        <v>251</v>
       </c>
       <c r="B28" s="12" t="n">
-        <v>890</v>
+        <v>25</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E28" s="19" t="n">
-        <f aca="false">B28*(1+Allgemein!$B$8)</f>
-        <v>1059.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="B29" s="18" t="n">
-        <v>7</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="D29" s="19" t="n">
-        <f aca="false">B29*Allgemein!$B$6</f>
-        <v>476</v>
-      </c>
-      <c r="E29" s="19" t="n">
-        <f aca="false">D29*(1+Allgemein!$B$8)</f>
-        <v>566.44</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="B29" s="21" t="s">
+        <v>253</v>
+      </c>
+      <c r="C29" s="11"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="A7:A9 A15:A22" type="list">
+      <formula1>"Ja,Nein"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -5341,6 +5641,491 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:F35"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="15" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="19" t="n">
+        <f aca="false">B6*(1+Allgemein!$B$8)</f>
+        <v>49.98</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="B7" s="18" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <f aca="false">B7*Allgemein!$B$6</f>
+        <v>51</v>
+      </c>
+      <c r="E7" s="19" t="n">
+        <f aca="false">D7*(1+Allgemein!$B$8)</f>
+        <v>60.69</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B8" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="19" t="n">
+        <f aca="false">B8*(1+Allgemein!$B$8)</f>
+        <v>61.88</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="B9" s="18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <f aca="false">B9*Allgemein!$B$6</f>
+        <v>81.6</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <f aca="false">D9*(1+Allgemein!$B$8)</f>
+        <v>97.104</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="19" t="n">
+        <f aca="false">B10*(1+Allgemein!$B$8)</f>
+        <v>35.7</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="B11" s="18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <f aca="false">B11*Allgemein!$B$6</f>
+        <v>40.8</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <f aca="false">D11*(1+Allgemein!$B$8)</f>
+        <v>48.552</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="15" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="B15" s="12" t="n">
+        <v>1650</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <f aca="false">B15*(1+Allgemein!$B$8)</f>
+        <v>1963.5</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="B16" s="18" t="n">
+        <v>18</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D16" s="19" t="n">
+        <f aca="false">B16*Allgemein!$B$6</f>
+        <v>1224</v>
+      </c>
+      <c r="E16" s="19" t="n">
+        <f aca="false">D16*(1+Allgemein!$B$8)</f>
+        <v>1456.56</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="19" t="n">
+        <f aca="false">B17*(1+Allgemein!$B$8)</f>
+        <v>65.45</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="B18" s="18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D18" s="19" t="n">
+        <f aca="false">B18*Allgemein!$B$6</f>
+        <v>95.2</v>
+      </c>
+      <c r="E18" s="19" t="n">
+        <f aca="false">D18*(1+Allgemein!$B$8)</f>
+        <v>113.288</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="B19" s="12" t="n">
+        <v>330</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="19" t="n">
+        <f aca="false">B19*(1+Allgemein!$B$8)</f>
+        <v>392.7</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="B20" s="18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D20" s="19" t="n">
+        <f aca="false">B20*Allgemein!$B$6</f>
+        <v>170</v>
+      </c>
+      <c r="E20" s="19" t="n">
+        <f aca="false">D20*(1+Allgemein!$B$8)</f>
+        <v>202.3</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="B21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="19" t="n">
+        <f aca="false">B21*(1+Allgemein!$B$8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="B22" s="18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D22" s="19" t="n">
+        <f aca="false">B22*Allgemein!$B$6</f>
+        <v>187</v>
+      </c>
+      <c r="E22" s="19" t="n">
+        <f aca="false">D22*(1+Allgemein!$B$8)</f>
+        <v>222.53</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="15" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="9" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>272</v>
+      </c>
+      <c r="D27" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>890</v>
+      </c>
+      <c r="F27" s="19" t="n">
+        <f aca="false">E27*(1+Allgemein!$B$8)</f>
+        <v>1059.1</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>273</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>274</v>
+      </c>
+      <c r="D28" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>720</v>
+      </c>
+      <c r="F28" s="19" t="n">
+        <f aca="false">E28*(1+Allgemein!$B$8)</f>
+        <v>856.8</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>275</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>276</v>
+      </c>
+      <c r="D29" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>990</v>
+      </c>
+      <c r="F29" s="19" t="n">
+        <f aca="false">E29*(1+Allgemein!$B$8)</f>
+        <v>1178.1</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>277</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>278</v>
+      </c>
+      <c r="D30" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>650</v>
+      </c>
+      <c r="F30" s="19" t="n">
+        <f aca="false">E30*(1+Allgemein!$B$8)</f>
+        <v>773.5</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="15" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="B35" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D35" s="19" t="n">
+        <f aca="false">B35*Allgemein!$B$6</f>
+        <v>476</v>
+      </c>
+      <c r="E35" s="19" t="n">
+        <f aca="false">D35*(1+Allgemein!$B$8)</f>
+        <v>566.44</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="A27:A30" type="list">
+      <formula1>"Ja,Nein"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:D20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -5352,250 +6137,250 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="22" t="s">
-        <v>236</v>
+        <v>281</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="23" t="s">
-        <v>237</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="24" t="s">
-        <v>236</v>
+        <v>281</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>238</v>
+        <v>283</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>239</v>
+        <v>284</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>240</v>
+        <v>285</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>241</v>
+        <v>286</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>242</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>243</v>
+        <v>288</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>241</v>
+        <v>286</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>244</v>
+        <v>289</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>245</v>
+        <v>290</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>241</v>
+        <v>286</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>246</v>
+        <v>291</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="25" t="s">
-        <v>247</v>
+        <v>292</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>248</v>
+        <v>293</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>241</v>
+        <v>286</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>249</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>250</v>
+        <v>295</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>251</v>
+        <v>296</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>241</v>
+        <v>286</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>252</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>253</v>
+        <v>298</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>254</v>
+        <v>299</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>255</v>
+        <v>300</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>256</v>
+        <v>301</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>257</v>
+        <v>302</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>254</v>
+        <v>299</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>255</v>
+        <v>300</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>258</v>
+        <v>303</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="25" t="s">
-        <v>259</v>
+        <v>304</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>254</v>
+        <v>299</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>255</v>
+        <v>300</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>260</v>
+        <v>305</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="25" t="s">
-        <v>261</v>
+        <v>306</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>254</v>
+        <v>299</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>255</v>
+        <v>300</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>262</v>
+        <v>307</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="25" t="s">
-        <v>263</v>
+        <v>308</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>254</v>
+        <v>299</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>255</v>
+        <v>300</v>
       </c>
       <c r="D14" s="26" t="s">
-        <v>264</v>
+        <v>309</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="25" t="s">
-        <v>265</v>
+        <v>310</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>254</v>
+        <v>299</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>255</v>
+        <v>300</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>266</v>
+        <v>311</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="25" t="s">
-        <v>267</v>
+        <v>229</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>254</v>
+        <v>299</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>255</v>
+        <v>300</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>268</v>
+        <v>312</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="25" t="s">
-        <v>269</v>
+        <v>228</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>254</v>
+        <v>299</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>255</v>
+        <v>300</v>
       </c>
       <c r="D17" s="26" t="s">
-        <v>270</v>
+        <v>313</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="25" t="s">
-        <v>271</v>
+        <v>314</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>254</v>
+        <v>299</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>255</v>
+        <v>300</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>272</v>
+        <v>315</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="25" t="s">
-        <v>273</v>
+        <v>316</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>254</v>
+        <v>299</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>255</v>
+        <v>300</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>274</v>
+        <v>317</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="25" t="s">
-        <v>275</v>
+        <v>318</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>254</v>
+        <v>299</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>255</v>
+        <v>300</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>276</v>
+        <v>319</v>
       </c>
     </row>
   </sheetData>

--- a/Ulshoefer-Preisliste-Angebotsrechner.xlsx
+++ b/Ulshoefer-Preisliste-Angebotsrechner.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Anleitung" sheetId="1" state="visible" r:id="rId3"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1371" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="523">
   <si>
     <t xml:space="preserve">Preisliste für den Online-Angebotsrechner</t>
   </si>
@@ -216,6 +216,30 @@
     <t xml:space="preserve">Nettopreis (€)</t>
   </si>
   <si>
+    <t xml:space="preserve">Energieklasse Kühlen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energieklasse Heizen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEER (–)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCOP (–)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schalldruck Innengerät ab (dB(A))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kältemittel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Link Energielabel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Link Produktdatenblatt</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bruttopreis (€)</t>
   </si>
   <si>
@@ -228,6 +252,15 @@
     <t xml:space="preserve">Standard</t>
   </si>
   <si>
+    <t xml:space="preserve">A++</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R32</t>
+  </si>
+  <si>
     <t xml:space="preserve">Seiya RAS-B13E2KVG-E / RAS-13E2AVG-E</t>
   </si>
   <si>
@@ -258,6 +291,9 @@
     <t xml:space="preserve">Daisekai 10 RAS-B13S4KVPG-E</t>
   </si>
   <si>
+    <t xml:space="preserve">A+++</t>
+  </si>
+  <si>
     <t xml:space="preserve">Daikin</t>
   </si>
   <si>
@@ -285,6 +321,9 @@
     <t xml:space="preserve">MSZ-AY25VGK / MUZ-AY25VG</t>
   </si>
   <si>
+    <t xml:space="preserve">–</t>
+  </si>
+  <si>
     <t xml:space="preserve">MSZ-AY35VGK / MUZ-AY35VG</t>
   </si>
   <si>
@@ -300,6 +339,9 @@
     <t xml:space="preserve">Multi-Split-Innengeräte</t>
   </si>
   <si>
+    <t xml:space="preserve">Energieklasse und Energielabel gelten für die Kombination – sie werden beim Außengerät eingetragen.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Seiya RAS-B10E2KVG-E (Multi)</t>
   </si>
   <si>
@@ -441,6 +483,9 @@
     <t xml:space="preserve">Die Website wählt das kleinste Gerät, das die Heizlast deckt; der Kunde kann nach Hersteller filtern.</t>
   </si>
   <si>
+    <t xml:space="preserve">Energieklasse (55 °C)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dimplex</t>
   </si>
   <si>
@@ -717,6 +762,12 @@
     <t xml:space="preserve">Anschluss/Montage brutto (€)</t>
   </si>
   <si>
+    <t xml:space="preserve">Energieklasse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Label-Skala</t>
+  </si>
+  <si>
     <t xml:space="preserve">Waschmaschine</t>
   </si>
   <si>
@@ -726,6 +777,12 @@
     <t xml:space="preserve">Beispielprodukt – Ausstattung und Preis folgen</t>
   </si>
   <si>
+    <t xml:space="preserve">A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A–G (nuova)</t>
+  </si>
+  <si>
     <t xml:space="preserve">iQ500 Waschmaschine 9 kg</t>
   </si>
   <si>
@@ -735,12 +792,18 @@
     <t xml:space="preserve">iQ500 Wärmepumpentrockner 8 kg</t>
   </si>
   <si>
+    <t xml:space="preserve">A+++–D</t>
+  </si>
+  <si>
     <t xml:space="preserve">Geschirrspüler</t>
   </si>
   <si>
     <t xml:space="preserve">iQ300 Einbau-Geschirrspüler 60 cm</t>
   </si>
   <si>
+    <t xml:space="preserve">C</t>
+  </si>
+  <si>
     <t xml:space="preserve">Backofen &amp; Herd</t>
   </si>
   <si>
@@ -774,6 +837,18 @@
     <t xml:space="preserve">In der Regel 3–10 Werktage, Liefertermin nach Absprache.</t>
   </si>
   <si>
+    <t xml:space="preserve">Liefergebiet (Text für den Kunden)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lauda-Königshofen und Umgebung – andere Orte auf Anfrage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zahlungsarten (Text für den Kunden)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Überweisung nach Erhalt der Rechnung oder Barzahlung bzw. EC-Karte bei Abholung im Fachgeschäft.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Installation pro m²</t>
   </si>
   <si>
@@ -981,127 +1056,130 @@
     <t xml:space="preserve">klima.geraete_single</t>
   </si>
   <si>
-    <t xml:space="preserve">aktiv|bool,hersteller|text,modell|text,kw|num,klasse|sel|std=Standard;pre=Premium,preis|num</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38:55</t>
+    <t xml:space="preserve">aktiv|bool,hersteller|text,modell|text,kw|num,klasse|sel|std=Standard;pre=Premium,preis|num,ek_kuehl|sel|=–;A+++=A+++;A++=A++;A+=A+;A=A;B=B;C=C;D=D,ek_heiz|sel|=–;A+++=A+++;A++=A++;A+=A+;A=A;B=B;C=C;D=D,seer|num,scop|num,schall|num,kaeltemittel|text,label|text,datenblatt|text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39:56</t>
   </si>
   <si>
     <t xml:space="preserve">klima.innengeraete_multi</t>
   </si>
   <si>
-    <t xml:space="preserve">60:73</t>
+    <t xml:space="preserve">aktiv|bool,hersteller|text,modell|text,kw|num,klasse|sel|std=Standard;pre=Premium,preis|num,schall|num,kaeltemittel|text,datenblatt|text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61:74</t>
   </si>
   <si>
     <t xml:space="preserve">klima.aussengeraete_multi</t>
   </si>
   <si>
-    <t xml:space="preserve">aktiv|bool,hersteller|text,modell|text,anschluesse|num,kw|num,preis|num</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B78</t>
+    <t xml:space="preserve">aktiv|bool,hersteller|text,modell|text,anschluesse|num,kw|num,preis|num,ek_kuehl|sel|=–;A+++=A+++;A++=A++;A+=A+;A=A;B=B;C=C;D=D,ek_heiz|sel|=–;A+++=A+++;A++=A++;A+=A+;A=A;B=B;C=C;D=D,seer|num,scop|num,kaeltemittel|text,label|text,datenblatt|text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B79</t>
   </si>
   <si>
     <t xml:space="preserve">klima.arbeit.single_h</t>
   </si>
   <si>
-    <t xml:space="preserve">B79</t>
+    <t xml:space="preserve">B80</t>
   </si>
   <si>
     <t xml:space="preserve">klima.arbeit.multi_basis_h</t>
   </si>
   <si>
-    <t xml:space="preserve">B80</t>
+    <t xml:space="preserve">B81</t>
   </si>
   <si>
     <t xml:space="preserve">klima.arbeit.multi_je_innen_h</t>
   </si>
   <si>
-    <t xml:space="preserve">B81</t>
+    <t xml:space="preserve">B82</t>
   </si>
   <si>
     <t xml:space="preserve">klima.arbeit.leitung_m_h</t>
   </si>
   <si>
-    <t xml:space="preserve">B82</t>
+    <t xml:space="preserve">B83</t>
   </si>
   <si>
     <t xml:space="preserve">klima.arbeit.kernbohrung_h</t>
   </si>
   <si>
-    <t xml:space="preserve">B83</t>
+    <t xml:space="preserve">B84</t>
   </si>
   <si>
     <t xml:space="preserve">klima.arbeit.pumpe_h</t>
   </si>
   <si>
-    <t xml:space="preserve">B84</t>
+    <t xml:space="preserve">B85</t>
   </si>
   <si>
     <t xml:space="preserve">klima.arbeit.stromkreis_h</t>
   </si>
   <si>
-    <t xml:space="preserve">B85</t>
+    <t xml:space="preserve">B86</t>
   </si>
   <si>
     <t xml:space="preserve">klima.arbeit.konsole_h</t>
   </si>
   <si>
-    <t xml:space="preserve">B89</t>
+    <t xml:space="preserve">B90</t>
   </si>
   <si>
     <t xml:space="preserve">klima.material.grund_single</t>
   </si>
   <si>
-    <t xml:space="preserve">B90</t>
+    <t xml:space="preserve">B91</t>
   </si>
   <si>
     <t xml:space="preserve">klima.material.grund_je_innen</t>
   </si>
   <si>
-    <t xml:space="preserve">B91</t>
+    <t xml:space="preserve">B92</t>
   </si>
   <si>
     <t xml:space="preserve">klima.material.leitung_m</t>
   </si>
   <si>
-    <t xml:space="preserve">B92</t>
+    <t xml:space="preserve">B93</t>
   </si>
   <si>
     <t xml:space="preserve">klima.material.bodenkonsole</t>
   </si>
   <si>
-    <t xml:space="preserve">B93</t>
+    <t xml:space="preserve">B94</t>
   </si>
   <si>
     <t xml:space="preserve">klima.material.dachgestell</t>
   </si>
   <si>
-    <t xml:space="preserve">B94</t>
+    <t xml:space="preserve">B95</t>
   </si>
   <si>
     <t xml:space="preserve">klima.material.kernbohrung</t>
   </si>
   <si>
-    <t xml:space="preserve">B95</t>
+    <t xml:space="preserve">B96</t>
   </si>
   <si>
     <t xml:space="preserve">klima.material.pumpe</t>
   </si>
   <si>
-    <t xml:space="preserve">B96</t>
+    <t xml:space="preserve">B97</t>
   </si>
   <si>
     <t xml:space="preserve">klima.material.stromkreis</t>
   </si>
   <si>
-    <t xml:space="preserve">B100</t>
+    <t xml:space="preserve">B101</t>
   </si>
   <si>
     <t xml:space="preserve">klima.wartung_jahr</t>
   </si>
   <si>
-    <t xml:space="preserve">B101</t>
+    <t xml:space="preserve">B102</t>
   </si>
   <si>
     <t xml:space="preserve">klima.kw_je_m2</t>
@@ -1113,93 +1191,96 @@
     <t xml:space="preserve">wp.geraete</t>
   </si>
   <si>
+    <t xml:space="preserve">aktiv|bool,hersteller|text,modell|text,kw|num,preis|num,ek|sel|=–;A+++=A+++;A++=A++;A+=A+;A=A;B=B;C=C;D=D,label|text,datenblatt|text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wp.arbeit.montage_h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wp.arbeit.demontage_oel_h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wp.arbeit.demontage_gas_h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wp.arbeit.demontage_ns_h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wp.arbeit.heizkoerper_h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wp.arbeit.zaehler_h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wp.material.hydraulik_paket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wp.material.entsorgung_oel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wp.material.entsorgung_gas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wp.material.entsorgung_ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wp.material.heizkoerper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wp.material.zaehler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wp.ww_kw_je_person</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pv.module</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aktiv|bool,hersteller|text,modell|text,wp|num,preis|num</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pv.wechselrichter</t>
+  </si>
+  <si>
     <t xml:space="preserve">aktiv|bool,hersteller|text,modell|text,kw|num,preis|num</t>
   </si>
   <si>
-    <t xml:space="preserve">B23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp.arbeit.montage_h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp.arbeit.demontage_oel_h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp.arbeit.demontage_gas_h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp.arbeit.demontage_ns_h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp.arbeit.heizkoerper_h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp.arbeit.zaehler_h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp.material.hydraulik_paket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp.material.entsorgung_oel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp.material.entsorgung_gas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp.material.entsorgung_ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp.material.heizkoerper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp.material.zaehler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wp.ww_kw_je_person</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pv.module</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aktiv|bool,hersteller|text,modell|text,wp|num,preis|num</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pv.wechselrichter</t>
-  </si>
-  <si>
     <t xml:space="preserve">36:43</t>
   </si>
   <si>
@@ -1449,7 +1530,7 @@
     <t xml:space="preserve">shop.produkte</t>
   </si>
   <si>
-    <t xml:space="preserve">aktiv|bool,partner|psel,kategorie|text,modell|text,info|text,preis|num,montage|num</t>
+    <t xml:space="preserve">aktiv|bool,partner|psel,kategorie|text,modell|text,info|text,preis|num,montage|num,ek|sel|=–;A+++=A+++;A++=A++;A+=A+;A=A;B=B;C=C;D=D;E=E;F=F;G=G,skala|sel|neu=A–G (nuova);alt=A+++–D,label|text,datenblatt|text</t>
   </si>
   <si>
     <t xml:space="preserve">shop.lieferung</t>
@@ -1459,6 +1540,12 @@
   </si>
   <si>
     <t xml:space="preserve">shop.lieferzeit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop.liefergebiet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop.zahlung</t>
   </si>
   <si>
     <t xml:space="preserve">elektro.neu.material_m2</t>
@@ -2310,7 +2397,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:O102"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -2348,7 +2435,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
         <v>56</v>
       </c>
@@ -2369,6 +2456,30 @@
       </c>
       <c r="G8" s="7" t="s">
         <v>62</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="O8" s="7" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2376,21 +2487,41 @@
         <v>24</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D9" s="12" t="n">
         <v>2.5</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>990</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="G9" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I9" s="12" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J9" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="6" t="n">
         <f aca="false">IF(F9="","",F9*(1+Allgemein!$B$19))</f>
         <v>1178.1</v>
       </c>
@@ -2400,21 +2531,41 @@
         <v>24</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="D10" s="12" t="n">
         <v>3.3</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>1120</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="G10" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I10" s="12" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J10" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="6" t="n">
         <f aca="false">IF(F10="","",F10*(1+Allgemein!$B$19))</f>
         <v>1332.8</v>
       </c>
@@ -2424,21 +2575,41 @@
         <v>24</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="D11" s="12" t="n">
         <v>4.2</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F11" s="9" t="n">
         <v>1390</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="G11" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I11" s="12" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J11" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="6" t="n">
         <f aca="false">IF(F11="","",F11*(1+Allgemein!$B$19))</f>
         <v>1654.1</v>
       </c>
@@ -2448,21 +2619,41 @@
         <v>24</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="D12" s="12" t="n">
         <v>5</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>1590</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="G12" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J12" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="6" t="n">
         <f aca="false">IF(F12="","",F12*(1+Allgemein!$B$19))</f>
         <v>1892.1</v>
       </c>
@@ -2472,21 +2663,41 @@
         <v>24</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="D13" s="12" t="n">
         <v>6.5</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>2090</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="G13" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I13" s="12" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J13" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="6" t="n">
         <f aca="false">IF(F13="","",F13*(1+Allgemein!$B$19))</f>
         <v>2487.1</v>
       </c>
@@ -2496,21 +2707,41 @@
         <v>24</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D14" s="12" t="n">
         <v>2.5</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>1390</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="G14" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I14" s="12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J14" s="12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K14" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="6" t="n">
         <f aca="false">IF(F14="","",F14*(1+Allgemein!$B$19))</f>
         <v>1654.1</v>
       </c>
@@ -2520,21 +2751,41 @@
         <v>24</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="D15" s="12" t="n">
         <v>3.5</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>1550</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="G15" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I15" s="12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J15" s="12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K15" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="6" t="n">
         <f aca="false">IF(F15="","",F15*(1+Allgemein!$B$19))</f>
         <v>1844.5</v>
       </c>
@@ -2544,21 +2795,41 @@
         <v>24</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="D16" s="12" t="n">
         <v>4.6</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>1790</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="G16" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J16" s="12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K16" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="6" t="n">
         <f aca="false">IF(F16="","",F16*(1+Allgemein!$B$19))</f>
         <v>2130.1</v>
       </c>
@@ -2568,21 +2839,41 @@
         <v>24</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="D17" s="12" t="n">
         <v>5</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>1990</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="G17" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I17" s="12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J17" s="12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K17" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="6" t="n">
         <f aca="false">IF(F17="","",F17*(1+Allgemein!$B$19))</f>
         <v>2368.1</v>
       </c>
@@ -2592,21 +2883,41 @@
         <v>24</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="D18" s="12" t="n">
         <v>3.5</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>2390</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="G18" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="I18" s="12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J18" s="12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K18" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="6" t="n">
         <f aca="false">IF(F18="","",F18*(1+Allgemein!$B$19))</f>
         <v>2844.1</v>
       </c>
@@ -2616,21 +2927,41 @@
         <v>24</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="D19" s="12" t="n">
         <v>2.5</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>1090</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="G19" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I19" s="12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J19" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K19" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="6" t="n">
         <f aca="false">IF(F19="","",F19*(1+Allgemein!$B$19))</f>
         <v>1297.1</v>
       </c>
@@ -2640,21 +2971,41 @@
         <v>24</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="D20" s="12" t="n">
         <v>3.5</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>1240</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="G20" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I20" s="12" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J20" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K20" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="6" t="n">
         <f aca="false">IF(F20="","",F20*(1+Allgemein!$B$19))</f>
         <v>1475.6</v>
       </c>
@@ -2664,21 +3015,41 @@
         <v>24</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D21" s="12" t="n">
         <v>5</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>1690</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="G21" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I21" s="12" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="J21" s="12" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="K21" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="6" t="n">
         <f aca="false">IF(F21="","",F21*(1+Allgemein!$B$19))</f>
         <v>2011.1</v>
       </c>
@@ -2688,21 +3059,41 @@
         <v>24</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="D22" s="12" t="n">
         <v>2.5</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>1490</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="G22" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="I22" s="12" t="n">
+        <v>8.7</v>
+      </c>
+      <c r="J22" s="12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K22" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="6" t="n">
         <f aca="false">IF(F22="","",F22*(1+Allgemein!$B$19))</f>
         <v>1773.1</v>
       </c>
@@ -2712,21 +3103,41 @@
         <v>24</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="D23" s="12" t="n">
         <v>3.5</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>1690</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="G23" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I23" s="12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J23" s="12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K23" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="6" t="n">
         <f aca="false">IF(F23="","",F23*(1+Allgemein!$B$19))</f>
         <v>2011.1</v>
       </c>
@@ -2736,21 +3147,41 @@
         <v>24</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="D24" s="12" t="n">
         <v>5</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>2190</v>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="G24" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I24" s="12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J24" s="12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K24" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="6" t="n">
         <f aca="false">IF(F24="","",F24*(1+Allgemein!$B$19))</f>
         <v>2606.1</v>
       </c>
@@ -2760,21 +3191,35 @@
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="D25" s="12" t="n">
         <v>2.5</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>1150</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="G25" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="I25" s="12"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="12"/>
+      <c r="L25" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="6" t="n">
         <f aca="false">IF(F25="","",F25*(1+Allgemein!$B$19))</f>
         <v>1368.5</v>
       </c>
@@ -2784,21 +3229,35 @@
         <v>24</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="D26" s="12" t="n">
         <v>3.5</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>1290</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="G26" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
+      <c r="L26" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="6" t="n">
         <f aca="false">IF(F26="","",F26*(1+Allgemein!$B$19))</f>
         <v>1535.1</v>
       </c>
@@ -2808,21 +3267,35 @@
         <v>24</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="D27" s="12" t="n">
         <v>5</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>1750</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="G27" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="I27" s="12"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12"/>
+      <c r="L27" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="6" t="n">
         <f aca="false">IF(F27="","",F27*(1+Allgemein!$B$19))</f>
         <v>2082.5</v>
       </c>
@@ -2832,21 +3305,35 @@
         <v>24</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="D28" s="12" t="n">
         <v>7.1</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>2390</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="G28" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="I28" s="12"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="12"/>
+      <c r="L28" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="6" t="n">
         <f aca="false">IF(F28="","",F28*(1+Allgemein!$B$19))</f>
         <v>2844.1</v>
       </c>
@@ -2858,7 +3345,15 @@
       <c r="D29" s="12"/>
       <c r="E29" s="5"/>
       <c r="F29" s="9"/>
-      <c r="G29" s="6" t="str">
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="6" t="str">
         <f aca="false">IF(F29="","",F29*(1+Allgemein!$B$19))</f>
         <v/>
       </c>
@@ -2870,7 +3365,15 @@
       <c r="D30" s="12"/>
       <c r="E30" s="5"/>
       <c r="F30" s="9"/>
-      <c r="G30" s="6" t="str">
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="12"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="6" t="str">
         <f aca="false">IF(F30="","",F30*(1+Allgemein!$B$19))</f>
         <v/>
       </c>
@@ -2882,7 +3385,15 @@
       <c r="D31" s="12"/>
       <c r="E31" s="5"/>
       <c r="F31" s="9"/>
-      <c r="G31" s="6" t="str">
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="12"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="6" t="str">
         <f aca="false">IF(F31="","",F31*(1+Allgemein!$B$19))</f>
         <v/>
       </c>
@@ -2894,7 +3405,15 @@
       <c r="D32" s="12"/>
       <c r="E32" s="5"/>
       <c r="F32" s="9"/>
-      <c r="G32" s="6" t="str">
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="6" t="str">
         <f aca="false">IF(F32="","",F32*(1+Allgemein!$B$19))</f>
         <v/>
       </c>
@@ -2906,66 +3425,64 @@
       <c r="D33" s="12"/>
       <c r="E33" s="5"/>
       <c r="F33" s="9"/>
-      <c r="G33" s="6" t="str">
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="12"/>
+      <c r="K33" s="12"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="6" t="str">
         <f aca="false">IF(F33="","",F33*(1+Allgemein!$B$19))</f>
         <v/>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="7" t="s">
+      <c r="A37" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B38" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C38" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D37" s="7" t="s">
+      <c r="D38" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E37" s="7" t="s">
+      <c r="E38" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="F37" s="7" t="s">
+      <c r="F38" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="G37" s="7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D38" s="12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F38" s="9" t="n">
-        <v>420</v>
-      </c>
-      <c r="G38" s="6" t="n">
-        <f aca="false">IF(F38="","",F38*(1+Allgemein!$B$19))</f>
-        <v>499.8</v>
+      <c r="G38" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="I38" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="J38" s="7" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2973,23 +3490,30 @@
         <v>24</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="D39" s="12" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>470</v>
-      </c>
-      <c r="G39" s="6" t="n">
+        <v>420</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="I39" s="5"/>
+      <c r="J39" s="6" t="n">
         <f aca="false">IF(F39="","",F39*(1+Allgemein!$B$19))</f>
-        <v>559.3</v>
+        <v>499.8</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2997,23 +3521,30 @@
         <v>24</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>560</v>
-      </c>
-      <c r="G40" s="6" t="n">
+        <v>470</v>
+      </c>
+      <c r="G40" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="I40" s="5"/>
+      <c r="J40" s="6" t="n">
         <f aca="false">IF(F40="","",F40*(1+Allgemein!$B$19))</f>
-        <v>666.4</v>
+        <v>559.3</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3021,23 +3552,30 @@
         <v>24</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="D41" s="12" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>590</v>
-      </c>
-      <c r="G41" s="6" t="n">
+        <v>560</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="I41" s="5"/>
+      <c r="J41" s="6" t="n">
         <f aca="false">IF(F41="","",F41*(1+Allgemein!$B$19))</f>
-        <v>702.1</v>
+        <v>666.4</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3045,23 +3583,30 @@
         <v>24</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>660</v>
-      </c>
-      <c r="G42" s="6" t="n">
+        <v>590</v>
+      </c>
+      <c r="G42" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="I42" s="5"/>
+      <c r="J42" s="6" t="n">
         <f aca="false">IF(F42="","",F42*(1+Allgemein!$B$19))</f>
-        <v>785.4</v>
+        <v>702.1</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3069,23 +3614,30 @@
         <v>24</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D43" s="12" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>760</v>
-      </c>
-      <c r="G43" s="6" t="n">
+        <v>660</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="I43" s="5"/>
+      <c r="J43" s="6" t="n">
         <f aca="false">IF(F43="","",F43*(1+Allgemein!$B$19))</f>
-        <v>904.4</v>
+        <v>785.4</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3093,23 +3645,30 @@
         <v>24</v>
       </c>
       <c r="B44" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D44" s="12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F44" s="9" t="n">
+        <v>760</v>
+      </c>
+      <c r="G44" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="H44" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C44" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="D44" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F44" s="9" t="n">
-        <v>560</v>
-      </c>
-      <c r="G44" s="6" t="n">
+      <c r="I44" s="5"/>
+      <c r="J44" s="6" t="n">
         <f aca="false">IF(F44="","",F44*(1+Allgemein!$B$19))</f>
-        <v>666.4</v>
+        <v>904.4</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3117,23 +3676,30 @@
         <v>24</v>
       </c>
       <c r="B45" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D45" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>560</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="H45" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C45" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D45" s="12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F45" s="9" t="n">
-        <v>600</v>
-      </c>
-      <c r="G45" s="6" t="n">
+      <c r="I45" s="5"/>
+      <c r="J45" s="6" t="n">
         <f aca="false">IF(F45="","",F45*(1+Allgemein!$B$19))</f>
-        <v>714</v>
+        <v>666.4</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3141,23 +3707,30 @@
         <v>24</v>
       </c>
       <c r="B46" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D46" s="12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F46" s="9" t="n">
+        <v>600</v>
+      </c>
+      <c r="G46" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="H46" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C46" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D46" s="12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F46" s="9" t="n">
-        <v>680</v>
-      </c>
-      <c r="G46" s="6" t="n">
+      <c r="I46" s="5"/>
+      <c r="J46" s="6" t="n">
         <f aca="false">IF(F46="","",F46*(1+Allgemein!$B$19))</f>
-        <v>809.2</v>
+        <v>714</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3165,23 +3738,30 @@
         <v>24</v>
       </c>
       <c r="B47" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D47" s="12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F47" s="9" t="n">
+        <v>680</v>
+      </c>
+      <c r="G47" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="H47" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C47" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="D47" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F47" s="9" t="n">
-        <v>860</v>
-      </c>
-      <c r="G47" s="6" t="n">
+      <c r="I47" s="5"/>
+      <c r="J47" s="6" t="n">
         <f aca="false">IF(F47="","",F47*(1+Allgemein!$B$19))</f>
-        <v>1023.4</v>
+        <v>809.2</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3189,23 +3769,30 @@
         <v>24</v>
       </c>
       <c r="B48" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D48" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F48" s="9" t="n">
+        <v>860</v>
+      </c>
+      <c r="G48" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="H48" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C48" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D48" s="12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F48" s="9" t="n">
-        <v>430</v>
-      </c>
-      <c r="G48" s="6" t="n">
+      <c r="I48" s="5"/>
+      <c r="J48" s="6" t="n">
         <f aca="false">IF(F48="","",F48*(1+Allgemein!$B$19))</f>
-        <v>511.7</v>
+        <v>1023.4</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3213,23 +3800,30 @@
         <v>24</v>
       </c>
       <c r="B49" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D49" s="12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F49" s="9" t="n">
+        <v>430</v>
+      </c>
+      <c r="G49" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="H49" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C49" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="D49" s="12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F49" s="9" t="n">
-        <v>490</v>
-      </c>
-      <c r="G49" s="6" t="n">
+      <c r="I49" s="5"/>
+      <c r="J49" s="6" t="n">
         <f aca="false">IF(F49="","",F49*(1+Allgemein!$B$19))</f>
-        <v>583.1</v>
+        <v>511.7</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3237,35 +3831,61 @@
         <v>24</v>
       </c>
       <c r="B50" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D50" s="12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F50" s="9" t="n">
+        <v>490</v>
+      </c>
+      <c r="G50" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="H50" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C50" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="D50" s="12" t="n">
+      <c r="I50" s="5"/>
+      <c r="J50" s="6" t="n">
+        <f aca="false">IF(F50="","",F50*(1+Allgemein!$B$19))</f>
+        <v>583.1</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D51" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="E50" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F50" s="9" t="n">
+      <c r="E51" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F51" s="9" t="n">
         <v>640</v>
       </c>
-      <c r="G50" s="6" t="n">
-        <f aca="false">IF(F50="","",F50*(1+Allgemein!$B$19))</f>
+      <c r="G51" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="H51" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="I51" s="5"/>
+      <c r="J51" s="6" t="n">
+        <f aca="false">IF(F51="","",F51*(1+Allgemein!$B$19))</f>
         <v>761.6</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="5"/>
-      <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="12"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="6" t="str">
-        <f aca="false">IF(F51="","",F51*(1+Allgemein!$B$19))</f>
-        <v/>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3275,7 +3895,10 @@
       <c r="D52" s="12"/>
       <c r="E52" s="5"/>
       <c r="F52" s="9"/>
-      <c r="G52" s="6" t="str">
+      <c r="G52" s="12"/>
+      <c r="H52" s="5"/>
+      <c r="I52" s="5"/>
+      <c r="J52" s="6" t="str">
         <f aca="false">IF(F52="","",F52*(1+Allgemein!$B$19))</f>
         <v/>
       </c>
@@ -3287,7 +3910,10 @@
       <c r="D53" s="12"/>
       <c r="E53" s="5"/>
       <c r="F53" s="9"/>
-      <c r="G53" s="6" t="str">
+      <c r="G53" s="12"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5"/>
+      <c r="J53" s="6" t="str">
         <f aca="false">IF(F53="","",F53*(1+Allgemein!$B$19))</f>
         <v/>
       </c>
@@ -3299,7 +3925,10 @@
       <c r="D54" s="12"/>
       <c r="E54" s="5"/>
       <c r="F54" s="9"/>
-      <c r="G54" s="6" t="str">
+      <c r="G54" s="12"/>
+      <c r="H54" s="5"/>
+      <c r="I54" s="5"/>
+      <c r="J54" s="6" t="str">
         <f aca="false">IF(F54="","",F54*(1+Allgemein!$B$19))</f>
         <v/>
       </c>
@@ -3311,66 +3940,81 @@
       <c r="D55" s="12"/>
       <c r="E55" s="5"/>
       <c r="F55" s="9"/>
-      <c r="G55" s="6" t="str">
+      <c r="G55" s="12"/>
+      <c r="H55" s="5"/>
+      <c r="I55" s="5"/>
+      <c r="J55" s="6" t="str">
         <f aca="false">IF(F55="","",F55*(1+Allgemein!$B$19))</f>
         <v/>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="3" t="s">
-        <v>103</v>
+      <c r="A56" s="5"/>
+      <c r="B56" s="5"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="12"/>
+      <c r="E56" s="5"/>
+      <c r="F56" s="9"/>
+      <c r="G56" s="12"/>
+      <c r="H56" s="5"/>
+      <c r="I56" s="5"/>
+      <c r="J56" s="6" t="str">
+        <f aca="false">IF(F56="","",F56*(1+Allgemein!$B$19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="7" t="s">
+      <c r="A59" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B59" s="7" t="s">
+      <c r="B60" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C60" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D59" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="E59" s="7" t="s">
+      <c r="D60" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="E60" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F59" s="7" t="s">
+      <c r="F60" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="G59" s="7" t="s">
+      <c r="G60" s="7" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B60" s="5" t="s">
+      <c r="H60" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C60" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="D60" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E60" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="F60" s="9" t="n">
-        <v>1590</v>
-      </c>
-      <c r="G60" s="6" t="n">
-        <f aca="false">IF(F60="","",F60*(1+Allgemein!$B$19))</f>
-        <v>1892.1</v>
+      <c r="I60" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="J60" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="K60" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="L60" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="M60" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="N60" s="7" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3378,23 +4022,36 @@
         <v>24</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="D61" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E61" s="12" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>1990</v>
-      </c>
-      <c r="G61" s="6" t="n">
+        <v>1590</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H61" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I61" s="12"/>
+      <c r="J61" s="12"/>
+      <c r="K61" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="L61" s="5"/>
+      <c r="M61" s="5"/>
+      <c r="N61" s="6" t="n">
         <f aca="false">IF(F61="","",F61*(1+Allgemein!$B$19))</f>
-        <v>2368.1</v>
+        <v>1892.1</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3402,23 +4059,36 @@
         <v>24</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="D62" s="12" t="n">
         <v>3</v>
       </c>
       <c r="E62" s="12" t="n">
-        <v>7.5</v>
+        <v>5.2</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>2390</v>
-      </c>
-      <c r="G62" s="6" t="n">
+        <v>1990</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H62" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I62" s="12"/>
+      <c r="J62" s="12"/>
+      <c r="K62" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="L62" s="5"/>
+      <c r="M62" s="5"/>
+      <c r="N62" s="6" t="n">
         <f aca="false">IF(F62="","",F62*(1+Allgemein!$B$19))</f>
-        <v>2844.1</v>
+        <v>2368.1</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3426,23 +4096,36 @@
         <v>24</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="D63" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E63" s="12" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>2690</v>
-      </c>
-      <c r="G63" s="6" t="n">
+        <v>2390</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H63" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I63" s="12"/>
+      <c r="J63" s="12"/>
+      <c r="K63" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="L63" s="5"/>
+      <c r="M63" s="5"/>
+      <c r="N63" s="6" t="n">
         <f aca="false">IF(F63="","",F63*(1+Allgemein!$B$19))</f>
-        <v>3201.1</v>
+        <v>2844.1</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3450,23 +4133,36 @@
         <v>24</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E64" s="12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>3190</v>
-      </c>
-      <c r="G64" s="6" t="n">
+        <v>2690</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H64" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I64" s="12"/>
+      <c r="J64" s="12"/>
+      <c r="K64" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="L64" s="5"/>
+      <c r="M64" s="5"/>
+      <c r="N64" s="6" t="n">
         <f aca="false">IF(F64="","",F64*(1+Allgemein!$B$19))</f>
-        <v>3796.1</v>
+        <v>3201.1</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3474,23 +4170,36 @@
         <v>24</v>
       </c>
       <c r="B65" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D65" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E65" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F65" s="9" t="n">
+        <v>3190</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H65" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I65" s="12"/>
+      <c r="J65" s="12"/>
+      <c r="K65" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C65" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D65" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E65" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="F65" s="9" t="n">
-        <v>1790</v>
-      </c>
-      <c r="G65" s="6" t="n">
+      <c r="L65" s="5"/>
+      <c r="M65" s="5"/>
+      <c r="N65" s="6" t="n">
         <f aca="false">IF(F65="","",F65*(1+Allgemein!$B$19))</f>
-        <v>2130.1</v>
+        <v>3796.1</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3498,23 +4207,36 @@
         <v>24</v>
       </c>
       <c r="B66" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D66" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E66" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F66" s="9" t="n">
+        <v>1790</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H66" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I66" s="12"/>
+      <c r="J66" s="12"/>
+      <c r="K66" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C66" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D66" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="E66" s="12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="F66" s="9" t="n">
-        <v>2190</v>
-      </c>
-      <c r="G66" s="6" t="n">
+      <c r="L66" s="5"/>
+      <c r="M66" s="5"/>
+      <c r="N66" s="6" t="n">
         <f aca="false">IF(F66="","",F66*(1+Allgemein!$B$19))</f>
-        <v>2606.1</v>
+        <v>2130.1</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3522,23 +4244,36 @@
         <v>24</v>
       </c>
       <c r="B67" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D67" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E67" s="12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F67" s="9" t="n">
+        <v>2190</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H67" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I67" s="12"/>
+      <c r="J67" s="12"/>
+      <c r="K67" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C67" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="D67" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E67" s="12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="F67" s="9" t="n">
-        <v>2690</v>
-      </c>
-      <c r="G67" s="6" t="n">
+      <c r="L67" s="5"/>
+      <c r="M67" s="5"/>
+      <c r="N67" s="6" t="n">
         <f aca="false">IF(F67="","",F67*(1+Allgemein!$B$19))</f>
-        <v>3201.1</v>
+        <v>2606.1</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3546,35 +4281,73 @@
         <v>24</v>
       </c>
       <c r="B68" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D68" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E68" s="12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="F68" s="9" t="n">
+        <v>2690</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H68" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I68" s="12"/>
+      <c r="J68" s="12"/>
+      <c r="K68" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C68" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="D68" s="12" t="n">
+      <c r="L68" s="5"/>
+      <c r="M68" s="5"/>
+      <c r="N68" s="6" t="n">
+        <f aca="false">IF(F68="","",F68*(1+Allgemein!$B$19))</f>
+        <v>3201.1</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D69" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="E68" s="12" t="n">
+      <c r="E69" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="F68" s="9" t="n">
+      <c r="F69" s="9" t="n">
         <v>3290</v>
       </c>
-      <c r="G68" s="6" t="n">
-        <f aca="false">IF(F68="","",F68*(1+Allgemein!$B$19))</f>
+      <c r="G69" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H69" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I69" s="12"/>
+      <c r="J69" s="12"/>
+      <c r="K69" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="L69" s="5"/>
+      <c r="M69" s="5"/>
+      <c r="N69" s="6" t="n">
+        <f aca="false">IF(F69="","",F69*(1+Allgemein!$B$19))</f>
         <v>3915.1</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="5"/>
-      <c r="B69" s="5"/>
-      <c r="C69" s="5"/>
-      <c r="D69" s="12"/>
-      <c r="E69" s="12"/>
-      <c r="F69" s="9"/>
-      <c r="G69" s="6" t="str">
-        <f aca="false">IF(F69="","",F69*(1+Allgemein!$B$19))</f>
-        <v/>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3584,7 +4357,14 @@
       <c r="D70" s="12"/>
       <c r="E70" s="12"/>
       <c r="F70" s="9"/>
-      <c r="G70" s="6" t="str">
+      <c r="G70" s="5"/>
+      <c r="H70" s="5"/>
+      <c r="I70" s="12"/>
+      <c r="J70" s="12"/>
+      <c r="K70" s="5"/>
+      <c r="L70" s="5"/>
+      <c r="M70" s="5"/>
+      <c r="N70" s="6" t="str">
         <f aca="false">IF(F70="","",F70*(1+Allgemein!$B$19))</f>
         <v/>
       </c>
@@ -3596,7 +4376,14 @@
       <c r="D71" s="12"/>
       <c r="E71" s="12"/>
       <c r="F71" s="9"/>
-      <c r="G71" s="6" t="str">
+      <c r="G71" s="5"/>
+      <c r="H71" s="5"/>
+      <c r="I71" s="12"/>
+      <c r="J71" s="12"/>
+      <c r="K71" s="5"/>
+      <c r="L71" s="5"/>
+      <c r="M71" s="5"/>
+      <c r="N71" s="6" t="str">
         <f aca="false">IF(F71="","",F71*(1+Allgemein!$B$19))</f>
         <v/>
       </c>
@@ -3608,7 +4395,14 @@
       <c r="D72" s="12"/>
       <c r="E72" s="12"/>
       <c r="F72" s="9"/>
-      <c r="G72" s="6" t="str">
+      <c r="G72" s="5"/>
+      <c r="H72" s="5"/>
+      <c r="I72" s="12"/>
+      <c r="J72" s="12"/>
+      <c r="K72" s="5"/>
+      <c r="L72" s="5"/>
+      <c r="M72" s="5"/>
+      <c r="N72" s="6" t="str">
         <f aca="false">IF(F72="","",F72*(1+Allgemein!$B$19))</f>
         <v/>
       </c>
@@ -3620,378 +4414,404 @@
       <c r="D73" s="12"/>
       <c r="E73" s="12"/>
       <c r="F73" s="9"/>
-      <c r="G73" s="6" t="str">
+      <c r="G73" s="5"/>
+      <c r="H73" s="5"/>
+      <c r="I73" s="12"/>
+      <c r="J73" s="12"/>
+      <c r="K73" s="5"/>
+      <c r="L73" s="5"/>
+      <c r="M73" s="5"/>
+      <c r="N73" s="6" t="str">
         <f aca="false">IF(F73="","",F73*(1+Allgemein!$B$19))</f>
         <v/>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="3" t="s">
-        <v>114</v>
+      <c r="A74" s="5"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="12"/>
+      <c r="E74" s="12"/>
+      <c r="F74" s="9"/>
+      <c r="G74" s="5"/>
+      <c r="H74" s="5"/>
+      <c r="I74" s="12"/>
+      <c r="J74" s="12"/>
+      <c r="K74" s="5"/>
+      <c r="L74" s="5"/>
+      <c r="M74" s="5"/>
+      <c r="N74" s="6" t="str">
+        <f aca="false">IF(F74="","",F74*(1+Allgemein!$B$19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="2" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="7" t="s">
+      <c r="A77" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B77" s="7" t="s">
+      <c r="B78" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C77" s="7" t="s">
+      <c r="C78" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D77" s="7" t="s">
+      <c r="D78" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E77" s="7" t="s">
+      <c r="E78" s="7" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="B78" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="C78" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="D78" s="6" t="n">
-        <f aca="false">B78*Allgemein!$B$17</f>
-        <v>408</v>
-      </c>
-      <c r="E78" s="6" t="n">
-        <f aca="false">D78*(1+Allgemein!$B$19)</f>
-        <v>485.52</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="8" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="B79" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D79" s="6" t="n">
         <f aca="false">B79*Allgemein!$B$17</f>
-        <v>476</v>
+        <v>408</v>
       </c>
       <c r="E79" s="6" t="n">
         <f aca="false">D79*(1+Allgemein!$B$19)</f>
-        <v>566.44</v>
+        <v>485.52</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="8" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="B80" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D80" s="6" t="n">
         <f aca="false">B80*Allgemein!$B$17</f>
-        <v>272</v>
+        <v>476</v>
       </c>
       <c r="E80" s="6" t="n">
         <f aca="false">D80*(1+Allgemein!$B$19)</f>
-        <v>323.68</v>
+        <v>566.44</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="8" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="B81" s="12" t="n">
-        <v>0.25</v>
+        <v>4</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D81" s="6" t="n">
         <f aca="false">B81*Allgemein!$B$17</f>
-        <v>17</v>
+        <v>272</v>
       </c>
       <c r="E81" s="6" t="n">
         <f aca="false">D81*(1+Allgemein!$B$19)</f>
-        <v>20.23</v>
+        <v>323.68</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="8" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="B82" s="12" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D82" s="6" t="n">
         <f aca="false">B82*Allgemein!$B$17</f>
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="E82" s="6" t="n">
         <f aca="false">D82*(1+Allgemein!$B$19)</f>
-        <v>60.69</v>
+        <v>20.23</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="8" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="B83" s="12" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D83" s="6" t="n">
         <f aca="false">B83*Allgemein!$B$17</f>
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="E83" s="6" t="n">
         <f aca="false">D83*(1+Allgemein!$B$19)</f>
-        <v>40.46</v>
+        <v>60.69</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="8" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="B84" s="12" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D84" s="6" t="n">
         <f aca="false">B84*Allgemein!$B$17</f>
-        <v>136</v>
+        <v>34</v>
       </c>
       <c r="E84" s="6" t="n">
         <f aca="false">D84*(1+Allgemein!$B$19)</f>
-        <v>161.84</v>
+        <v>40.46</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="8" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="B85" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D85" s="6" t="n">
         <f aca="false">B85*Allgemein!$B$17</f>
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="E85" s="6" t="n">
         <f aca="false">D85*(1+Allgemein!$B$19)</f>
+        <v>161.84</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B86" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="D86" s="6" t="n">
+        <f aca="false">B86*Allgemein!$B$17</f>
+        <v>68</v>
+      </c>
+      <c r="E86" s="6" t="n">
+        <f aca="false">D86*(1+Allgemein!$B$19)</f>
         <v>80.92</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="7" t="s">
+      <c r="A88" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B88" s="7" t="s">
+      <c r="B89" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C88" s="7" t="s">
+      <c r="C89" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D88" s="7" t="s">
+      <c r="D89" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E88" s="7" t="s">
+      <c r="E89" s="7" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="B89" s="9" t="n">
-        <v>190</v>
-      </c>
-      <c r="C89" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E89" s="6" t="n">
-        <f aca="false">B89*(1+Allgemein!$B$19)</f>
-        <v>226.1</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="8" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="B90" s="9" t="n">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="C90" s="8" t="s">
         <v>40</v>
       </c>
       <c r="E90" s="6" t="n">
         <f aca="false">B90*(1+Allgemein!$B$19)</f>
-        <v>178.5</v>
+        <v>226.1</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="8" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="B91" s="9" t="n">
-        <v>26</v>
+        <v>150</v>
       </c>
       <c r="C91" s="8" t="s">
         <v>40</v>
       </c>
       <c r="E91" s="6" t="n">
         <f aca="false">B91*(1+Allgemein!$B$19)</f>
-        <v>30.94</v>
+        <v>178.5</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="8" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B92" s="9" t="n">
-        <v>110</v>
+        <v>26</v>
       </c>
       <c r="C92" s="8" t="s">
         <v>40</v>
       </c>
       <c r="E92" s="6" t="n">
         <f aca="false">B92*(1+Allgemein!$B$19)</f>
-        <v>130.9</v>
+        <v>30.94</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="8" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="B93" s="9" t="n">
-        <v>360</v>
+        <v>110</v>
       </c>
       <c r="C93" s="8" t="s">
         <v>40</v>
       </c>
       <c r="E93" s="6" t="n">
         <f aca="false">B93*(1+Allgemein!$B$19)</f>
-        <v>428.4</v>
+        <v>130.9</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="8" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="B94" s="9" t="n">
-        <v>55</v>
+        <v>360</v>
       </c>
       <c r="C94" s="8" t="s">
         <v>40</v>
       </c>
       <c r="E94" s="6" t="n">
         <f aca="false">B94*(1+Allgemein!$B$19)</f>
-        <v>65.45</v>
+        <v>428.4</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="8" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B95" s="9" t="n">
-        <v>135</v>
+        <v>55</v>
       </c>
       <c r="C95" s="8" t="s">
         <v>40</v>
       </c>
       <c r="E95" s="6" t="n">
         <f aca="false">B95*(1+Allgemein!$B$19)</f>
-        <v>160.65</v>
+        <v>65.45</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="8" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="B96" s="9" t="n">
-        <v>170</v>
+        <v>135</v>
       </c>
       <c r="C96" s="8" t="s">
         <v>40</v>
       </c>
       <c r="E96" s="6" t="n">
         <f aca="false">B96*(1+Allgemein!$B$19)</f>
+        <v>160.65</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="B97" s="9" t="n">
+        <v>170</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E97" s="6" t="n">
+        <f aca="false">B97*(1+Allgemein!$B$19)</f>
         <v>202.3</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="7" t="s">
+      <c r="A99" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B99" s="7" t="s">
+      <c r="B100" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C99" s="7" t="s">
+      <c r="C100" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D99" s="7" t="s">
+      <c r="D100" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E99" s="7" t="s">
+      <c r="E100" s="7" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="B100" s="9" t="n">
-        <v>149</v>
-      </c>
-      <c r="C100" s="8" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="B101" s="12" t="n">
+        <v>146</v>
+      </c>
+      <c r="B101" s="9" t="n">
+        <v>149</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="B102" s="12" t="n">
         <v>0.1</v>
       </c>
-      <c r="C101" s="8" t="s">
-        <v>134</v>
+      <c r="C102" s="8" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="6">
+  <dataValidations count="10">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B4" type="list">
       <formula1>"Ja,Nein"</formula1>
       <formula2>0</formula2>
@@ -4004,16 +4824,32 @@
       <formula1>"Standard,Premium"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A38:A55" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G9:G33" type="list">
+      <formula1>"–,A+++,A++,A+,A,B,C,D"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H9:H33" type="list">
+      <formula1>"–,A+++,A++,A+,A,B,C,D"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A39:A56" type="list">
       <formula1>"Ja,Nein"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E38:E55" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E39:E56" type="list">
       <formula1>"Standard,Premium"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A60:A73" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A61:A74" type="list">
       <formula1>"Ja,Nein"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G61:G74" type="list">
+      <formula1>"–,A+++,A++,A+,A,B,C,D"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H61:H74" type="list">
+      <formula1>"–,A+++,A++,A+,A,B,C,D"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -4032,7 +4868,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -4062,15 +4898,15 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
         <v>56</v>
       </c>
@@ -4087,7 +4923,16 @@
         <v>61</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>62</v>
+        <v>151</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4095,10 +4940,10 @@
         <v>24</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="D9" s="12" t="n">
         <v>6</v>
@@ -4106,7 +4951,12 @@
       <c r="E9" s="9" t="n">
         <v>8900</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="6" t="n">
         <f aca="false">IF(E9="","",E9*(1+Allgemein!$B$19))</f>
         <v>10591</v>
       </c>
@@ -4116,10 +4966,10 @@
         <v>24</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="D10" s="12" t="n">
         <v>9</v>
@@ -4127,7 +4977,12 @@
       <c r="E10" s="9" t="n">
         <v>10400</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="6" t="n">
         <f aca="false">IF(E10="","",E10*(1+Allgemein!$B$19))</f>
         <v>12376</v>
       </c>
@@ -4137,10 +4992,10 @@
         <v>24</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="D11" s="12" t="n">
         <v>12</v>
@@ -4148,7 +5003,12 @@
       <c r="E11" s="9" t="n">
         <v>11900</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="6" t="n">
         <f aca="false">IF(E11="","",E11*(1+Allgemein!$B$19))</f>
         <v>14161</v>
       </c>
@@ -4158,10 +5018,10 @@
         <v>24</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="D12" s="12" t="n">
         <v>16</v>
@@ -4169,7 +5029,12 @@
       <c r="E12" s="9" t="n">
         <v>13400</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="6" t="n">
         <f aca="false">IF(E12="","",E12*(1+Allgemein!$B$19))</f>
         <v>15946</v>
       </c>
@@ -4179,10 +5044,10 @@
         <v>24</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="D13" s="12" t="n">
         <v>18</v>
@@ -4190,7 +5055,12 @@
       <c r="E13" s="9" t="n">
         <v>14900</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F13" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="6" t="n">
         <f aca="false">IF(E13="","",E13*(1+Allgemein!$B$19))</f>
         <v>17731</v>
       </c>
@@ -4201,7 +5071,10 @@
       <c r="C14" s="5"/>
       <c r="D14" s="12"/>
       <c r="E14" s="9"/>
-      <c r="F14" s="6" t="str">
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="6" t="str">
         <f aca="false">IF(E14="","",E14*(1+Allgemein!$B$19))</f>
         <v/>
       </c>
@@ -4212,7 +5085,10 @@
       <c r="C15" s="5"/>
       <c r="D15" s="12"/>
       <c r="E15" s="9"/>
-      <c r="F15" s="6" t="str">
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="6" t="str">
         <f aca="false">IF(E15="","",E15*(1+Allgemein!$B$19))</f>
         <v/>
       </c>
@@ -4223,7 +5099,10 @@
       <c r="C16" s="5"/>
       <c r="D16" s="12"/>
       <c r="E16" s="9"/>
-      <c r="F16" s="6" t="str">
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="6" t="str">
         <f aca="false">IF(E16="","",E16*(1+Allgemein!$B$19))</f>
         <v/>
       </c>
@@ -4234,7 +5113,10 @@
       <c r="C17" s="5"/>
       <c r="D17" s="12"/>
       <c r="E17" s="9"/>
-      <c r="F17" s="6" t="str">
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="6" t="str">
         <f aca="false">IF(E17="","",E17*(1+Allgemein!$B$19))</f>
         <v/>
       </c>
@@ -4245,19 +5127,22 @@
       <c r="C18" s="5"/>
       <c r="D18" s="12"/>
       <c r="E18" s="9"/>
-      <c r="F18" s="6" t="str">
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="6" t="str">
         <f aca="false">IF(E18="","",E18*(1+Allgemein!$B$19))</f>
         <v/>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4279,13 +5164,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="B23" s="12" t="n">
         <v>30</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D23" s="6" t="n">
         <f aca="false">B23*Allgemein!$B$17</f>
@@ -4298,13 +5183,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="B24" s="12" t="n">
         <v>12</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D24" s="6" t="n">
         <f aca="false">B24*Allgemein!$B$17</f>
@@ -4317,13 +5202,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="B25" s="12" t="n">
         <v>6</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D25" s="6" t="n">
         <f aca="false">B25*Allgemein!$B$17</f>
@@ -4336,13 +5221,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="B26" s="12" t="n">
         <v>10</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D26" s="6" t="n">
         <f aca="false">B26*Allgemein!$B$17</f>
@@ -4355,13 +5240,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="B27" s="12" t="n">
         <v>2.5</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D27" s="6" t="n">
         <f aca="false">B27*Allgemein!$B$17</f>
@@ -4374,13 +5259,13 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="B28" s="12" t="n">
         <v>6</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D28" s="6" t="n">
         <f aca="false">B28*Allgemein!$B$17</f>
@@ -4393,7 +5278,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4415,7 +5300,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="B32" s="9" t="n">
         <v>4200</v>
@@ -4430,7 +5315,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="B33" s="9" t="n">
         <v>900</v>
@@ -4445,7 +5330,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="B34" s="9" t="n">
         <v>150</v>
@@ -4460,7 +5345,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="B35" s="9" t="n">
         <v>350</v>
@@ -4475,7 +5360,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="B36" s="9" t="n">
         <v>380</v>
@@ -4490,7 +5375,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="B37" s="9" t="n">
         <v>650</v>
@@ -4505,7 +5390,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4527,23 +5412,27 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="B41" s="12" t="n">
         <v>0.25</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B4" type="list">
       <formula1>"Ja,Nein"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A9:A18" type="list">
       <formula1>"Ja,Nein"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F9:F18" type="list">
+      <formula1>"–,A+++,A++,A+,A,B,C,D"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -4592,12 +5481,12 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4611,13 +5500,13 @@
         <v>58</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4625,10 +5514,10 @@
         <v>24</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="D9" s="12" t="n">
         <v>450</v>
@@ -4646,10 +5535,10 @@
         <v>24</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="D10" s="12" t="n">
         <v>400</v>
@@ -4719,17 +5608,17 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4749,7 +5638,7 @@
         <v>61</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4757,10 +5646,10 @@
         <v>24</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="D21" s="12" t="n">
         <v>4</v>
@@ -4778,10 +5667,10 @@
         <v>24</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="D22" s="12" t="n">
         <v>6</v>
@@ -4799,10 +5688,10 @@
         <v>24</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="D23" s="12" t="n">
         <v>8</v>
@@ -4820,10 +5709,10 @@
         <v>24</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="D24" s="12" t="n">
         <v>10</v>
@@ -4841,10 +5730,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="D25" s="12" t="n">
         <v>15</v>
@@ -4914,17 +5803,17 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4938,13 +5827,13 @@
         <v>58</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>61</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4952,10 +5841,10 @@
         <v>24</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="D36" s="12" t="n">
         <v>5.1</v>
@@ -4973,10 +5862,10 @@
         <v>24</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="D37" s="12" t="n">
         <v>7.7</v>
@@ -4994,10 +5883,10 @@
         <v>24</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="D38" s="12" t="n">
         <v>10.2</v>
@@ -5067,17 +5956,17 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5099,13 +5988,13 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="B49" s="12" t="n">
         <v>5</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D49" s="6" t="n">
         <f aca="false">B49*Allgemein!$B$17</f>
@@ -5118,7 +6007,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5140,13 +6029,13 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="B53" s="12" t="n">
         <v>8</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D53" s="6" t="n">
         <f aca="false">B53*Allgemein!$B$17</f>
@@ -5159,13 +6048,13 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="B54" s="12" t="n">
         <v>0.6</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D54" s="6" t="n">
         <f aca="false">B54*Allgemein!$B$17</f>
@@ -5178,13 +6067,13 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="B55" s="12" t="n">
         <v>4</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D55" s="6" t="n">
         <f aca="false">B55*Allgemein!$B$17</f>
@@ -5197,13 +6086,13 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="B56" s="12" t="n">
         <v>4</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D56" s="6" t="n">
         <f aca="false">B56*Allgemein!$B$17</f>
@@ -5216,7 +6105,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5238,7 +6127,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="8" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="B60" s="9" t="n">
         <v>48</v>
@@ -5253,7 +6142,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="8" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="B61" s="9" t="n">
         <v>480</v>
@@ -5268,7 +6157,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="8" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="B62" s="9" t="n">
         <v>650</v>
@@ -5283,7 +6172,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="B63" s="9" t="n">
         <v>450</v>
@@ -5298,7 +6187,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="8" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="B64" s="9" t="n">
         <v>250</v>
@@ -5313,7 +6202,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="8" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="B65" s="9" t="n">
         <v>450</v>
@@ -5328,7 +6217,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="3" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5350,35 +6239,35 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="8" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="B69" s="12" t="n">
         <v>950</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="8" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="B70" s="13" t="n">
         <v>0.35</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="B71" s="13" t="n">
         <v>0.077</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -5445,7 +6334,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5467,16 +6356,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="C8" s="8"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="B9" s="9" t="n">
         <v>900</v>
@@ -5491,13 +6380,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="B10" s="12" t="n">
         <v>12</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D10" s="6" t="n">
         <f aca="false">B10*Allgemein!$B$17</f>
@@ -5510,7 +6399,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="B11" s="9" t="n">
         <v>160</v>
@@ -5525,13 +6414,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="B12" s="12" t="n">
         <v>1.5</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D12" s="6" t="n">
         <f aca="false">B12*Allgemein!$B$17</f>
@@ -5544,7 +6433,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="B13" s="9" t="n">
         <v>120</v>
@@ -5559,13 +6448,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="B14" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D14" s="6" t="n">
         <f aca="false">B14*Allgemein!$B$17</f>
@@ -5578,7 +6467,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="B15" s="9" t="n">
         <v>140</v>
@@ -5593,13 +6482,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="B16" s="12" t="n">
         <v>1.5</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D16" s="6" t="n">
         <f aca="false">B16*Allgemein!$B$17</f>
@@ -5612,7 +6501,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="B17" s="9" t="n">
         <v>600</v>
@@ -5627,13 +6516,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="B18" s="12" t="n">
         <v>5</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D18" s="6" t="n">
         <f aca="false">B18*Allgemein!$B$17</f>
@@ -5646,7 +6535,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5668,16 +6557,16 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="C22" s="8"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="B23" s="9" t="n">
         <v>180</v>
@@ -5692,13 +6581,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="B24" s="12" t="n">
         <v>3</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D24" s="6" t="n">
         <f aca="false">B24*Allgemein!$B$17</f>
@@ -5711,7 +6600,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="B25" s="9" t="n">
         <v>75</v>
@@ -5726,13 +6615,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="B26" s="12" t="n">
         <v>1.25</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D26" s="6" t="n">
         <f aca="false">B26*Allgemein!$B$17</f>
@@ -5745,7 +6634,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="B27" s="9" t="n">
         <v>65</v>
@@ -5760,13 +6649,13 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="B28" s="12" t="n">
         <v>0.75</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D28" s="6" t="n">
         <f aca="false">B28*Allgemein!$B$17</f>
@@ -5779,7 +6668,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="B29" s="9" t="n">
         <v>70</v>
@@ -5794,13 +6683,13 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="B30" s="12" t="n">
         <v>1.25</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D30" s="6" t="n">
         <f aca="false">B30*Allgemein!$B$17</f>
@@ -5813,7 +6702,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="B31" s="9" t="n">
         <v>450</v>
@@ -5828,13 +6717,13 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="B32" s="12" t="n">
         <v>4</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D32" s="6" t="n">
         <f aca="false">B32*Allgemein!$B$17</f>
@@ -5847,7 +6736,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5869,16 +6758,16 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="C36" s="8"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="B37" s="9" t="n">
         <v>1300</v>
@@ -5893,13 +6782,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="B38" s="12" t="n">
         <v>14</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D38" s="6" t="n">
         <f aca="false">B38*Allgemein!$B$17</f>
@@ -5912,7 +6801,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="B39" s="9" t="n">
         <v>180</v>
@@ -5927,13 +6816,13 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="B40" s="12" t="n">
         <v>2</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D40" s="6" t="n">
         <f aca="false">B40*Allgemein!$B$17</f>
@@ -5946,7 +6835,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="B41" s="9" t="n">
         <v>140</v>
@@ -5961,13 +6850,13 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="B42" s="12" t="n">
         <v>1.5</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D42" s="6" t="n">
         <f aca="false">B42*Allgemein!$B$17</f>
@@ -5980,7 +6869,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="B43" s="9" t="n">
         <v>150</v>
@@ -5995,13 +6884,13 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="B44" s="12" t="n">
         <v>1.75</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D44" s="6" t="n">
         <f aca="false">B44*Allgemein!$B$17</f>
@@ -6014,7 +6903,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="B45" s="9" t="n">
         <v>700</v>
@@ -6029,13 +6918,13 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="B46" s="12" t="n">
         <v>7</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D46" s="6" t="n">
         <f aca="false">B46*Allgemein!$B$17</f>
@@ -6068,7 +6957,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -6080,12 +6969,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6098,12 +6987,12 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6111,7 +7000,7 @@
         <v>56</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6119,7 +7008,7 @@
         <v>24</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6127,7 +7016,7 @@
         <v>24</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6135,7 +7024,7 @@
         <v>24</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6160,20 +7049,20 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
         <v>56</v>
       </c>
@@ -6181,19 +7070,31 @@
         <v>57</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>58</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>228</v>
+        <v>243</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6201,16 +7102,16 @@
         <v>24</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>599</v>
@@ -6218,22 +7119,30 @@
       <c r="G22" s="9" t="n">
         <v>49</v>
       </c>
+      <c r="H22" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>799</v>
@@ -6241,22 +7150,30 @@
       <c r="G23" s="9" t="n">
         <v>49</v>
       </c>
+      <c r="H23" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>849</v>
@@ -6264,22 +7181,30 @@
       <c r="G24" s="9" t="n">
         <v>39</v>
       </c>
+      <c r="H24" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>649</v>
@@ -6287,22 +7212,30 @@
       <c r="G25" s="9" t="n">
         <v>149</v>
       </c>
+      <c r="H25" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>237</v>
+        <v>258</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>699</v>
@@ -6310,22 +7243,30 @@
       <c r="G26" s="9" t="n">
         <v>129</v>
       </c>
+      <c r="H26" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>749</v>
@@ -6333,22 +7274,30 @@
       <c r="G27" s="9" t="n">
         <v>39</v>
       </c>
+      <c r="H27" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>1199</v>
@@ -6356,22 +7305,30 @@
       <c r="G28" s="9" t="n">
         <v>49</v>
       </c>
+      <c r="H28" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
         <v>24</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>999</v>
@@ -6379,6 +7336,14 @@
       <c r="G29" s="9" t="n">
         <v>39</v>
       </c>
+      <c r="H29" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5"/>
@@ -6388,6 +7353,10 @@
       <c r="E30" s="5"/>
       <c r="F30" s="9"/>
       <c r="G30" s="9"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5"/>
@@ -6397,6 +7366,10 @@
       <c r="E31" s="5"/>
       <c r="F31" s="9"/>
       <c r="G31" s="9"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5"/>
@@ -6406,6 +7379,10 @@
       <c r="E32" s="5"/>
       <c r="F32" s="9"/>
       <c r="G32" s="9"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="5"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5"/>
@@ -6415,6 +7392,10 @@
       <c r="E33" s="5"/>
       <c r="F33" s="9"/>
       <c r="G33" s="9"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5"/>
@@ -6424,15 +7405,19 @@
       <c r="E34" s="5"/>
       <c r="F34" s="9"/>
       <c r="G34" s="9"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="5"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6454,7 +7439,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="B39" s="9" t="n">
         <v>39</v>
@@ -6465,7 +7450,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
       <c r="B40" s="9" t="n">
         <v>25</v>
@@ -6476,15 +7461,33 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="s">
-        <v>246</v>
+        <v>267</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="C41" s="8"/>
     </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="C42" s="8"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="C43" s="8"/>
+    </row>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations count="6">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B4" type="list">
       <formula1>"Ja,Nein"</formula1>
       <formula2>0</formula2>
@@ -6499,6 +7502,14 @@
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B22:B34" type="list">
       <formula1>"Siemens Hausgeräte,Miele,Liebherr"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H22:H34" type="list">
+      <formula1>"–,A+++,A++,A+,A,B,C,D,E,F,G"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I22:I34" type="list">
+      <formula1>"A–G (nuova),A+++–D"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -6547,7 +7558,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>248</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6569,7 +7580,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>249</v>
+        <v>274</v>
       </c>
       <c r="B8" s="9" t="n">
         <v>42</v>
@@ -6584,13 +7595,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="B9" s="12" t="n">
         <v>0.75</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D9" s="6" t="n">
         <f aca="false">B9*Allgemein!$B$17</f>
@@ -6603,7 +7614,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="B10" s="9" t="n">
         <v>52</v>
@@ -6618,13 +7629,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="B11" s="12" t="n">
         <v>1.2</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D11" s="6" t="n">
         <f aca="false">B11*Allgemein!$B$17</f>
@@ -6637,7 +7648,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>253</v>
+        <v>278</v>
       </c>
       <c r="B12" s="9" t="n">
         <v>30</v>
@@ -6652,13 +7663,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>254</v>
+        <v>279</v>
       </c>
       <c r="B13" s="12" t="n">
         <v>0.6</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D13" s="6" t="n">
         <f aca="false">B13*Allgemein!$B$17</f>
@@ -6671,7 +7682,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>255</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6693,7 +7704,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>256</v>
+        <v>281</v>
       </c>
       <c r="B17" s="9" t="n">
         <v>1650</v>
@@ -6708,13 +7719,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>257</v>
+        <v>282</v>
       </c>
       <c r="B18" s="12" t="n">
         <v>18</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D18" s="6" t="n">
         <f aca="false">B18*Allgemein!$B$17</f>
@@ -6727,7 +7738,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>258</v>
+        <v>283</v>
       </c>
       <c r="B19" s="9" t="n">
         <v>55</v>
@@ -6742,13 +7753,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>259</v>
+        <v>284</v>
       </c>
       <c r="B20" s="12" t="n">
         <v>1.4</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D20" s="6" t="n">
         <f aca="false">B20*Allgemein!$B$17</f>
@@ -6761,7 +7772,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>260</v>
+        <v>285</v>
       </c>
       <c r="B21" s="9" t="n">
         <v>330</v>
@@ -6776,13 +7787,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>261</v>
+        <v>286</v>
       </c>
       <c r="B22" s="12" t="n">
         <v>2.5</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D22" s="6" t="n">
         <f aca="false">B22*Allgemein!$B$17</f>
@@ -6795,7 +7806,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>262</v>
+        <v>287</v>
       </c>
       <c r="B23" s="9" t="n">
         <v>0</v>
@@ -6810,13 +7821,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>263</v>
+        <v>288</v>
       </c>
       <c r="B24" s="12" t="n">
         <v>2.75</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D24" s="6" t="n">
         <f aca="false">B24*Allgemein!$B$17</f>
@@ -6829,12 +7840,12 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>264</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>265</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6854,7 +7865,7 @@
         <v>61</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6862,10 +7873,10 @@
         <v>24</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>266</v>
+        <v>291</v>
       </c>
       <c r="D29" s="12" t="n">
         <v>11</v>
@@ -6883,10 +7894,10 @@
         <v>24</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>267</v>
+        <v>292</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>268</v>
+        <v>293</v>
       </c>
       <c r="D30" s="12" t="n">
         <v>11</v>
@@ -6904,10 +7915,10 @@
         <v>24</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>269</v>
+        <v>294</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>270</v>
+        <v>295</v>
       </c>
       <c r="D31" s="12" t="n">
         <v>11</v>
@@ -6925,10 +7936,10 @@
         <v>24</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>271</v>
+        <v>296</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>272</v>
+        <v>297</v>
       </c>
       <c r="D32" s="12" t="n">
         <v>11</v>
@@ -6998,12 +8009,12 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>273</v>
+        <v>298</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7025,13 +8036,13 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="s">
-        <v>274</v>
+        <v>299</v>
       </c>
       <c r="B42" s="12" t="n">
         <v>7</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D42" s="6" t="n">
         <f aca="false">B42*Allgemein!$B$17</f>
@@ -7068,2161 +8079,2195 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E129"/>
+  <dimension ref="A1:E131"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>276</v>
+        <v>301</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>277</v>
+        <v>302</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>278</v>
+        <v>303</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>279</v>
+        <v>304</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>281</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>282</v>
+        <v>307</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>283</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>287</v>
+        <v>312</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>288</v>
+        <v>313</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>289</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>291</v>
+        <v>316</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>292</v>
+        <v>317</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>294</v>
+        <v>319</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>295</v>
+        <v>320</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>296</v>
+        <v>321</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>297</v>
+        <v>322</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>298</v>
+        <v>323</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>299</v>
+        <v>324</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>298</v>
+        <v>323</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>301</v>
+        <v>326</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>302</v>
+        <v>327</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>303</v>
+        <v>328</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>304</v>
+        <v>329</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>298</v>
+        <v>323</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>305</v>
+        <v>330</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>306</v>
+        <v>331</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>298</v>
+        <v>323</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>307</v>
+        <v>332</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>308</v>
+        <v>333</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>298</v>
+        <v>323</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B16" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>309</v>
+        <v>334</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>310</v>
+        <v>335</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>298</v>
+        <v>323</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B17" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>311</v>
+        <v>336</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>312</v>
+        <v>337</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="B18" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>281</v>
+        <v>306</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="B19" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>316</v>
+        <v>341</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>317</v>
+        <v>342</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="B20" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>318</v>
+        <v>343</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>317</v>
+        <v>345</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="B21" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>320</v>
+        <v>346</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>321</v>
+        <v>347</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>322</v>
+        <v>348</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B22" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>323</v>
+        <v>349</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>324</v>
+        <v>350</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B23" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>326</v>
+        <v>352</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B24" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>327</v>
+        <v>353</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>328</v>
+        <v>354</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B25" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>329</v>
+        <v>355</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>330</v>
+        <v>356</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B26" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>331</v>
+        <v>357</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>332</v>
+        <v>358</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B27" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>333</v>
+        <v>359</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>334</v>
+        <v>360</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B28" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>335</v>
+        <v>361</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>336</v>
+        <v>362</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B29" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>337</v>
+        <v>363</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>338</v>
+        <v>364</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B30" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>339</v>
+        <v>365</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>340</v>
+        <v>366</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B31" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>341</v>
+        <v>367</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B32" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>343</v>
+        <v>369</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>344</v>
+        <v>370</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B33" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>345</v>
+        <v>371</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>346</v>
+        <v>372</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B34" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>347</v>
+        <v>373</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>348</v>
+        <v>374</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B35" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>349</v>
+        <v>375</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>350</v>
+        <v>376</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B36" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>352</v>
+        <v>378</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B37" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>353</v>
+        <v>379</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>354</v>
+        <v>380</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B38" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>355</v>
+        <v>381</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>356</v>
+        <v>382</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B39" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>357</v>
+        <v>383</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>358</v>
+        <v>384</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="B40" s="14" t="s">
         <v>23</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>277</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="B41" s="14" t="s">
         <v>23</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>359</v>
+        <v>385</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>361</v>
+        <v>387</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B42" s="14" t="s">
         <v>23</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>362</v>
+        <v>388</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>363</v>
+        <v>389</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B43" s="14" t="s">
         <v>23</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>364</v>
+        <v>390</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>365</v>
+        <v>391</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B44" s="14" t="s">
         <v>23</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>366</v>
+        <v>392</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>367</v>
+        <v>393</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B45" s="14" t="s">
         <v>23</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>303</v>
+        <v>328</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>368</v>
+        <v>394</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B46" s="14" t="s">
         <v>23</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>305</v>
+        <v>330</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B47" s="14" t="s">
         <v>23</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>307</v>
+        <v>332</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>370</v>
+        <v>396</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B48" s="14" t="s">
         <v>23</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>371</v>
+        <v>397</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>372</v>
+        <v>398</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B49" s="14" t="s">
         <v>23</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>373</v>
+        <v>399</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>374</v>
+        <v>400</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B50" s="14" t="s">
         <v>23</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>375</v>
+        <v>401</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>376</v>
+        <v>402</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B51" s="14" t="s">
         <v>23</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>377</v>
+        <v>403</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>378</v>
+        <v>404</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B52" s="14" t="s">
         <v>23</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>379</v>
+        <v>405</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>380</v>
+        <v>406</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B53" s="14" t="s">
         <v>23</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>381</v>
+        <v>407</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B54" s="14" t="s">
         <v>23</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>383</v>
+        <v>409</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>384</v>
+        <v>410</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="14" t="s">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="B55" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>279</v>
+        <v>304</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="14" t="s">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="B56" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>385</v>
+        <v>411</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>386</v>
+        <v>412</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>387</v>
+        <v>413</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="14" t="s">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="B57" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>388</v>
+        <v>414</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>389</v>
+        <v>415</v>
       </c>
       <c r="E57" s="14" t="s">
-        <v>361</v>
+        <v>416</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="14" t="s">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="B58" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>390</v>
+        <v>417</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>391</v>
+        <v>418</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>392</v>
+        <v>419</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B59" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>393</v>
+        <v>420</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>394</v>
+        <v>421</v>
       </c>
       <c r="E59" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B60" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>395</v>
+        <v>422</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>396</v>
+        <v>423</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B61" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>397</v>
+        <v>424</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>398</v>
+        <v>425</v>
       </c>
       <c r="E61" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B62" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>399</v>
+        <v>426</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>400</v>
+        <v>427</v>
       </c>
       <c r="E62" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B63" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C63" s="14" t="s">
-        <v>401</v>
+        <v>428</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>402</v>
+        <v>429</v>
       </c>
       <c r="E63" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B64" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>403</v>
+        <v>430</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>404</v>
+        <v>431</v>
       </c>
       <c r="E64" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B65" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C65" s="14" t="s">
-        <v>405</v>
+        <v>432</v>
       </c>
       <c r="D65" s="14" t="s">
-        <v>406</v>
+        <v>433</v>
       </c>
       <c r="E65" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B66" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>407</v>
+        <v>434</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>408</v>
+        <v>435</v>
       </c>
       <c r="E66" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B67" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C67" s="14" t="s">
-        <v>409</v>
+        <v>436</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>410</v>
+        <v>437</v>
       </c>
       <c r="E67" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B68" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>411</v>
+        <v>438</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>412</v>
+        <v>439</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B69" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C69" s="14" t="s">
-        <v>413</v>
+        <v>440</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>414</v>
+        <v>441</v>
       </c>
       <c r="E69" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B70" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C70" s="14" t="s">
-        <v>415</v>
+        <v>442</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>416</v>
+        <v>443</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B71" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C71" s="14" t="s">
-        <v>417</v>
+        <v>444</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>418</v>
+        <v>445</v>
       </c>
       <c r="E71" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B72" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>419</v>
+        <v>446</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>420</v>
+        <v>447</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="14" t="s">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="B73" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C73" s="14" t="s">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="D73" s="14" t="s">
-        <v>283</v>
+        <v>308</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B74" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C74" s="14" t="s">
-        <v>278</v>
+        <v>303</v>
       </c>
       <c r="D74" s="14" t="s">
-        <v>421</v>
+        <v>448</v>
       </c>
       <c r="E74" s="14" t="s">
-        <v>422</v>
+        <v>449</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B75" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C75" s="14" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="D75" s="14" t="s">
-        <v>423</v>
+        <v>450</v>
       </c>
       <c r="E75" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B76" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C76" s="14" t="s">
-        <v>282</v>
+        <v>307</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>424</v>
+        <v>451</v>
       </c>
       <c r="E76" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B77" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C77" s="14" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="D77" s="14" t="s">
-        <v>425</v>
+        <v>452</v>
       </c>
       <c r="E77" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B78" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C78" s="14" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="D78" s="14" t="s">
-        <v>426</v>
+        <v>453</v>
       </c>
       <c r="E78" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B79" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C79" s="14" t="s">
-        <v>288</v>
+        <v>313</v>
       </c>
       <c r="D79" s="14" t="s">
-        <v>427</v>
+        <v>454</v>
       </c>
       <c r="E79" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B80" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>428</v>
+        <v>455</v>
       </c>
       <c r="D80" s="14" t="s">
-        <v>429</v>
+        <v>456</v>
       </c>
       <c r="E80" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B81" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C81" s="14" t="s">
-        <v>430</v>
+        <v>457</v>
       </c>
       <c r="D81" s="14" t="s">
-        <v>431</v>
+        <v>458</v>
       </c>
       <c r="E81" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B82" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C82" s="14" t="s">
-        <v>432</v>
+        <v>459</v>
       </c>
       <c r="D82" s="14" t="s">
-        <v>433</v>
+        <v>460</v>
       </c>
       <c r="E82" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B83" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C83" s="14" t="s">
-        <v>291</v>
+        <v>316</v>
       </c>
       <c r="D83" s="14" t="s">
-        <v>434</v>
+        <v>461</v>
       </c>
       <c r="E83" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B84" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C84" s="14" t="s">
-        <v>294</v>
+        <v>319</v>
       </c>
       <c r="D84" s="14" t="s">
-        <v>435</v>
+        <v>462</v>
       </c>
       <c r="E84" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B85" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C85" s="14" t="s">
-        <v>436</v>
+        <v>463</v>
       </c>
       <c r="D85" s="14" t="s">
-        <v>437</v>
+        <v>464</v>
       </c>
       <c r="E85" s="14" t="s">
-        <v>422</v>
+        <v>449</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B86" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C86" s="14" t="s">
-        <v>362</v>
+        <v>388</v>
       </c>
       <c r="D86" s="14" t="s">
-        <v>438</v>
+        <v>465</v>
       </c>
       <c r="E86" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B87" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C87" s="14" t="s">
-        <v>364</v>
+        <v>390</v>
       </c>
       <c r="D87" s="14" t="s">
-        <v>439</v>
+        <v>466</v>
       </c>
       <c r="E87" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B88" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C88" s="14" t="s">
-        <v>366</v>
+        <v>392</v>
       </c>
       <c r="D88" s="14" t="s">
-        <v>440</v>
+        <v>467</v>
       </c>
       <c r="E88" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B89" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C89" s="14" t="s">
-        <v>303</v>
+        <v>328</v>
       </c>
       <c r="D89" s="14" t="s">
-        <v>441</v>
+        <v>468</v>
       </c>
       <c r="E89" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B90" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C90" s="14" t="s">
-        <v>305</v>
+        <v>330</v>
       </c>
       <c r="D90" s="14" t="s">
-        <v>442</v>
+        <v>469</v>
       </c>
       <c r="E90" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B91" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C91" s="14" t="s">
-        <v>307</v>
+        <v>332</v>
       </c>
       <c r="D91" s="14" t="s">
-        <v>443</v>
+        <v>470</v>
       </c>
       <c r="E91" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B92" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C92" s="14" t="s">
-        <v>309</v>
+        <v>334</v>
       </c>
       <c r="D92" s="14" t="s">
-        <v>444</v>
+        <v>471</v>
       </c>
       <c r="E92" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B93" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C93" s="14" t="s">
-        <v>311</v>
+        <v>336</v>
       </c>
       <c r="D93" s="14" t="s">
-        <v>445</v>
+        <v>472</v>
       </c>
       <c r="E93" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B94" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C94" s="14" t="s">
-        <v>446</v>
+        <v>473</v>
       </c>
       <c r="D94" s="14" t="s">
-        <v>447</v>
+        <v>474</v>
       </c>
       <c r="E94" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B95" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C95" s="14" t="s">
-        <v>371</v>
+        <v>397</v>
       </c>
       <c r="D95" s="14" t="s">
-        <v>448</v>
+        <v>475</v>
       </c>
       <c r="E95" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B96" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C96" s="14" t="s">
-        <v>379</v>
+        <v>405</v>
       </c>
       <c r="D96" s="14" t="s">
+        <v>476</v>
+      </c>
+      <c r="E96" s="14" t="s">
         <v>449</v>
-      </c>
-      <c r="E96" s="14" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B97" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C97" s="14" t="s">
-        <v>381</v>
+        <v>407</v>
       </c>
       <c r="D97" s="14" t="s">
-        <v>450</v>
+        <v>477</v>
       </c>
       <c r="E97" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B98" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C98" s="14" t="s">
-        <v>451</v>
+        <v>478</v>
       </c>
       <c r="D98" s="14" t="s">
-        <v>452</v>
+        <v>479</v>
       </c>
       <c r="E98" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B99" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C99" s="14" t="s">
-        <v>453</v>
+        <v>480</v>
       </c>
       <c r="D99" s="14" t="s">
-        <v>454</v>
+        <v>481</v>
       </c>
       <c r="E99" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B100" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C100" s="14" t="s">
-        <v>455</v>
+        <v>482</v>
       </c>
       <c r="D100" s="14" t="s">
-        <v>456</v>
+        <v>483</v>
       </c>
       <c r="E100" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B101" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C101" s="14" t="s">
-        <v>383</v>
+        <v>409</v>
       </c>
       <c r="D101" s="14" t="s">
-        <v>457</v>
+        <v>484</v>
       </c>
       <c r="E101" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B102" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C102" s="14" t="s">
-        <v>458</v>
+        <v>485</v>
       </c>
       <c r="D102" s="14" t="s">
-        <v>459</v>
+        <v>486</v>
       </c>
       <c r="E102" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B103" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C103" s="14" t="s">
-        <v>460</v>
+        <v>487</v>
       </c>
       <c r="D103" s="14" t="s">
-        <v>461</v>
+        <v>488</v>
       </c>
       <c r="E103" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B104" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C104" s="14" t="s">
-        <v>462</v>
+        <v>489</v>
       </c>
       <c r="D104" s="14" t="s">
-        <v>463</v>
+        <v>490</v>
       </c>
       <c r="E104" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B105" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C105" s="14" t="s">
-        <v>464</v>
+        <v>491</v>
       </c>
       <c r="D105" s="14" t="s">
-        <v>465</v>
+        <v>492</v>
       </c>
       <c r="E105" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B106" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C106" s="14" t="s">
-        <v>466</v>
+        <v>493</v>
       </c>
       <c r="D106" s="14" t="s">
-        <v>467</v>
+        <v>494</v>
       </c>
       <c r="E106" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="14" t="s">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="B107" s="14" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="C107" s="14" t="s">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="D107" s="14" t="s">
-        <v>287</v>
+        <v>312</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="14" t="s">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="B108" s="14" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="C108" s="14" t="s">
-        <v>468</v>
+        <v>495</v>
       </c>
       <c r="D108" s="14" t="s">
-        <v>469</v>
+        <v>496</v>
       </c>
       <c r="E108" s="14" t="s">
-        <v>470</v>
+        <v>497</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="14" t="s">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="B109" s="14" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="C109" s="14" t="s">
-        <v>471</v>
+        <v>498</v>
       </c>
       <c r="D109" s="14" t="s">
-        <v>472</v>
+        <v>499</v>
       </c>
       <c r="E109" s="14" t="s">
-        <v>473</v>
+        <v>500</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B110" s="14" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="C110" s="14" t="s">
-        <v>453</v>
+        <v>480</v>
       </c>
       <c r="D110" s="14" t="s">
-        <v>474</v>
+        <v>501</v>
       </c>
       <c r="E110" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B111" s="14" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="C111" s="14" t="s">
-        <v>455</v>
+        <v>482</v>
       </c>
       <c r="D111" s="14" t="s">
-        <v>475</v>
+        <v>502</v>
       </c>
       <c r="E111" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B112" s="14" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="C112" s="14" t="s">
-        <v>383</v>
+        <v>409</v>
       </c>
       <c r="D112" s="14" t="s">
-        <v>476</v>
+        <v>503</v>
       </c>
       <c r="E112" s="14" t="s">
-        <v>422</v>
+        <v>449</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="14" t="s">
-        <v>275</v>
+        <v>315</v>
       </c>
       <c r="B113" s="14" t="s">
-        <v>28</v>
+        <v>231</v>
       </c>
       <c r="C113" s="14" t="s">
-        <v>313</v>
+        <v>485</v>
       </c>
       <c r="D113" s="14" t="s">
-        <v>285</v>
+        <v>504</v>
+      </c>
+      <c r="E113" s="14" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B114" s="14" t="s">
-        <v>28</v>
+        <v>231</v>
       </c>
       <c r="C114" s="14" t="s">
-        <v>278</v>
+        <v>487</v>
       </c>
       <c r="D114" s="14" t="s">
-        <v>477</v>
+        <v>505</v>
       </c>
       <c r="E114" s="14" t="s">
-        <v>293</v>
+        <v>449</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="14" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="B115" s="14" t="s">
         <v>28</v>
       </c>
       <c r="C115" s="14" t="s">
-        <v>280</v>
+        <v>338</v>
       </c>
       <c r="D115" s="14" t="s">
-        <v>478</v>
-      </c>
-      <c r="E115" s="14" t="s">
-        <v>293</v>
+        <v>310</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B116" s="14" t="s">
         <v>28</v>
       </c>
       <c r="C116" s="14" t="s">
-        <v>282</v>
+        <v>303</v>
       </c>
       <c r="D116" s="14" t="s">
-        <v>479</v>
+        <v>506</v>
       </c>
       <c r="E116" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B117" s="14" t="s">
         <v>28</v>
       </c>
       <c r="C117" s="14" t="s">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="D117" s="14" t="s">
-        <v>480</v>
+        <v>507</v>
       </c>
       <c r="E117" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B118" s="14" t="s">
         <v>28</v>
       </c>
       <c r="C118" s="14" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="D118" s="14" t="s">
-        <v>481</v>
+        <v>508</v>
       </c>
       <c r="E118" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B119" s="14" t="s">
         <v>28</v>
       </c>
       <c r="C119" s="14" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="D119" s="14" t="s">
-        <v>482</v>
+        <v>509</v>
       </c>
       <c r="E119" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B120" s="14" t="s">
         <v>28</v>
       </c>
       <c r="C120" s="14" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="D120" s="14" t="s">
-        <v>483</v>
+        <v>510</v>
       </c>
       <c r="E120" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B121" s="14" t="s">
         <v>28</v>
       </c>
       <c r="C121" s="14" t="s">
-        <v>294</v>
+        <v>313</v>
       </c>
       <c r="D121" s="14" t="s">
-        <v>484</v>
+        <v>511</v>
       </c>
       <c r="E121" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B122" s="14" t="s">
         <v>28</v>
       </c>
       <c r="C122" s="14" t="s">
-        <v>296</v>
+        <v>316</v>
       </c>
       <c r="D122" s="14" t="s">
-        <v>485</v>
+        <v>512</v>
       </c>
       <c r="E122" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B123" s="14" t="s">
         <v>28</v>
       </c>
       <c r="C123" s="14" t="s">
-        <v>299</v>
+        <v>319</v>
       </c>
       <c r="D123" s="14" t="s">
-        <v>486</v>
+        <v>513</v>
       </c>
       <c r="E123" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B124" s="14" t="s">
         <v>28</v>
       </c>
       <c r="C124" s="14" t="s">
-        <v>301</v>
+        <v>321</v>
       </c>
       <c r="D124" s="14" t="s">
-        <v>487</v>
+        <v>514</v>
       </c>
       <c r="E124" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B125" s="14" t="s">
         <v>28</v>
       </c>
       <c r="C125" s="14" t="s">
-        <v>436</v>
+        <v>324</v>
       </c>
       <c r="D125" s="14" t="s">
-        <v>488</v>
+        <v>515</v>
       </c>
       <c r="E125" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B126" s="14" t="s">
         <v>28</v>
       </c>
       <c r="C126" s="14" t="s">
-        <v>362</v>
+        <v>326</v>
       </c>
       <c r="D126" s="14" t="s">
-        <v>489</v>
+        <v>516</v>
       </c>
       <c r="E126" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B127" s="14" t="s">
         <v>28</v>
       </c>
       <c r="C127" s="14" t="s">
-        <v>364</v>
+        <v>463</v>
       </c>
       <c r="D127" s="14" t="s">
-        <v>490</v>
+        <v>517</v>
       </c>
       <c r="E127" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B128" s="14" t="s">
         <v>28</v>
       </c>
       <c r="C128" s="14" t="s">
-        <v>491</v>
+        <v>388</v>
       </c>
       <c r="D128" s="14" t="s">
-        <v>492</v>
+        <v>518</v>
       </c>
       <c r="E128" s="14" t="s">
-        <v>361</v>
+        <v>318</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="14" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B129" s="14" t="s">
         <v>28</v>
       </c>
       <c r="C129" s="14" t="s">
-        <v>458</v>
+        <v>390</v>
       </c>
       <c r="D129" s="14" t="s">
-        <v>493</v>
+        <v>519</v>
       </c>
       <c r="E129" s="14" t="s">
-        <v>293</v>
+        <v>318</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="14" t="s">
+        <v>339</v>
+      </c>
+      <c r="B130" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C130" s="14" t="s">
+        <v>520</v>
+      </c>
+      <c r="D130" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="E130" s="14" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="B131" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C131" s="14" t="s">
+        <v>485</v>
+      </c>
+      <c r="D131" s="14" t="s">
+        <v>522</v>
+      </c>
+      <c r="E131" s="14" t="s">
+        <v>318</v>
       </c>
     </row>
   </sheetData>

--- a/Ulshoefer-Preisliste-Angebotsrechner.xlsx
+++ b/Ulshoefer-Preisliste-Angebotsrechner.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1639" uniqueCount="564">
   <si>
     <t xml:space="preserve">Preisliste für den Online-Angebotsrechner</t>
   </si>
@@ -255,151 +255,259 @@
     <t xml:space="preserve">A++</t>
   </si>
   <si>
+    <t xml:space="preserve">R32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://data.toshiba-klima.at/de/Seiya%20NEW%20-%202%2C50%20kW%20-%20R32%20-%20SET120%20-%20Home%20RAS-B10E2KVG-E%20-%20RAS-10E2AVG-E%20de.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seiya RAS-B13E2KVG-E / RAS-13E2AVG-E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://data.toshiba-klima.at/de/Seiya%20NEW%20-%203%2C30%20kW%20-%20R32%20-%20SET120%20-%20Home%20RAS-B13E2KVG-E%20-%20RAS-13E2AVG-E%20de.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seiya RAS-B16E2KVG-E / RAS-16E2AVG-E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://data.toshiba-klima.at/de/Seiya%20NEW%20-%204%2C20%20kW%20-%20R32%20-%20SET120%20-%20Home%20RAS-B16E2KVG-E%20-%20RAS-16E2AVG-E%20de.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seiya RAS-B18E2KVG-E / RAS-18E2AVG-E</t>
+  </si>
+  <si>
     <t xml:space="preserve">A+</t>
   </si>
   <si>
-    <t xml:space="preserve">R32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seiya RAS-B13E2KVG-E / RAS-13E2AVG-E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seiya RAS-B16E2KVG-E / RAS-16E2AVG-E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seiya RAS-B18E2KVG-E / RAS-18E2AVG-E</t>
+    <t xml:space="preserve">https://data.toshiba-klima.at/de/Seiya%20NEW%20-%205%2C00%20kW%20-%20R32%20-%20SET120%20-%20Home%20RAS-B18E2KVG-E%20-%20RAS-18E2AVG-E%20de.pdf</t>
   </si>
   <si>
     <t xml:space="preserve">Seiya RAS-B24E2KVG-E / RAS-24E2AVG-E</t>
   </si>
   <si>
-    <t xml:space="preserve">Shorai Curve RAS-B10P2KVSG-E</t>
+    <t xml:space="preserve">https://data.toshiba-klima.at/de/Seiya%20NEW%20-%206%2C50%20kW%20-%20R32%20-%20SET120%20-%20Home%20RAS-B24E2KVG-E%20-%20RAS-24E2AVG-E%20de.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shorai Curve RAS-B10P2KVSG-E / RAS-10P2AVSG-E</t>
   </si>
   <si>
     <t xml:space="preserve">Premium</t>
   </si>
   <si>
-    <t xml:space="preserve">Shorai Curve RAS-B13P2KVSG-E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shorai Curve RAS-B16P2KVSG-E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shorai Curve RAS-B18P2KVSG-E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daisekai 10 RAS-B13S4KVPG-E</t>
-  </si>
-  <si>
     <t xml:space="preserve">A+++</t>
   </si>
   <si>
+    <t xml:space="preserve">https://data.toshiba-klima.at/de/SHORAI%20CURVE%20WHITE%20-%202%2C50%20kW%20-%20R32%20-%20SET160%20-%20Home%20RAS-B10P2KVSG-E%20-%20RAS-10P2AVSG-E%20de.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shorai Curve RAS-B13P2KVSG-E / RAS-13P2AVSG-E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://data.toshiba-klima.at/de/SHORAI%20CURVE%20WHITE%20-%203%2C50%20kW%20-%20R32%20-%20SET160%20-%20Home%20RAS-B13P2KVSG-E%20-%20RAS-13P2AVSG-E%20de.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shorai Curve RAS-B16P2KVSG-E / RAS-16P2AVSG-E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://data.toshiba-klima.at/de/SHORAI%20CURVE%20WHITE%20-%204%2C60%20kW%20-%20R32%20-%20SET160%20-%20Home%20RAS-B16P2KVSG-E%20-%20RAS-16P2AVSG-E%20de.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shorai Curve RAS-B18P2KVSG-E / RAS-18P2AVSG-E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://data.toshiba-klima.at/de/SHORAI%20CURVE%20WHITE%20-%205%2C00%20kW%20-%20R32%20-%20SET160%20-%20Home%20RAS-B18P2KVSG-E%20-%20RAS-18P2AVSG-E%20de.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shorai Curve RAS-B22P2KVSG-E / RAS-22P2AVSG-E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://data.toshiba-klima.at/de/SHORAI%20CURVE%20WHITE%20-%206%2C10%20kW%20-%20R32%20-%20SET160%20-%20Home%20RAS-B22P2KVSG-E%20-%20RAS-22P2AVSG-E%20de.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shorai Curve RAS-B24P2KVSG-E / RAS-24P2AVSG-E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://data.toshiba-klima.at/de/SHORAI%20CURVE%20WHITE%20-%207%2C00%20kW%20-%20R32%20-%20SET160%20-%20Home%20RAS-B24P2KVSG-E%20-%20RAS-24P2AVSG-E%20de.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daiseikai 10 RAS-B10S4KVPG-E / RAS-10S4AVPG-E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://data.toshiba-klima.at/de/Daiseikai%2010%20-%20WHITE%20-%202%2C50%20kW%20-%20R32%20-%20SET145%20-%20Home%20RAS-B10S4KVPG-E%20-%20RAS-10S4AVPG-E%20de.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daiseikai 10 RAS-B13S4KVPG-E / RAS-13S4AVPG-E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://data.toshiba-klima.at/de/Daiseikai%2010%20-%20WHITE%20-%203%2C50%20kW%20-%20R32%20-%20SET145%20-%20Home%20RAS-B13S4KVPG-E%20-%20RAS-13S4AVPG-E%20de.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daiseikai 10 RAS-B18S4KVPG-E / RAS-18S4AVPG-E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://data.toshiba-klima.at/de/Daiseikai%2010%20-%20WHITE%20-%205%2C00%20kW%20-%20R32%20-%20SET145%20-%20Home%20RAS-B18S4KVPG-E%20-%20RAS-18S4AVPG-E%20de.pdf</t>
+  </si>
+  <si>
     <t xml:space="preserve">Daikin</t>
   </si>
   <si>
-    <t xml:space="preserve">Sensira FTXF25D / RXF25D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sensira FTXF35D / RXF35D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sensira FTXF50D / RXF50D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perfera FTXM25R / RXM25R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perfera FTXM35R / RXM35R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perfera FTXM50R / RXM50R</t>
+    <t xml:space="preserve">Comfora FTXP25N / RXP25N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.daikin.de/de_de/produkte/product.table.html/FTXP-N9---RXP-N9.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comfora FTXP35N / RXP35N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comfora FTXP50N / RXP50N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.daikin.de/de_de/produkte/product.table.html/FTXP-N9---RXP-N8.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perfera FTXM25A / RXM25A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.daikin.de/de_de/produkte/product.table.html/FTXM-A---RXM-A9.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perfera FTXM35A / RXM35A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perfera FTXM50A / RXM50A</t>
   </si>
   <si>
     <t xml:space="preserve">Mitsubishi Electric</t>
   </si>
   <si>
-    <t xml:space="preserve">MSZ-AY25VGK / MUZ-AY25VG</t>
+    <t xml:space="preserve">MSZ-AY25VGKP / MUZ-AY25VG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.mitsubishi-les.com/de-de/dam-upload/daswandgeraetmszaybroschuere.pdf?rev=346288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSZ-AY35VGKP / MUZ-AY35VG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSZ-AY42VGKP / MUZ-AY42VG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MSZ-AY50VGKP / MUZ-AY50VG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freie gelbe Zeilen: hier neue Einträge eintragen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-Split-Innengeräte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energieklasse und Energielabel gelten für die Kombination – sie werden beim Außengerät eingetragen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seiya RAS-B10E2KVG-E (Multi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seiya RAS-B13E2KVG-E (Multi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seiya RAS-B16E2KVG-E (Multi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shorai Curve RAS-M05P2KVSG-E (Multi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://data.toshiba-klima.at/de/SHORAI%20CURVE%20WHITE%20-%201%2C50%20kW%20-%20R32%20-%20Home%20RAS-M05P2KVSG-E%20de.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shorai Curve RAS-B10P2KVSG-E (Multi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shorai Curve RAS-B13P2KVSG-E (Multi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shorai Curve RAS-B16P2KVSG-E (Multi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comfora FTXP25N (Multi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.daikin.de/de_de/produkte/product.table.html/FTXP-N9.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comfora FTXP35N (Multi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comfora FTXP50N (Multi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perfera FTXM20A (Multi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.daikin.de/de_de/produkte/product.table.html/FTXM-A.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perfera FTXM25A (Multi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perfera FTXM35A (Multi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perfera FTXM42A (Multi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perfera FTXM50A (Multi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-Split-Außengeräte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anschlüsse (Stk.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAS-2M14G3AVG-E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://data.toshiba-klima.at/de/Multisplit%20Next%20R32%20-%204%2C00%20kW%20-%20R32%20-%20Home%20RAS-2M14G3AVG-E%20de.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAS-2M18G3AVG-E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://data.toshiba-klima.at/de/Multisplit%20Next%20R32%20-%205%2C20%20kW%20-%20R32%20-%20Home%20RAS-2M18G3AVG-E%20de.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAS-3M18G3AVG-E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://data.toshiba-klima.at/de/Multisplit%20Next%20R32%20-%205%2C20%20kW%20-%20R32%20-%20Home%20RAS-3M18G3AVG-E%20de.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAS-3M26G3AVG-E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://data.toshiba-klima.at/de/Multisplit%20Next%20R32%20-%207%2C00%20kW%20-%20R32%20-%20Home%20RAS-3M26G3AVG-E%20de.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAS-4M27G3AVG-E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://data.toshiba-klima.at/de/Multisplit%20Next%20R32%20-%208%2C00%20kW%20-%20R32%20-%20Home%20RAS-4M27G3AVG-E%20de.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAS-5M34G3AVG-E1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://data.toshiba-klima.at/de/Multisplit%20Next%20R32%20-%2010%2C00%20kW%20-%20R32%20-%20Home%20RAS-5M34G3AVG-E1%20de.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2MXM40A</t>
   </si>
   <si>
     <t xml:space="preserve">–</t>
   </si>
   <si>
-    <t xml:space="preserve">MSZ-AY35VGK / MUZ-AY35VG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSZ-AY50VGK / MUZ-AY50VG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MSZ-AY71VGK / MUZ-AY71VG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freie gelbe Zeilen: hier neue Einträge eintragen.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multi-Split-Innengeräte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energieklasse und Energielabel gelten für die Kombination – sie werden beim Außengerät eingetragen.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seiya RAS-B10E2KVG-E (Multi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seiya RAS-B13E2KVG-E (Multi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seiya RAS-B16E2KVG-E (Multi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shorai Curve RAS-B10P2KVSG-E (Multi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shorai Curve RAS-B13P2KVSG-E (Multi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shorai Curve RAS-B16P2KVSG-E (Multi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perfera FTXM20R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perfera FTXM25R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perfera FTXM35R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perfera FTXM50R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sensira FTXF25D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sensira FTXF35D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sensira FTXF50D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multi-Split-Außengeräte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anschlüsse (Stk.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAS-2M14G3AVG-E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAS-3M18G3AVG-E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAS-3M26G3AVG-E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAS-4M27G3AVG-E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAS-5M34G3AVG-E</t>
+    <t xml:space="preserve">https://www.daikin.de/de_de/produkte/product.table.html/2MXM-A9.html</t>
   </si>
   <si>
     <t xml:space="preserve">2MXM50A</t>
@@ -408,12 +516,27 @@
     <t xml:space="preserve">3MXM52A</t>
   </si>
   <si>
-    <t xml:space="preserve">4MXM68A</t>
+    <t xml:space="preserve">https://www.daikin.de/de_de/produkte/product.table.html/FTXM-A---3MXM-A9.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3MXM68A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.daikin.de/de_de/produkte/product.table.html/3MXM-A9.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4MXM80A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.daikin.de/de_de/produkte/product.table.html/4MXM-A9.html</t>
   </si>
   <si>
     <t xml:space="preserve">5MXM90A</t>
   </si>
   <si>
+    <t xml:space="preserve">https://www.daikin.de/de_de/produkte/product.table.html/5MXM-A9.html</t>
+  </si>
+  <si>
     <t xml:space="preserve">Arbeitszeit (Stunden)</t>
   </si>
   <si>
@@ -1050,7 +1173,7 @@
     <t xml:space="preserve">T</t>
   </si>
   <si>
-    <t xml:space="preserve">9:33</t>
+    <t xml:space="preserve">9:37</t>
   </si>
   <si>
     <t xml:space="preserve">klima.geraete_single</t>
@@ -1059,7 +1182,7 @@
     <t xml:space="preserve">aktiv|bool,hersteller|text,modell|text,kw|num,klasse|sel|std=Standard;pre=Premium,preis|num,ek_kuehl|sel|=–;A+++=A+++;A++=A++;A+=A+;A=A;B=B;C=C;D=D,ek_heiz|sel|=–;A+++=A+++;A++=A++;A+=A+;A=A;B=B;C=C;D=D,seer|num,scop|num,schall|num,kaeltemittel|text,label|text,datenblatt|text</t>
   </si>
   <si>
-    <t xml:space="preserve">39:56</t>
+    <t xml:space="preserve">43:62</t>
   </si>
   <si>
     <t xml:space="preserve">klima.innengeraete_multi</t>
@@ -1068,7 +1191,7 @@
     <t xml:space="preserve">aktiv|bool,hersteller|text,modell|text,kw|num,klasse|sel|std=Standard;pre=Premium,preis|num,schall|num,kaeltemittel|text,datenblatt|text</t>
   </si>
   <si>
-    <t xml:space="preserve">61:74</t>
+    <t xml:space="preserve">67:83</t>
   </si>
   <si>
     <t xml:space="preserve">klima.aussengeraete_multi</t>
@@ -1077,109 +1200,109 @@
     <t xml:space="preserve">aktiv|bool,hersteller|text,modell|text,anschluesse|num,kw|num,preis|num,ek_kuehl|sel|=–;A+++=A+++;A++=A++;A+=A+;A=A;B=B;C=C;D=D,ek_heiz|sel|=–;A+++=A+++;A++=A++;A+=A+;A=A;B=B;C=C;D=D,seer|num,scop|num,kaeltemittel|text,label|text,datenblatt|text</t>
   </si>
   <si>
-    <t xml:space="preserve">B79</t>
+    <t xml:space="preserve">B88</t>
   </si>
   <si>
     <t xml:space="preserve">klima.arbeit.single_h</t>
   </si>
   <si>
-    <t xml:space="preserve">B80</t>
+    <t xml:space="preserve">B89</t>
   </si>
   <si>
     <t xml:space="preserve">klima.arbeit.multi_basis_h</t>
   </si>
   <si>
-    <t xml:space="preserve">B81</t>
+    <t xml:space="preserve">B90</t>
   </si>
   <si>
     <t xml:space="preserve">klima.arbeit.multi_je_innen_h</t>
   </si>
   <si>
-    <t xml:space="preserve">B82</t>
+    <t xml:space="preserve">B91</t>
   </si>
   <si>
     <t xml:space="preserve">klima.arbeit.leitung_m_h</t>
   </si>
   <si>
-    <t xml:space="preserve">B83</t>
+    <t xml:space="preserve">B92</t>
   </si>
   <si>
     <t xml:space="preserve">klima.arbeit.kernbohrung_h</t>
   </si>
   <si>
-    <t xml:space="preserve">B84</t>
+    <t xml:space="preserve">B93</t>
   </si>
   <si>
     <t xml:space="preserve">klima.arbeit.pumpe_h</t>
   </si>
   <si>
-    <t xml:space="preserve">B85</t>
+    <t xml:space="preserve">B94</t>
   </si>
   <si>
     <t xml:space="preserve">klima.arbeit.stromkreis_h</t>
   </si>
   <si>
-    <t xml:space="preserve">B86</t>
+    <t xml:space="preserve">B95</t>
   </si>
   <si>
     <t xml:space="preserve">klima.arbeit.konsole_h</t>
   </si>
   <si>
-    <t xml:space="preserve">B90</t>
+    <t xml:space="preserve">B99</t>
   </si>
   <si>
     <t xml:space="preserve">klima.material.grund_single</t>
   </si>
   <si>
-    <t xml:space="preserve">B91</t>
+    <t xml:space="preserve">B100</t>
   </si>
   <si>
     <t xml:space="preserve">klima.material.grund_je_innen</t>
   </si>
   <si>
-    <t xml:space="preserve">B92</t>
+    <t xml:space="preserve">B101</t>
   </si>
   <si>
     <t xml:space="preserve">klima.material.leitung_m</t>
   </si>
   <si>
-    <t xml:space="preserve">B93</t>
+    <t xml:space="preserve">B102</t>
   </si>
   <si>
     <t xml:space="preserve">klima.material.bodenkonsole</t>
   </si>
   <si>
-    <t xml:space="preserve">B94</t>
+    <t xml:space="preserve">B103</t>
   </si>
   <si>
     <t xml:space="preserve">klima.material.dachgestell</t>
   </si>
   <si>
-    <t xml:space="preserve">B95</t>
+    <t xml:space="preserve">B104</t>
   </si>
   <si>
     <t xml:space="preserve">klima.material.kernbohrung</t>
   </si>
   <si>
-    <t xml:space="preserve">B96</t>
+    <t xml:space="preserve">B105</t>
   </si>
   <si>
     <t xml:space="preserve">klima.material.pumpe</t>
   </si>
   <si>
-    <t xml:space="preserve">B97</t>
+    <t xml:space="preserve">B106</t>
   </si>
   <si>
     <t xml:space="preserve">klima.material.stromkreis</t>
   </si>
   <si>
-    <t xml:space="preserve">B101</t>
+    <t xml:space="preserve">B110</t>
   </si>
   <si>
     <t xml:space="preserve">klima.wartung_jahr</t>
   </si>
   <si>
-    <t xml:space="preserve">B102</t>
+    <t xml:space="preserve">B111</t>
   </si>
   <si>
     <t xml:space="preserve">klima.kw_je_m2</t>
@@ -2397,7 +2520,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O102"/>
+  <dimension ref="A1:O111"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -2505,22 +2628,24 @@
         <v>74</v>
       </c>
       <c r="H9" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I9" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J9" s="12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K9" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="L9" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="12" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J9" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K9" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="L9" s="5" t="s">
+      <c r="M9" s="5"/>
+      <c r="N9" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
       <c r="O9" s="6" t="n">
         <f aca="false">IF(F9="","",F9*(1+Allgemein!$B$19))</f>
         <v>1178.1</v>
@@ -2549,22 +2674,24 @@
         <v>74</v>
       </c>
       <c r="H10" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I10" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J10" s="12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K10" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="L10" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I10" s="12" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J10" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K10" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>76</v>
-      </c>
       <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
+      <c r="N10" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="O10" s="6" t="n">
         <f aca="false">IF(F10="","",F10*(1+Allgemein!$B$19))</f>
         <v>1332.8</v>
@@ -2578,7 +2705,7 @@
         <v>71</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D11" s="12" t="n">
         <v>4.2</v>
@@ -2593,22 +2720,24 @@
         <v>74</v>
       </c>
       <c r="H11" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I11" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J11" s="12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K11" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="L11" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I11" s="12" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J11" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="L11" s="5" t="s">
-        <v>76</v>
-      </c>
       <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
+      <c r="N11" s="5" t="s">
+        <v>80</v>
+      </c>
       <c r="O11" s="6" t="n">
         <f aca="false">IF(F11="","",F11*(1+Allgemein!$B$19))</f>
         <v>1654.1</v>
@@ -2622,7 +2751,7 @@
         <v>71</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D12" s="12" t="n">
         <v>5</v>
@@ -2637,22 +2766,24 @@
         <v>74</v>
       </c>
       <c r="H12" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J12" s="12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K12" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="L12" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I12" s="12" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="J12" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K12" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="L12" s="5" t="s">
-        <v>76</v>
-      </c>
       <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
+      <c r="N12" s="5" t="s">
+        <v>83</v>
+      </c>
       <c r="O12" s="6" t="n">
         <f aca="false">IF(F12="","",F12*(1+Allgemein!$B$19))</f>
         <v>1892.1</v>
@@ -2666,7 +2797,7 @@
         <v>71</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D13" s="12" t="n">
         <v>6.5</v>
@@ -2681,22 +2812,24 @@
         <v>74</v>
       </c>
       <c r="H13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="I13" s="12" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J13" s="12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K13" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="L13" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I13" s="12" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J13" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K13" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="L13" s="5" t="s">
-        <v>76</v>
-      </c>
       <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
+      <c r="N13" s="5" t="s">
+        <v>85</v>
+      </c>
       <c r="O13" s="6" t="n">
         <f aca="false">IF(F13="","",F13*(1+Allgemein!$B$19))</f>
         <v>2487.1</v>
@@ -2710,37 +2843,39 @@
         <v>71</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D14" s="12" t="n">
         <v>2.5</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>1390</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="H14" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="I14" s="12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J14" s="12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K14" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="L14" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I14" s="12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J14" s="12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K14" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="L14" s="5" t="s">
-        <v>76</v>
-      </c>
       <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
+      <c r="N14" s="5" t="s">
+        <v>89</v>
+      </c>
       <c r="O14" s="6" t="n">
         <f aca="false">IF(F14="","",F14*(1+Allgemein!$B$19))</f>
         <v>1654.1</v>
@@ -2754,37 +2889,39 @@
         <v>71</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D15" s="12" t="n">
         <v>3.5</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>1550</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="H15" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="I15" s="12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J15" s="12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K15" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="L15" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I15" s="12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J15" s="12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K15" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="L15" s="5" t="s">
-        <v>76</v>
-      </c>
       <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
+      <c r="N15" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="O15" s="6" t="n">
         <f aca="false">IF(F15="","",F15*(1+Allgemein!$B$19))</f>
         <v>1844.5</v>
@@ -2798,13 +2935,13 @@
         <v>71</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D16" s="12" t="n">
         <v>4.6</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>1790</v>
@@ -2813,22 +2950,24 @@
         <v>74</v>
       </c>
       <c r="H16" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J16" s="12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K16" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="L16" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I16" s="12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J16" s="12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K16" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="L16" s="5" t="s">
-        <v>76</v>
-      </c>
       <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
+      <c r="N16" s="5" t="s">
+        <v>93</v>
+      </c>
       <c r="O16" s="6" t="n">
         <f aca="false">IF(F16="","",F16*(1+Allgemein!$B$19))</f>
         <v>2130.1</v>
@@ -2842,13 +2981,13 @@
         <v>71</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D17" s="12" t="n">
         <v>5</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>1990</v>
@@ -2857,22 +2996,24 @@
         <v>74</v>
       </c>
       <c r="H17" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="I17" s="12" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J17" s="12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K17" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="L17" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I17" s="12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J17" s="12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K17" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="L17" s="5" t="s">
-        <v>76</v>
-      </c>
       <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
+      <c r="N17" s="5" t="s">
+        <v>95</v>
+      </c>
       <c r="O17" s="6" t="n">
         <f aca="false">IF(F17="","",F17*(1+Allgemein!$B$19))</f>
         <v>2368.1</v>
@@ -2886,40 +3027,42 @@
         <v>71</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>3.5</v>
+        <v>6.1</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>2390</v>
+        <v>2290</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>10.5</v>
+        <v>7.3</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="L18" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
+      <c r="N18" s="5" t="s">
+        <v>97</v>
+      </c>
       <c r="O18" s="6" t="n">
         <f aca="false">IF(F18="","",F18*(1+Allgemein!$B$19))</f>
-        <v>2844.1</v>
+        <v>2725.1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2927,43 +3070,45 @@
         <v>24</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1090</v>
+        <v>2490</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>74</v>
       </c>
       <c r="H19" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="I19" s="12" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="J19" s="12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K19" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="L19" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I19" s="12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J19" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K19" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="L19" s="5" t="s">
-        <v>76</v>
-      </c>
       <c r="M19" s="5"/>
-      <c r="N19" s="5"/>
+      <c r="N19" s="5" t="s">
+        <v>99</v>
+      </c>
       <c r="O19" s="6" t="n">
         <f aca="false">IF(F19="","",F19*(1+Allgemein!$B$19))</f>
-        <v>1297.1</v>
+        <v>2963.1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2971,43 +3116,45 @@
         <v>24</v>
       </c>
       <c r="B20" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20" s="12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>2190</v>
+      </c>
+      <c r="G20" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D20" s="12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="F20" s="9" t="n">
-        <v>1240</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>74</v>
-      </c>
       <c r="H20" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="I20" s="12" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J20" s="12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K20" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="L20" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I20" s="12" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="J20" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K20" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="L20" s="5" t="s">
-        <v>76</v>
-      </c>
       <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
+      <c r="N20" s="5" t="s">
+        <v>101</v>
+      </c>
       <c r="O20" s="6" t="n">
         <f aca="false">IF(F20="","",F20*(1+Allgemein!$B$19))</f>
-        <v>1475.6</v>
+        <v>2606.1</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3015,43 +3162,45 @@
         <v>24</v>
       </c>
       <c r="B21" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>2390</v>
+      </c>
+      <c r="G21" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="D21" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="F21" s="9" t="n">
-        <v>1690</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>74</v>
-      </c>
       <c r="H21" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="I21" s="12" t="n">
+        <v>9.7</v>
+      </c>
+      <c r="J21" s="12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K21" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="L21" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I21" s="12" t="n">
-        <v>6.21</v>
-      </c>
-      <c r="J21" s="12" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="K21" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="L21" s="5" t="s">
-        <v>76</v>
-      </c>
       <c r="M21" s="5"/>
-      <c r="N21" s="5"/>
+      <c r="N21" s="5" t="s">
+        <v>103</v>
+      </c>
       <c r="O21" s="6" t="n">
         <f aca="false">IF(F21="","",F21*(1+Allgemein!$B$19))</f>
-        <v>2011.1</v>
+        <v>2844.1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3059,43 +3208,45 @@
         <v>24</v>
       </c>
       <c r="B22" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="D22" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>2890</v>
+      </c>
+      <c r="G22" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="D22" s="12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="F22" s="9" t="n">
-        <v>1490</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>87</v>
-      </c>
       <c r="H22" s="5" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>8.7</v>
+        <v>8.6</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M22" s="5"/>
-      <c r="N22" s="5"/>
+      <c r="N22" s="5" t="s">
+        <v>105</v>
+      </c>
       <c r="O22" s="6" t="n">
         <f aca="false">IF(F22="","",F22*(1+Allgemein!$B$19))</f>
-        <v>1773.1</v>
+        <v>3439.1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3103,43 +3254,45 @@
         <v>24</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1690</v>
+        <v>1150</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>74</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>4.6</v>
+        <v>4.61</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>19</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M23" s="5"/>
-      <c r="N23" s="5"/>
+      <c r="N23" s="5" t="s">
+        <v>108</v>
+      </c>
       <c r="O23" s="6" t="n">
         <f aca="false">IF(F23="","",F23*(1+Allgemein!$B$19))</f>
-        <v>2011.1</v>
+        <v>1368.5</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3147,19 +3300,19 @@
         <v>24</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>2190</v>
+        <v>1290</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>74</v>
@@ -3168,22 +3321,24 @@
         <v>74</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>4.6</v>
+        <v>4.64</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="L24" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M24" s="5"/>
-      <c r="N24" s="5"/>
+      <c r="N24" s="5" t="s">
+        <v>108</v>
+      </c>
       <c r="O24" s="6" t="n">
         <f aca="false">IF(F24="","",F24*(1+Allgemein!$B$19))</f>
-        <v>2606.1</v>
+        <v>1535.1</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3191,37 +3346,45 @@
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D25" s="12" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>73</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>1150</v>
+        <v>1790</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
+        <v>82</v>
+      </c>
+      <c r="I25" s="12" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J25" s="12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K25" s="12" t="n">
+        <v>27</v>
+      </c>
       <c r="L25" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M25" s="5"/>
-      <c r="N25" s="5"/>
+      <c r="N25" s="5" t="s">
+        <v>111</v>
+      </c>
       <c r="O25" s="6" t="n">
         <f aca="false">IF(F25="","",F25*(1+Allgemein!$B$19))</f>
-        <v>1368.5</v>
+        <v>2130.1</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3229,37 +3392,45 @@
         <v>24</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>1290</v>
+        <v>1490</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="I26" s="12"/>
-      <c r="J26" s="12"/>
-      <c r="K26" s="12"/>
+        <v>88</v>
+      </c>
+      <c r="I26" s="12" t="n">
+        <v>9.47</v>
+      </c>
+      <c r="J26" s="12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K26" s="12" t="n">
+        <v>19</v>
+      </c>
       <c r="L26" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M26" s="5"/>
-      <c r="N26" s="5"/>
+      <c r="N26" s="5" t="s">
+        <v>113</v>
+      </c>
       <c r="O26" s="6" t="n">
         <f aca="false">IF(F26="","",F26*(1+Allgemein!$B$19))</f>
-        <v>1535.1</v>
+        <v>1773.1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3267,37 +3438,45 @@
         <v>24</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="D27" s="12" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>1750</v>
+        <v>1690</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
+        <v>88</v>
+      </c>
+      <c r="I27" s="12" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="J27" s="12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K27" s="12" t="n">
+        <v>19</v>
+      </c>
       <c r="L27" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M27" s="5"/>
-      <c r="N27" s="5"/>
+      <c r="N27" s="5" t="s">
+        <v>113</v>
+      </c>
       <c r="O27" s="6" t="n">
         <f aca="false">IF(F27="","",F27*(1+Allgemein!$B$19))</f>
-        <v>2082.5</v>
+        <v>2011.1</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3305,117 +3484,229 @@
         <v>24</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>7.1</v>
+        <v>5</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>2390</v>
+        <v>2190</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="I28" s="12"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="12"/>
+        <v>74</v>
+      </c>
+      <c r="I28" s="12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J28" s="12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K28" s="12" t="n">
+        <v>27</v>
+      </c>
       <c r="L28" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M28" s="5"/>
-      <c r="N28" s="5"/>
+      <c r="N28" s="5" t="s">
+        <v>113</v>
+      </c>
       <c r="O28" s="6" t="n">
         <f aca="false">IF(F28="","",F28*(1+Allgemein!$B$19))</f>
-        <v>2844.1</v>
+        <v>2606.1</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="5"/>
+      <c r="A29" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D29" s="12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>1150</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I29" s="12" t="n">
+        <v>8.7</v>
+      </c>
+      <c r="J29" s="12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K29" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="L29" s="5" t="s">
+        <v>75</v>
+      </c>
       <c r="M29" s="5"/>
-      <c r="N29" s="5"/>
-      <c r="O29" s="6" t="str">
+      <c r="N29" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="O29" s="6" t="n">
         <f aca="false">IF(F29="","",F29*(1+Allgemein!$B$19))</f>
-        <v/>
+        <v>1368.5</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="5"/>
+      <c r="A30" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D30" s="12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>1290</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I30" s="12" t="n">
+        <v>8.7</v>
+      </c>
+      <c r="J30" s="12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K30" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="L30" s="5" t="s">
+        <v>75</v>
+      </c>
       <c r="M30" s="5"/>
-      <c r="N30" s="5"/>
-      <c r="O30" s="6" t="str">
+      <c r="N30" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="O30" s="6" t="n">
         <f aca="false">IF(F30="","",F30*(1+Allgemein!$B$19))</f>
-        <v/>
+        <v>1535.1</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="5"/>
+      <c r="A31" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D31" s="12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>1490</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I31" s="12" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="J31" s="12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K31" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="L31" s="5" t="s">
+        <v>75</v>
+      </c>
       <c r="M31" s="5"/>
-      <c r="N31" s="5"/>
-      <c r="O31" s="6" t="str">
+      <c r="N31" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="O31" s="6" t="n">
         <f aca="false">IF(F31="","",F31*(1+Allgemein!$B$19))</f>
-        <v/>
+        <v>1773.1</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="5"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="12"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="5"/>
+      <c r="A32" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D32" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F32" s="9" t="n">
+        <v>1750</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I32" s="12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J32" s="12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K32" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="L32" s="5" t="s">
+        <v>75</v>
+      </c>
       <c r="M32" s="5"/>
-      <c r="N32" s="5"/>
-      <c r="O32" s="6" t="str">
+      <c r="N32" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="O32" s="6" t="n">
         <f aca="false">IF(F32="","",F32*(1+Allgemein!$B$19))</f>
-        <v/>
+        <v>2082.5</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3439,174 +3730,130 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="s">
-        <v>101</v>
+      <c r="A34" s="5"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="12"/>
+      <c r="K34" s="12"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="6" t="str">
+        <f aca="false">IF(F34="","",F34*(1+Allgemein!$B$19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="5"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="12"/>
+      <c r="K35" s="12"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="6" t="str">
+        <f aca="false">IF(F35="","",F35*(1+Allgemein!$B$19))</f>
+        <v/>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="3" t="s">
-        <v>102</v>
+      <c r="A36" s="5"/>
+      <c r="B36" s="5"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="12"/>
+      <c r="K36" s="12"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="6" t="str">
+        <f aca="false">IF(F36="","",F36*(1+Allgemein!$B$19))</f>
+        <v/>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="7" t="s">
+      <c r="A37" s="5"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="12"/>
+      <c r="K37" s="12"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="6" t="str">
+        <f aca="false">IF(F37="","",F37*(1+Allgemein!$B$19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="B42" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C42" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D38" s="7" t="s">
+      <c r="D42" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E38" s="7" t="s">
+      <c r="E42" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="F38" s="7" t="s">
+      <c r="F42" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="G38" s="7" t="s">
+      <c r="G42" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="H38" s="7" t="s">
+      <c r="H42" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="I38" s="7" t="s">
+      <c r="I42" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="J38" s="7" t="s">
+      <c r="J42" s="7" t="s">
         <v>70</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="D39" s="12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="F39" s="9" t="n">
-        <v>420</v>
-      </c>
-      <c r="G39" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="H39" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="I39" s="5"/>
-      <c r="J39" s="6" t="n">
-        <f aca="false">IF(F39="","",F39*(1+Allgemein!$B$19))</f>
-        <v>499.8</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="D40" s="12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="F40" s="9" t="n">
-        <v>470</v>
-      </c>
-      <c r="G40" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="I40" s="5"/>
-      <c r="J40" s="6" t="n">
-        <f aca="false">IF(F40="","",F40*(1+Allgemein!$B$19))</f>
-        <v>559.3</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="D41" s="12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="F41" s="9" t="n">
-        <v>560</v>
-      </c>
-      <c r="G41" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="H41" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="I41" s="5"/>
-      <c r="J41" s="6" t="n">
-        <f aca="false">IF(F41="","",F41*(1+Allgemein!$B$19))</f>
-        <v>666.4</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="D42" s="12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="F42" s="9" t="n">
-        <v>590</v>
-      </c>
-      <c r="G42" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="H42" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="I42" s="5"/>
-      <c r="J42" s="6" t="n">
-        <f aca="false">IF(F42="","",F42*(1+Allgemein!$B$19))</f>
-        <v>702.1</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3617,27 +3864,29 @@
         <v>71</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="D43" s="12" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>660</v>
+        <v>420</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H43" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I43" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="I43" s="5"/>
       <c r="J43" s="6" t="n">
         <f aca="false">IF(F43="","",F43*(1+Allgemein!$B$19))</f>
-        <v>785.4</v>
+        <v>499.8</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3648,27 +3897,29 @@
         <v>71</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>760</v>
+        <v>470</v>
       </c>
       <c r="G44" s="12" t="n">
         <v>20</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="I44" s="5"/>
+        <v>75</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="J44" s="6" t="n">
         <f aca="false">IF(F44="","",F44*(1+Allgemein!$B$19))</f>
-        <v>904.4</v>
+        <v>559.3</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3676,27 +3927,29 @@
         <v>24</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="D45" s="12" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="F45" s="9" t="n">
         <v>560</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="I45" s="5"/>
+        <v>75</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>80</v>
+      </c>
       <c r="J45" s="6" t="n">
         <f aca="false">IF(F45="","",F45*(1+Allgemein!$B$19))</f>
         <v>666.4</v>
@@ -3707,30 +3960,32 @@
         <v>24</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>600</v>
+        <v>540</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="I46" s="5"/>
+        <v>75</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>129</v>
+      </c>
       <c r="J46" s="6" t="n">
         <f aca="false">IF(F46="","",F46*(1+Allgemein!$B$19))</f>
-        <v>714</v>
+        <v>642.6</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3738,30 +3993,32 @@
         <v>24</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="D47" s="12" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>680</v>
+        <v>590</v>
       </c>
       <c r="G47" s="12" t="n">
         <v>19</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="I47" s="5"/>
+        <v>75</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>89</v>
+      </c>
       <c r="J47" s="6" t="n">
         <f aca="false">IF(F47="","",F47*(1+Allgemein!$B$19))</f>
-        <v>809.2</v>
+        <v>702.1</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3769,30 +4026,32 @@
         <v>24</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>860</v>
+        <v>660</v>
       </c>
       <c r="G48" s="12" t="n">
         <v>19</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="I48" s="5"/>
+        <v>75</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="J48" s="6" t="n">
         <f aca="false">IF(F48="","",F48*(1+Allgemein!$B$19))</f>
-        <v>1023.4</v>
+        <v>785.4</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3800,30 +4059,32 @@
         <v>24</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="D49" s="12" t="n">
-        <v>2.5</v>
+        <v>4.6</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>430</v>
+        <v>760</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="I49" s="5"/>
+        <v>75</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>93</v>
+      </c>
       <c r="J49" s="6" t="n">
         <f aca="false">IF(F49="","",F49*(1+Allgemein!$B$19))</f>
-        <v>511.7</v>
+        <v>904.4</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3831,30 +4092,32 @@
         <v>24</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>73</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>490</v>
+        <v>470</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="I50" s="5"/>
+        <v>75</v>
+      </c>
+      <c r="I50" s="5" t="s">
+        <v>134</v>
+      </c>
       <c r="J50" s="6" t="n">
         <f aca="false">IF(F50="","",F50*(1+Allgemein!$B$19))</f>
-        <v>583.1</v>
+        <v>559.3</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3862,381 +4125,359 @@
         <v>24</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="D51" s="12" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>73</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>640</v>
+        <v>520</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="I51" s="5"/>
+        <v>75</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>134</v>
+      </c>
       <c r="J51" s="6" t="n">
         <f aca="false">IF(F51="","",F51*(1+Allgemein!$B$19))</f>
-        <v>761.6</v>
+        <v>618.8</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="5"/>
-      <c r="B52" s="5"/>
-      <c r="C52" s="5"/>
-      <c r="D52" s="12"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="12"/>
-      <c r="H52" s="5"/>
-      <c r="I52" s="5"/>
-      <c r="J52" s="6" t="str">
+      <c r="A52" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D52" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F52" s="9" t="n">
+        <v>680</v>
+      </c>
+      <c r="G52" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="H52" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="J52" s="6" t="n">
         <f aca="false">IF(F52="","",F52*(1+Allgemein!$B$19))</f>
+        <v>809.2</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="D53" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F53" s="9" t="n">
+        <v>560</v>
+      </c>
+      <c r="G53" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="H53" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="J53" s="6" t="n">
+        <f aca="false">IF(F53="","",F53*(1+Allgemein!$B$19))</f>
+        <v>666.4</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D54" s="12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F54" s="9" t="n">
+        <v>600</v>
+      </c>
+      <c r="G54" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="J54" s="6" t="n">
+        <f aca="false">IF(F54="","",F54*(1+Allgemein!$B$19))</f>
+        <v>714</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D55" s="12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F55" s="9" t="n">
+        <v>680</v>
+      </c>
+      <c r="G55" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="H55" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I55" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="J55" s="6" t="n">
+        <f aca="false">IF(F55="","",F55*(1+Allgemein!$B$19))</f>
+        <v>809.2</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D56" s="12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F56" s="9" t="n">
+        <v>760</v>
+      </c>
+      <c r="G56" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="H56" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I56" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="J56" s="6" t="n">
+        <f aca="false">IF(F56="","",F56*(1+Allgemein!$B$19))</f>
+        <v>904.4</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D57" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F57" s="9" t="n">
+        <v>860</v>
+      </c>
+      <c r="G57" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="H57" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="J57" s="6" t="n">
+        <f aca="false">IF(F57="","",F57*(1+Allgemein!$B$19))</f>
+        <v>1023.4</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="5"/>
+      <c r="B58" s="5"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="12"/>
+      <c r="E58" s="5"/>
+      <c r="F58" s="9"/>
+      <c r="G58" s="12"/>
+      <c r="H58" s="5"/>
+      <c r="I58" s="5"/>
+      <c r="J58" s="6" t="str">
+        <f aca="false">IF(F58="","",F58*(1+Allgemein!$B$19))</f>
         <v/>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="5"/>
-      <c r="B53" s="5"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="12"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="12"/>
-      <c r="H53" s="5"/>
-      <c r="I53" s="5"/>
-      <c r="J53" s="6" t="str">
-        <f aca="false">IF(F53="","",F53*(1+Allgemein!$B$19))</f>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="5"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="12"/>
+      <c r="E59" s="5"/>
+      <c r="F59" s="9"/>
+      <c r="G59" s="12"/>
+      <c r="H59" s="5"/>
+      <c r="I59" s="5"/>
+      <c r="J59" s="6" t="str">
+        <f aca="false">IF(F59="","",F59*(1+Allgemein!$B$19))</f>
         <v/>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="5"/>
-      <c r="B54" s="5"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="12"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="5"/>
-      <c r="I54" s="5"/>
-      <c r="J54" s="6" t="str">
-        <f aca="false">IF(F54="","",F54*(1+Allgemein!$B$19))</f>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="5"/>
+      <c r="B60" s="5"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="12"/>
+      <c r="E60" s="5"/>
+      <c r="F60" s="9"/>
+      <c r="G60" s="12"/>
+      <c r="H60" s="5"/>
+      <c r="I60" s="5"/>
+      <c r="J60" s="6" t="str">
+        <f aca="false">IF(F60="","",F60*(1+Allgemein!$B$19))</f>
         <v/>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="5"/>
-      <c r="B55" s="5"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="12"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="5"/>
-      <c r="I55" s="5"/>
-      <c r="J55" s="6" t="str">
-        <f aca="false">IF(F55="","",F55*(1+Allgemein!$B$19))</f>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="5"/>
+      <c r="B61" s="5"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="12"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="9"/>
+      <c r="G61" s="12"/>
+      <c r="H61" s="5"/>
+      <c r="I61" s="5"/>
+      <c r="J61" s="6" t="str">
+        <f aca="false">IF(F61="","",F61*(1+Allgemein!$B$19))</f>
         <v/>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="5"/>
-      <c r="B56" s="5"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="12"/>
-      <c r="E56" s="5"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="12"/>
-      <c r="H56" s="5"/>
-      <c r="I56" s="5"/>
-      <c r="J56" s="6" t="str">
-        <f aca="false">IF(F56="","",F56*(1+Allgemein!$B$19))</f>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="5"/>
+      <c r="B62" s="5"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="12"/>
+      <c r="E62" s="5"/>
+      <c r="F62" s="9"/>
+      <c r="G62" s="12"/>
+      <c r="H62" s="5"/>
+      <c r="I62" s="5"/>
+      <c r="J62" s="6" t="str">
+        <f aca="false">IF(F62="","",F62*(1+Allgemein!$B$19))</f>
         <v/>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="7" t="s">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B60" s="7" t="s">
+      <c r="B66" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="C66" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D60" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="E60" s="7" t="s">
+      <c r="D66" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="E66" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F60" s="7" t="s">
+      <c r="F66" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="G60" s="7" t="s">
+      <c r="G66" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="H60" s="7" t="s">
+      <c r="H66" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="I60" s="7" t="s">
+      <c r="I66" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="J60" s="7" t="s">
+      <c r="J66" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="K60" s="7" t="s">
+      <c r="K66" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="L60" s="7" t="s">
+      <c r="L66" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="M60" s="7" t="s">
+      <c r="M66" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="N60" s="7" t="s">
+      <c r="N66" s="7" t="s">
         <v>70</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="D61" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E61" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="F61" s="9" t="n">
-        <v>1590</v>
-      </c>
-      <c r="G61" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="H61" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="I61" s="12"/>
-      <c r="J61" s="12"/>
-      <c r="K61" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="L61" s="5"/>
-      <c r="M61" s="5"/>
-      <c r="N61" s="6" t="n">
-        <f aca="false">IF(F61="","",F61*(1+Allgemein!$B$19))</f>
-        <v>1892.1</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="D62" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="E62" s="12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="F62" s="9" t="n">
-        <v>1990</v>
-      </c>
-      <c r="G62" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="H62" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="I62" s="12"/>
-      <c r="J62" s="12"/>
-      <c r="K62" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="L62" s="5"/>
-      <c r="M62" s="5"/>
-      <c r="N62" s="6" t="n">
-        <f aca="false">IF(F62="","",F62*(1+Allgemein!$B$19))</f>
-        <v>2368.1</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="D63" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="E63" s="12" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F63" s="9" t="n">
-        <v>2390</v>
-      </c>
-      <c r="G63" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="H63" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="I63" s="12"/>
-      <c r="J63" s="12"/>
-      <c r="K63" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="L63" s="5"/>
-      <c r="M63" s="5"/>
-      <c r="N63" s="6" t="n">
-        <f aca="false">IF(F63="","",F63*(1+Allgemein!$B$19))</f>
-        <v>2844.1</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D64" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E64" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="F64" s="9" t="n">
-        <v>2690</v>
-      </c>
-      <c r="G64" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="H64" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="I64" s="12"/>
-      <c r="J64" s="12"/>
-      <c r="K64" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="L64" s="5"/>
-      <c r="M64" s="5"/>
-      <c r="N64" s="6" t="n">
-        <f aca="false">IF(F64="","",F64*(1+Allgemein!$B$19))</f>
-        <v>3201.1</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="D65" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="E65" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="F65" s="9" t="n">
-        <v>3190</v>
-      </c>
-      <c r="G65" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="H65" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="I65" s="12"/>
-      <c r="J65" s="12"/>
-      <c r="K65" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="L65" s="5"/>
-      <c r="M65" s="5"/>
-      <c r="N65" s="6" t="n">
-        <f aca="false">IF(F65="","",F65*(1+Allgemein!$B$19))</f>
-        <v>3796.1</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D66" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E66" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="F66" s="9" t="n">
-        <v>1790</v>
-      </c>
-      <c r="G66" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="H66" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="I66" s="12"/>
-      <c r="J66" s="12"/>
-      <c r="K66" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="L66" s="5"/>
-      <c r="M66" s="5"/>
-      <c r="N66" s="6" t="n">
-        <f aca="false">IF(F66="","",F66*(1+Allgemein!$B$19))</f>
-        <v>2130.1</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4244,36 +4485,42 @@
         <v>24</v>
       </c>
       <c r="B67" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="D67" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E67" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F67" s="9" t="n">
+        <v>1590</v>
+      </c>
+      <c r="G67" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C67" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D67" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="E67" s="12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="F67" s="9" t="n">
-        <v>2190</v>
-      </c>
-      <c r="G67" s="5" t="s">
+      <c r="H67" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="H67" s="5" t="s">
+      <c r="I67" s="12" t="n">
+        <v>8.7</v>
+      </c>
+      <c r="J67" s="12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K67" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I67" s="12"/>
-      <c r="J67" s="12"/>
-      <c r="K67" s="5" t="s">
-        <v>76</v>
-      </c>
       <c r="L67" s="5"/>
-      <c r="M67" s="5"/>
+      <c r="M67" s="5" t="s">
+        <v>146</v>
+      </c>
       <c r="N67" s="6" t="n">
         <f aca="false">IF(F67="","",F67*(1+Allgemein!$B$19))</f>
-        <v>2606.1</v>
+        <v>1892.1</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4281,36 +4528,42 @@
         <v>24</v>
       </c>
       <c r="B68" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D68" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E68" s="12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F68" s="9" t="n">
+        <v>1790</v>
+      </c>
+      <c r="G68" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C68" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="D68" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E68" s="12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="F68" s="9" t="n">
-        <v>2690</v>
-      </c>
-      <c r="G68" s="5" t="s">
+      <c r="H68" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="H68" s="5" t="s">
+      <c r="I68" s="12" t="n">
+        <v>8.7</v>
+      </c>
+      <c r="J68" s="12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K68" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I68" s="12"/>
-      <c r="J68" s="12"/>
-      <c r="K68" s="5" t="s">
-        <v>76</v>
-      </c>
       <c r="L68" s="5"/>
-      <c r="M68" s="5"/>
+      <c r="M68" s="5" t="s">
+        <v>148</v>
+      </c>
       <c r="N68" s="6" t="n">
         <f aca="false">IF(F68="","",F68*(1+Allgemein!$B$19))</f>
-        <v>3201.1</v>
+        <v>2130.1</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4318,496 +4571,869 @@
         <v>24</v>
       </c>
       <c r="B69" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D69" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E69" s="12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F69" s="9" t="n">
+        <v>1990</v>
+      </c>
+      <c r="G69" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C69" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="D69" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="E69" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="F69" s="9" t="n">
-        <v>3290</v>
-      </c>
-      <c r="G69" s="5" t="s">
+      <c r="H69" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="H69" s="5" t="s">
+      <c r="I69" s="12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J69" s="12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K69" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I69" s="12"/>
-      <c r="J69" s="12"/>
-      <c r="K69" s="5" t="s">
-        <v>76</v>
-      </c>
       <c r="L69" s="5"/>
-      <c r="M69" s="5"/>
+      <c r="M69" s="5" t="s">
+        <v>150</v>
+      </c>
       <c r="N69" s="6" t="n">
         <f aca="false">IF(F69="","",F69*(1+Allgemein!$B$19))</f>
-        <v>3915.1</v>
+        <v>2368.1</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="5"/>
-      <c r="B70" s="5"/>
-      <c r="C70" s="5"/>
-      <c r="D70" s="12"/>
-      <c r="E70" s="12"/>
-      <c r="F70" s="9"/>
-      <c r="G70" s="5"/>
-      <c r="H70" s="5"/>
-      <c r="I70" s="12"/>
-      <c r="J70" s="12"/>
-      <c r="K70" s="5"/>
+      <c r="A70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D70" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E70" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="F70" s="9" t="n">
+        <v>2390</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="H70" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I70" s="12" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J70" s="12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K70" s="5" t="s">
+        <v>75</v>
+      </c>
       <c r="L70" s="5"/>
-      <c r="M70" s="5"/>
-      <c r="N70" s="6" t="str">
+      <c r="M70" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="N70" s="6" t="n">
         <f aca="false">IF(F70="","",F70*(1+Allgemein!$B$19))</f>
-        <v/>
+        <v>2844.1</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="5"/>
-      <c r="B71" s="5"/>
-      <c r="C71" s="5"/>
-      <c r="D71" s="12"/>
-      <c r="E71" s="12"/>
-      <c r="F71" s="9"/>
-      <c r="G71" s="5"/>
-      <c r="H71" s="5"/>
-      <c r="I71" s="12"/>
-      <c r="J71" s="12"/>
-      <c r="K71" s="5"/>
+      <c r="A71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="D71" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E71" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F71" s="9" t="n">
+        <v>2690</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H71" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I71" s="12" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="J71" s="12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K71" s="5" t="s">
+        <v>75</v>
+      </c>
       <c r="L71" s="5"/>
-      <c r="M71" s="5"/>
-      <c r="N71" s="6" t="str">
+      <c r="M71" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="N71" s="6" t="n">
         <f aca="false">IF(F71="","",F71*(1+Allgemein!$B$19))</f>
-        <v/>
+        <v>3201.1</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="5"/>
-      <c r="B72" s="5"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="12"/>
-      <c r="E72" s="12"/>
-      <c r="F72" s="9"/>
-      <c r="G72" s="5"/>
-      <c r="H72" s="5"/>
-      <c r="I72" s="12"/>
-      <c r="J72" s="12"/>
-      <c r="K72" s="5"/>
+      <c r="A72" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D72" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E72" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F72" s="9" t="n">
+        <v>3190</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H72" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="I72" s="12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J72" s="12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K72" s="5" t="s">
+        <v>75</v>
+      </c>
       <c r="L72" s="5"/>
-      <c r="M72" s="5"/>
-      <c r="N72" s="6" t="str">
+      <c r="M72" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="N72" s="6" t="n">
         <f aca="false">IF(F72="","",F72*(1+Allgemein!$B$19))</f>
-        <v/>
+        <v>3796.1</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="5"/>
-      <c r="B73" s="5"/>
-      <c r="C73" s="5"/>
-      <c r="D73" s="12"/>
-      <c r="E73" s="12"/>
-      <c r="F73" s="9"/>
-      <c r="G73" s="5"/>
-      <c r="H73" s="5"/>
+      <c r="A73" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="D73" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E73" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F73" s="9" t="n">
+        <v>1690</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="H73" s="5" t="s">
+        <v>158</v>
+      </c>
       <c r="I73" s="12"/>
       <c r="J73" s="12"/>
-      <c r="K73" s="5"/>
+      <c r="K73" s="5" t="s">
+        <v>75</v>
+      </c>
       <c r="L73" s="5"/>
-      <c r="M73" s="5"/>
-      <c r="N73" s="6" t="str">
+      <c r="M73" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="N73" s="6" t="n">
         <f aca="false">IF(F73="","",F73*(1+Allgemein!$B$19))</f>
-        <v/>
+        <v>2011.1</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="5"/>
-      <c r="B74" s="5"/>
-      <c r="C74" s="5"/>
-      <c r="D74" s="12"/>
-      <c r="E74" s="12"/>
-      <c r="F74" s="9"/>
-      <c r="G74" s="5"/>
-      <c r="H74" s="5"/>
+      <c r="A74" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D74" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E74" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F74" s="9" t="n">
+        <v>1790</v>
+      </c>
+      <c r="G74" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="H74" s="5" t="s">
+        <v>158</v>
+      </c>
       <c r="I74" s="12"/>
       <c r="J74" s="12"/>
-      <c r="K74" s="5"/>
+      <c r="K74" s="5" t="s">
+        <v>75</v>
+      </c>
       <c r="L74" s="5"/>
-      <c r="M74" s="5"/>
-      <c r="N74" s="6" t="str">
+      <c r="M74" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="N74" s="6" t="n">
         <f aca="false">IF(F74="","",F74*(1+Allgemein!$B$19))</f>
+        <v>2130.1</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="D75" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E75" s="12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="F75" s="9" t="n">
+        <v>2190</v>
+      </c>
+      <c r="G75" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="H75" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="I75" s="12" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="J75" s="12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K75" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L75" s="5"/>
+      <c r="M75" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="N75" s="6" t="n">
+        <f aca="false">IF(F75="","",F75*(1+Allgemein!$B$19))</f>
+        <v>2606.1</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="D76" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E76" s="12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="F76" s="9" t="n">
+        <v>2490</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="H76" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="I76" s="12"/>
+      <c r="J76" s="12"/>
+      <c r="K76" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L76" s="5"/>
+      <c r="M76" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="N76" s="6" t="n">
+        <f aca="false">IF(F76="","",F76*(1+Allgemein!$B$19))</f>
+        <v>2963.1</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D77" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E77" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F77" s="9" t="n">
+        <v>2890</v>
+      </c>
+      <c r="G77" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="H77" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="I77" s="12"/>
+      <c r="J77" s="12"/>
+      <c r="K77" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L77" s="5"/>
+      <c r="M77" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="N77" s="6" t="n">
+        <f aca="false">IF(F77="","",F77*(1+Allgemein!$B$19))</f>
+        <v>3439.1</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D78" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E78" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F78" s="9" t="n">
+        <v>3290</v>
+      </c>
+      <c r="G78" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="H78" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="I78" s="12"/>
+      <c r="J78" s="12"/>
+      <c r="K78" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L78" s="5"/>
+      <c r="M78" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="N78" s="6" t="n">
+        <f aca="false">IF(F78="","",F78*(1+Allgemein!$B$19))</f>
+        <v>3915.1</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="5"/>
+      <c r="B79" s="5"/>
+      <c r="C79" s="5"/>
+      <c r="D79" s="12"/>
+      <c r="E79" s="12"/>
+      <c r="F79" s="9"/>
+      <c r="G79" s="5"/>
+      <c r="H79" s="5"/>
+      <c r="I79" s="12"/>
+      <c r="J79" s="12"/>
+      <c r="K79" s="5"/>
+      <c r="L79" s="5"/>
+      <c r="M79" s="5"/>
+      <c r="N79" s="6" t="str">
+        <f aca="false">IF(F79="","",F79*(1+Allgemein!$B$19))</f>
         <v/>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="7" t="s">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="5"/>
+      <c r="B80" s="5"/>
+      <c r="C80" s="5"/>
+      <c r="D80" s="12"/>
+      <c r="E80" s="12"/>
+      <c r="F80" s="9"/>
+      <c r="G80" s="5"/>
+      <c r="H80" s="5"/>
+      <c r="I80" s="12"/>
+      <c r="J80" s="12"/>
+      <c r="K80" s="5"/>
+      <c r="L80" s="5"/>
+      <c r="M80" s="5"/>
+      <c r="N80" s="6" t="str">
+        <f aca="false">IF(F80="","",F80*(1+Allgemein!$B$19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="5"/>
+      <c r="B81" s="5"/>
+      <c r="C81" s="5"/>
+      <c r="D81" s="12"/>
+      <c r="E81" s="12"/>
+      <c r="F81" s="9"/>
+      <c r="G81" s="5"/>
+      <c r="H81" s="5"/>
+      <c r="I81" s="12"/>
+      <c r="J81" s="12"/>
+      <c r="K81" s="5"/>
+      <c r="L81" s="5"/>
+      <c r="M81" s="5"/>
+      <c r="N81" s="6" t="str">
+        <f aca="false">IF(F81="","",F81*(1+Allgemein!$B$19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="5"/>
+      <c r="B82" s="5"/>
+      <c r="C82" s="5"/>
+      <c r="D82" s="12"/>
+      <c r="E82" s="12"/>
+      <c r="F82" s="9"/>
+      <c r="G82" s="5"/>
+      <c r="H82" s="5"/>
+      <c r="I82" s="12"/>
+      <c r="J82" s="12"/>
+      <c r="K82" s="5"/>
+      <c r="L82" s="5"/>
+      <c r="M82" s="5"/>
+      <c r="N82" s="6" t="str">
+        <f aca="false">IF(F82="","",F82*(1+Allgemein!$B$19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="5"/>
+      <c r="B83" s="5"/>
+      <c r="C83" s="5"/>
+      <c r="D83" s="12"/>
+      <c r="E83" s="12"/>
+      <c r="F83" s="9"/>
+      <c r="G83" s="5"/>
+      <c r="H83" s="5"/>
+      <c r="I83" s="12"/>
+      <c r="J83" s="12"/>
+      <c r="K83" s="5"/>
+      <c r="L83" s="5"/>
+      <c r="M83" s="5"/>
+      <c r="N83" s="6" t="str">
+        <f aca="false">IF(F83="","",F83*(1+Allgemein!$B$19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B78" s="7" t="s">
+      <c r="B87" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C78" s="7" t="s">
+      <c r="C87" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D78" s="7" t="s">
+      <c r="D87" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E78" s="7" t="s">
+      <c r="E87" s="7" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="B79" s="12" t="n">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="B88" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="C79" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="D79" s="6" t="n">
-        <f aca="false">B79*Allgemein!$B$17</f>
+      <c r="C88" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="D88" s="6" t="n">
+        <f aca="false">B88*Allgemein!$B$17</f>
         <v>408</v>
       </c>
-      <c r="E79" s="6" t="n">
-        <f aca="false">D79*(1+Allgemein!$B$19)</f>
+      <c r="E88" s="6" t="n">
+        <f aca="false">D88*(1+Allgemein!$B$19)</f>
         <v>485.52</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="B80" s="12" t="n">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="B89" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="C80" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="D80" s="6" t="n">
-        <f aca="false">B80*Allgemein!$B$17</f>
+      <c r="C89" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="D89" s="6" t="n">
+        <f aca="false">B89*Allgemein!$B$17</f>
         <v>476</v>
       </c>
-      <c r="E80" s="6" t="n">
-        <f aca="false">D80*(1+Allgemein!$B$19)</f>
+      <c r="E89" s="6" t="n">
+        <f aca="false">D89*(1+Allgemein!$B$19)</f>
         <v>566.44</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="B81" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="C81" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="D81" s="6" t="n">
-        <f aca="false">B81*Allgemein!$B$17</f>
-        <v>272</v>
-      </c>
-      <c r="E81" s="6" t="n">
-        <f aca="false">D81*(1+Allgemein!$B$19)</f>
-        <v>323.68</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="B82" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C82" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="D82" s="6" t="n">
-        <f aca="false">B82*Allgemein!$B$17</f>
-        <v>17</v>
-      </c>
-      <c r="E82" s="6" t="n">
-        <f aca="false">D82*(1+Allgemein!$B$19)</f>
-        <v>20.23</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="B83" s="12" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="C83" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="D83" s="6" t="n">
-        <f aca="false">B83*Allgemein!$B$17</f>
-        <v>51</v>
-      </c>
-      <c r="E83" s="6" t="n">
-        <f aca="false">D83*(1+Allgemein!$B$19)</f>
-        <v>60.69</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="B84" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C84" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="D84" s="6" t="n">
-        <f aca="false">B84*Allgemein!$B$17</f>
-        <v>34</v>
-      </c>
-      <c r="E84" s="6" t="n">
-        <f aca="false">D84*(1+Allgemein!$B$19)</f>
-        <v>40.46</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="B85" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C85" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="D85" s="6" t="n">
-        <f aca="false">B85*Allgemein!$B$17</f>
-        <v>136</v>
-      </c>
-      <c r="E85" s="6" t="n">
-        <f aca="false">D85*(1+Allgemein!$B$19)</f>
-        <v>161.84</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="B86" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C86" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="D86" s="6" t="n">
-        <f aca="false">B86*Allgemein!$B$17</f>
-        <v>68</v>
-      </c>
-      <c r="E86" s="6" t="n">
-        <f aca="false">D86*(1+Allgemein!$B$19)</f>
-        <v>80.92</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B89" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D89" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E89" s="7" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="B90" s="9" t="n">
-        <v>190</v>
+        <v>173</v>
+      </c>
+      <c r="B90" s="12" t="n">
+        <v>4</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>40</v>
+        <v>171</v>
+      </c>
+      <c r="D90" s="6" t="n">
+        <f aca="false">B90*Allgemein!$B$17</f>
+        <v>272</v>
       </c>
       <c r="E90" s="6" t="n">
-        <f aca="false">B90*(1+Allgemein!$B$19)</f>
-        <v>226.1</v>
+        <f aca="false">D90*(1+Allgemein!$B$19)</f>
+        <v>323.68</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="B91" s="9" t="n">
-        <v>150</v>
+        <v>174</v>
+      </c>
+      <c r="B91" s="12" t="n">
+        <v>0.25</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>40</v>
+        <v>171</v>
+      </c>
+      <c r="D91" s="6" t="n">
+        <f aca="false">B91*Allgemein!$B$17</f>
+        <v>17</v>
       </c>
       <c r="E91" s="6" t="n">
-        <f aca="false">B91*(1+Allgemein!$B$19)</f>
-        <v>178.5</v>
+        <f aca="false">D91*(1+Allgemein!$B$19)</f>
+        <v>20.23</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="B92" s="9" t="n">
-        <v>26</v>
+        <v>175</v>
+      </c>
+      <c r="B92" s="12" t="n">
+        <v>0.75</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>40</v>
+        <v>171</v>
+      </c>
+      <c r="D92" s="6" t="n">
+        <f aca="false">B92*Allgemein!$B$17</f>
+        <v>51</v>
       </c>
       <c r="E92" s="6" t="n">
-        <f aca="false">B92*(1+Allgemein!$B$19)</f>
-        <v>30.94</v>
+        <f aca="false">D92*(1+Allgemein!$B$19)</f>
+        <v>60.69</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="B93" s="9" t="n">
-        <v>110</v>
+        <v>176</v>
+      </c>
+      <c r="B93" s="12" t="n">
+        <v>0.5</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>40</v>
+        <v>171</v>
+      </c>
+      <c r="D93" s="6" t="n">
+        <f aca="false">B93*Allgemein!$B$17</f>
+        <v>34</v>
       </c>
       <c r="E93" s="6" t="n">
-        <f aca="false">B93*(1+Allgemein!$B$19)</f>
-        <v>130.9</v>
+        <f aca="false">D93*(1+Allgemein!$B$19)</f>
+        <v>40.46</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="B94" s="9" t="n">
-        <v>360</v>
+        <v>177</v>
+      </c>
+      <c r="B94" s="12" t="n">
+        <v>2</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>40</v>
+        <v>171</v>
+      </c>
+      <c r="D94" s="6" t="n">
+        <f aca="false">B94*Allgemein!$B$17</f>
+        <v>136</v>
       </c>
       <c r="E94" s="6" t="n">
-        <f aca="false">B94*(1+Allgemein!$B$19)</f>
-        <v>428.4</v>
+        <f aca="false">D94*(1+Allgemein!$B$19)</f>
+        <v>161.84</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="B95" s="9" t="n">
-        <v>55</v>
+        <v>178</v>
+      </c>
+      <c r="B95" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="C95" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="D95" s="6" t="n">
+        <f aca="false">B95*Allgemein!$B$17</f>
+        <v>68</v>
+      </c>
+      <c r="E95" s="6" t="n">
+        <f aca="false">D95*(1+Allgemein!$B$19)</f>
+        <v>80.92</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E98" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="B99" s="9" t="n">
+        <v>190</v>
+      </c>
+      <c r="C99" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="E95" s="6" t="n">
-        <f aca="false">B95*(1+Allgemein!$B$19)</f>
-        <v>65.45</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="B96" s="9" t="n">
-        <v>135</v>
-      </c>
-      <c r="C96" s="8" t="s">
+      <c r="E99" s="6" t="n">
+        <f aca="false">B99*(1+Allgemein!$B$19)</f>
+        <v>226.1</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="B100" s="9" t="n">
+        <v>150</v>
+      </c>
+      <c r="C100" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="E96" s="6" t="n">
-        <f aca="false">B96*(1+Allgemein!$B$19)</f>
-        <v>160.65</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="B97" s="9" t="n">
-        <v>170</v>
-      </c>
-      <c r="C97" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E97" s="6" t="n">
-        <f aca="false">B97*(1+Allgemein!$B$19)</f>
-        <v>202.3</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="3" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B100" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C100" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D100" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E100" s="7" t="s">
-        <v>36</v>
+      <c r="E100" s="6" t="n">
+        <f aca="false">B100*(1+Allgemein!$B$19)</f>
+        <v>178.5</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="8" t="s">
-        <v>146</v>
+        <v>174</v>
       </c>
       <c r="B101" s="9" t="n">
-        <v>149</v>
+        <v>26</v>
       </c>
       <c r="C101" s="8" t="s">
         <v>40</v>
       </c>
+      <c r="E101" s="6" t="n">
+        <f aca="false">B101*(1+Allgemein!$B$19)</f>
+        <v>30.94</v>
+      </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="B102" s="12" t="n">
+        <v>182</v>
+      </c>
+      <c r="B102" s="9" t="n">
+        <v>110</v>
+      </c>
+      <c r="C102" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E102" s="6" t="n">
+        <f aca="false">B102*(1+Allgemein!$B$19)</f>
+        <v>130.9</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="B103" s="9" t="n">
+        <v>360</v>
+      </c>
+      <c r="C103" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E103" s="6" t="n">
+        <f aca="false">B103*(1+Allgemein!$B$19)</f>
+        <v>428.4</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="B104" s="9" t="n">
+        <v>55</v>
+      </c>
+      <c r="C104" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E104" s="6" t="n">
+        <f aca="false">B104*(1+Allgemein!$B$19)</f>
+        <v>65.45</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="B105" s="9" t="n">
+        <v>135</v>
+      </c>
+      <c r="C105" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E105" s="6" t="n">
+        <f aca="false">B105*(1+Allgemein!$B$19)</f>
+        <v>160.65</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B106" s="9" t="n">
+        <v>170</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E106" s="6" t="n">
+        <f aca="false">B106*(1+Allgemein!$B$19)</f>
+        <v>202.3</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E109" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="B110" s="9" t="n">
+        <v>149</v>
+      </c>
+      <c r="C110" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="B111" s="12" t="n">
         <v>0.1</v>
       </c>
-      <c r="C102" s="8" t="s">
-        <v>148</v>
+      <c r="C111" s="8" t="s">
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -4816,39 +5442,39 @@
       <formula1>"Ja,Nein"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A9:A33" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A9:A37" type="list">
       <formula1>"Ja,Nein"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E9:E33" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E9:E37" type="list">
       <formula1>"Standard,Premium"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G9:G33" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G9:G37" type="list">
       <formula1>"–,A+++,A++,A+,A,B,C,D"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H9:H33" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H9:H37" type="list">
       <formula1>"–,A+++,A++,A+,A,B,C,D"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A39:A56" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A43:A62" type="list">
       <formula1>"Ja,Nein"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E39:E56" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E43:E62" type="list">
       <formula1>"Standard,Premium"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A61:A74" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A67:A83" type="list">
       <formula1>"Ja,Nein"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G61:G74" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G67:G83" type="list">
       <formula1>"–,A+++,A++,A+,A,B,C,D"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H61:H74" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H67:H83" type="list">
       <formula1>"–,A+++,A++,A+,A,B,C,D"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4898,12 +5524,12 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>149</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>150</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4923,7 +5549,7 @@
         <v>61</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>151</v>
+        <v>192</v>
       </c>
       <c r="G8" s="7" t="s">
         <v>68</v>
@@ -4940,10 +5566,10 @@
         <v>24</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>152</v>
+        <v>193</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>153</v>
+        <v>194</v>
       </c>
       <c r="D9" s="12" t="n">
         <v>6</v>
@@ -4952,7 +5578,7 @@
         <v>8900</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
@@ -4966,10 +5592,10 @@
         <v>24</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>152</v>
+        <v>193</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>154</v>
+        <v>195</v>
       </c>
       <c r="D10" s="12" t="n">
         <v>9</v>
@@ -4978,7 +5604,7 @@
         <v>10400</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
@@ -4992,10 +5618,10 @@
         <v>24</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>152</v>
+        <v>193</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>155</v>
+        <v>196</v>
       </c>
       <c r="D11" s="12" t="n">
         <v>12</v>
@@ -5004,7 +5630,7 @@
         <v>11900</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
@@ -5018,10 +5644,10 @@
         <v>24</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>152</v>
+        <v>193</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>156</v>
+        <v>197</v>
       </c>
       <c r="D12" s="12" t="n">
         <v>16</v>
@@ -5030,7 +5656,7 @@
         <v>13400</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
@@ -5044,10 +5670,10 @@
         <v>24</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>152</v>
+        <v>193</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>157</v>
+        <v>198</v>
       </c>
       <c r="D13" s="12" t="n">
         <v>18</v>
@@ -5056,7 +5682,7 @@
         <v>14900</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
@@ -5137,12 +5763,12 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5164,13 +5790,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>158</v>
+        <v>199</v>
       </c>
       <c r="B23" s="12" t="n">
         <v>30</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D23" s="6" t="n">
         <f aca="false">B23*Allgemein!$B$17</f>
@@ -5183,13 +5809,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>159</v>
+        <v>200</v>
       </c>
       <c r="B24" s="12" t="n">
         <v>12</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D24" s="6" t="n">
         <f aca="false">B24*Allgemein!$B$17</f>
@@ -5202,13 +5828,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>160</v>
+        <v>201</v>
       </c>
       <c r="B25" s="12" t="n">
         <v>6</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D25" s="6" t="n">
         <f aca="false">B25*Allgemein!$B$17</f>
@@ -5221,13 +5847,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>161</v>
+        <v>202</v>
       </c>
       <c r="B26" s="12" t="n">
         <v>10</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D26" s="6" t="n">
         <f aca="false">B26*Allgemein!$B$17</f>
@@ -5240,13 +5866,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>162</v>
+        <v>203</v>
       </c>
       <c r="B27" s="12" t="n">
         <v>2.5</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D27" s="6" t="n">
         <f aca="false">B27*Allgemein!$B$17</f>
@@ -5259,13 +5885,13 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>163</v>
+        <v>204</v>
       </c>
       <c r="B28" s="12" t="n">
         <v>6</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D28" s="6" t="n">
         <f aca="false">B28*Allgemein!$B$17</f>
@@ -5278,7 +5904,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>138</v>
+        <v>179</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5300,7 +5926,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>164</v>
+        <v>205</v>
       </c>
       <c r="B32" s="9" t="n">
         <v>4200</v>
@@ -5315,7 +5941,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>165</v>
+        <v>206</v>
       </c>
       <c r="B33" s="9" t="n">
         <v>900</v>
@@ -5330,7 +5956,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
-        <v>166</v>
+        <v>207</v>
       </c>
       <c r="B34" s="9" t="n">
         <v>150</v>
@@ -5345,7 +5971,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>167</v>
+        <v>208</v>
       </c>
       <c r="B35" s="9" t="n">
         <v>350</v>
@@ -5360,7 +5986,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>168</v>
+        <v>209</v>
       </c>
       <c r="B36" s="9" t="n">
         <v>380</v>
@@ -5375,7 +6001,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>169</v>
+        <v>210</v>
       </c>
       <c r="B37" s="9" t="n">
         <v>650</v>
@@ -5390,7 +6016,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>170</v>
+        <v>211</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5412,13 +6038,13 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="s">
-        <v>171</v>
+        <v>212</v>
       </c>
       <c r="B41" s="12" t="n">
         <v>0.25</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>148</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -5481,12 +6107,12 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>172</v>
+        <v>213</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>173</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5500,10 +6126,10 @@
         <v>58</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>174</v>
+        <v>215</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>175</v>
+        <v>216</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>70</v>
@@ -5514,10 +6140,10 @@
         <v>24</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>176</v>
+        <v>217</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="D9" s="12" t="n">
         <v>450</v>
@@ -5535,10 +6161,10 @@
         <v>24</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>179</v>
+        <v>220</v>
       </c>
       <c r="D10" s="12" t="n">
         <v>400</v>
@@ -5608,17 +6234,17 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>180</v>
+        <v>221</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5646,10 +6272,10 @@
         <v>24</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>182</v>
+        <v>223</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="D21" s="12" t="n">
         <v>4</v>
@@ -5667,10 +6293,10 @@
         <v>24</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>182</v>
+        <v>223</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>184</v>
+        <v>225</v>
       </c>
       <c r="D22" s="12" t="n">
         <v>6</v>
@@ -5688,10 +6314,10 @@
         <v>24</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>182</v>
+        <v>223</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>185</v>
+        <v>226</v>
       </c>
       <c r="D23" s="12" t="n">
         <v>8</v>
@@ -5709,10 +6335,10 @@
         <v>24</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>182</v>
+        <v>223</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>186</v>
+        <v>227</v>
       </c>
       <c r="D24" s="12" t="n">
         <v>10</v>
@@ -5730,10 +6356,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>182</v>
+        <v>223</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>187</v>
+        <v>228</v>
       </c>
       <c r="D25" s="12" t="n">
         <v>15</v>
@@ -5803,17 +6429,17 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>188</v>
+        <v>229</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>189</v>
+        <v>230</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5827,7 +6453,7 @@
         <v>58</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>190</v>
+        <v>231</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>61</v>
@@ -5841,10 +6467,10 @@
         <v>24</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>192</v>
+        <v>233</v>
       </c>
       <c r="D36" s="12" t="n">
         <v>5.1</v>
@@ -5862,10 +6488,10 @@
         <v>24</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
       <c r="D37" s="12" t="n">
         <v>7.7</v>
@@ -5883,10 +6509,10 @@
         <v>24</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>194</v>
+        <v>235</v>
       </c>
       <c r="D38" s="12" t="n">
         <v>10.2</v>
@@ -5956,17 +6582,17 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>195</v>
+        <v>236</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>196</v>
+        <v>237</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5988,13 +6614,13 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="s">
-        <v>197</v>
+        <v>238</v>
       </c>
       <c r="B49" s="12" t="n">
         <v>5</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D49" s="6" t="n">
         <f aca="false">B49*Allgemein!$B$17</f>
@@ -6007,7 +6633,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6029,13 +6655,13 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="s">
-        <v>198</v>
+        <v>239</v>
       </c>
       <c r="B53" s="12" t="n">
         <v>8</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D53" s="6" t="n">
         <f aca="false">B53*Allgemein!$B$17</f>
@@ -6048,13 +6674,13 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="s">
-        <v>199</v>
+        <v>240</v>
       </c>
       <c r="B54" s="12" t="n">
         <v>0.6</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D54" s="6" t="n">
         <f aca="false">B54*Allgemein!$B$17</f>
@@ -6067,13 +6693,13 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="s">
-        <v>200</v>
+        <v>241</v>
       </c>
       <c r="B55" s="12" t="n">
         <v>4</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D55" s="6" t="n">
         <f aca="false">B55*Allgemein!$B$17</f>
@@ -6086,13 +6712,13 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="s">
-        <v>201</v>
+        <v>242</v>
       </c>
       <c r="B56" s="12" t="n">
         <v>4</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D56" s="6" t="n">
         <f aca="false">B56*Allgemein!$B$17</f>
@@ -6105,7 +6731,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
-        <v>138</v>
+        <v>179</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6127,7 +6753,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="8" t="s">
-        <v>202</v>
+        <v>243</v>
       </c>
       <c r="B60" s="9" t="n">
         <v>48</v>
@@ -6142,7 +6768,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="8" t="s">
-        <v>203</v>
+        <v>244</v>
       </c>
       <c r="B61" s="9" t="n">
         <v>480</v>
@@ -6157,7 +6783,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="8" t="s">
-        <v>204</v>
+        <v>245</v>
       </c>
       <c r="B62" s="9" t="n">
         <v>650</v>
@@ -6172,7 +6798,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="s">
-        <v>205</v>
+        <v>246</v>
       </c>
       <c r="B63" s="9" t="n">
         <v>450</v>
@@ -6187,7 +6813,7 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="8" t="s">
-        <v>206</v>
+        <v>247</v>
       </c>
       <c r="B64" s="9" t="n">
         <v>250</v>
@@ -6202,7 +6828,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="8" t="s">
-        <v>207</v>
+        <v>248</v>
       </c>
       <c r="B65" s="9" t="n">
         <v>450</v>
@@ -6217,7 +6843,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="3" t="s">
-        <v>208</v>
+        <v>249</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6239,35 +6865,35 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="8" t="s">
-        <v>209</v>
+        <v>250</v>
       </c>
       <c r="B69" s="12" t="n">
         <v>950</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>210</v>
+        <v>251</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="8" t="s">
-        <v>211</v>
+        <v>252</v>
       </c>
       <c r="B70" s="13" t="n">
         <v>0.35</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>212</v>
+        <v>253</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="s">
-        <v>213</v>
+        <v>254</v>
       </c>
       <c r="B71" s="13" t="n">
         <v>0.077</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>212</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -6334,7 +6960,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>214</v>
+        <v>255</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6356,16 +6982,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>215</v>
+        <v>256</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>216</v>
+        <v>257</v>
       </c>
       <c r="C8" s="8"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>217</v>
+        <v>258</v>
       </c>
       <c r="B9" s="9" t="n">
         <v>900</v>
@@ -6380,13 +7006,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>218</v>
+        <v>259</v>
       </c>
       <c r="B10" s="12" t="n">
         <v>12</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D10" s="6" t="n">
         <f aca="false">B10*Allgemein!$B$17</f>
@@ -6399,7 +7025,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>219</v>
+        <v>260</v>
       </c>
       <c r="B11" s="9" t="n">
         <v>160</v>
@@ -6414,13 +7040,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>220</v>
+        <v>261</v>
       </c>
       <c r="B12" s="12" t="n">
         <v>1.5</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D12" s="6" t="n">
         <f aca="false">B12*Allgemein!$B$17</f>
@@ -6433,7 +7059,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>221</v>
+        <v>262</v>
       </c>
       <c r="B13" s="9" t="n">
         <v>120</v>
@@ -6448,13 +7074,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>222</v>
+        <v>263</v>
       </c>
       <c r="B14" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D14" s="6" t="n">
         <f aca="false">B14*Allgemein!$B$17</f>
@@ -6467,7 +7093,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>223</v>
+        <v>264</v>
       </c>
       <c r="B15" s="9" t="n">
         <v>140</v>
@@ -6482,13 +7108,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>224</v>
+        <v>265</v>
       </c>
       <c r="B16" s="12" t="n">
         <v>1.5</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D16" s="6" t="n">
         <f aca="false">B16*Allgemein!$B$17</f>
@@ -6501,7 +7127,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>225</v>
+        <v>266</v>
       </c>
       <c r="B17" s="9" t="n">
         <v>600</v>
@@ -6516,13 +7142,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>226</v>
+        <v>267</v>
       </c>
       <c r="B18" s="12" t="n">
         <v>5</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D18" s="6" t="n">
         <f aca="false">B18*Allgemein!$B$17</f>
@@ -6535,7 +7161,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>227</v>
+        <v>268</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6557,16 +7183,16 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>215</v>
+        <v>256</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>228</v>
+        <v>269</v>
       </c>
       <c r="C22" s="8"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>217</v>
+        <v>258</v>
       </c>
       <c r="B23" s="9" t="n">
         <v>180</v>
@@ -6581,13 +7207,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>218</v>
+        <v>259</v>
       </c>
       <c r="B24" s="12" t="n">
         <v>3</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D24" s="6" t="n">
         <f aca="false">B24*Allgemein!$B$17</f>
@@ -6600,7 +7226,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>219</v>
+        <v>260</v>
       </c>
       <c r="B25" s="9" t="n">
         <v>75</v>
@@ -6615,13 +7241,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>220</v>
+        <v>261</v>
       </c>
       <c r="B26" s="12" t="n">
         <v>1.25</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D26" s="6" t="n">
         <f aca="false">B26*Allgemein!$B$17</f>
@@ -6634,7 +7260,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>221</v>
+        <v>262</v>
       </c>
       <c r="B27" s="9" t="n">
         <v>65</v>
@@ -6649,13 +7275,13 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>222</v>
+        <v>263</v>
       </c>
       <c r="B28" s="12" t="n">
         <v>0.75</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D28" s="6" t="n">
         <f aca="false">B28*Allgemein!$B$17</f>
@@ -6668,7 +7294,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>223</v>
+        <v>264</v>
       </c>
       <c r="B29" s="9" t="n">
         <v>70</v>
@@ -6683,13 +7309,13 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>224</v>
+        <v>265</v>
       </c>
       <c r="B30" s="12" t="n">
         <v>1.25</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D30" s="6" t="n">
         <f aca="false">B30*Allgemein!$B$17</f>
@@ -6702,7 +7328,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>225</v>
+        <v>266</v>
       </c>
       <c r="B31" s="9" t="n">
         <v>450</v>
@@ -6717,13 +7343,13 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>226</v>
+        <v>267</v>
       </c>
       <c r="B32" s="12" t="n">
         <v>4</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D32" s="6" t="n">
         <f aca="false">B32*Allgemein!$B$17</f>
@@ -6736,7 +7362,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>229</v>
+        <v>270</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6758,16 +7384,16 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>215</v>
+        <v>256</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>230</v>
+        <v>271</v>
       </c>
       <c r="C36" s="8"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>217</v>
+        <v>258</v>
       </c>
       <c r="B37" s="9" t="n">
         <v>1300</v>
@@ -6782,13 +7408,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
-        <v>218</v>
+        <v>259</v>
       </c>
       <c r="B38" s="12" t="n">
         <v>14</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D38" s="6" t="n">
         <f aca="false">B38*Allgemein!$B$17</f>
@@ -6801,7 +7427,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
-        <v>219</v>
+        <v>260</v>
       </c>
       <c r="B39" s="9" t="n">
         <v>180</v>
@@ -6816,13 +7442,13 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>220</v>
+        <v>261</v>
       </c>
       <c r="B40" s="12" t="n">
         <v>2</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D40" s="6" t="n">
         <f aca="false">B40*Allgemein!$B$17</f>
@@ -6835,7 +7461,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="s">
-        <v>221</v>
+        <v>262</v>
       </c>
       <c r="B41" s="9" t="n">
         <v>140</v>
@@ -6850,13 +7476,13 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="s">
-        <v>222</v>
+        <v>263</v>
       </c>
       <c r="B42" s="12" t="n">
         <v>1.5</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D42" s="6" t="n">
         <f aca="false">B42*Allgemein!$B$17</f>
@@ -6869,7 +7495,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>223</v>
+        <v>264</v>
       </c>
       <c r="B43" s="9" t="n">
         <v>150</v>
@@ -6884,13 +7510,13 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="s">
-        <v>224</v>
+        <v>265</v>
       </c>
       <c r="B44" s="12" t="n">
         <v>1.75</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D44" s="6" t="n">
         <f aca="false">B44*Allgemein!$B$17</f>
@@ -6903,7 +7529,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="s">
-        <v>225</v>
+        <v>266</v>
       </c>
       <c r="B45" s="9" t="n">
         <v>700</v>
@@ -6918,13 +7544,13 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="s">
-        <v>226</v>
+        <v>267</v>
       </c>
       <c r="B46" s="12" t="n">
         <v>7</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D46" s="6" t="n">
         <f aca="false">B46*Allgemein!$B$17</f>
@@ -6969,12 +7595,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>231</v>
+        <v>272</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>232</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6987,12 +7613,12 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>234</v>
+        <v>275</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7000,7 +7626,7 @@
         <v>56</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>235</v>
+        <v>276</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7008,7 +7634,7 @@
         <v>24</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>236</v>
+        <v>277</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7016,7 +7642,7 @@
         <v>24</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>237</v>
+        <v>278</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7024,7 +7650,7 @@
         <v>24</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>238</v>
+        <v>279</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7049,17 +7675,17 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>239</v>
+        <v>280</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>240</v>
+        <v>281</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7070,25 +7696,25 @@
         <v>57</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>58</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>242</v>
+        <v>283</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>70</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>243</v>
+        <v>284</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>244</v>
+        <v>285</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>245</v>
+        <v>286</v>
       </c>
       <c r="J21" s="7" t="s">
         <v>68</v>
@@ -7102,16 +7728,16 @@
         <v>24</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>236</v>
+        <v>277</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>246</v>
+        <v>287</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>247</v>
+        <v>288</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>248</v>
+        <v>289</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>599</v>
@@ -7120,10 +7746,10 @@
         <v>49</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>249</v>
+        <v>290</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>250</v>
+        <v>291</v>
       </c>
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
@@ -7133,16 +7759,16 @@
         <v>24</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>236</v>
+        <v>277</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>246</v>
+        <v>287</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>251</v>
+        <v>292</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>248</v>
+        <v>289</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>799</v>
@@ -7151,10 +7777,10 @@
         <v>49</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>249</v>
+        <v>290</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>250</v>
+        <v>291</v>
       </c>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
@@ -7164,16 +7790,16 @@
         <v>24</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>236</v>
+        <v>277</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>252</v>
+        <v>293</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>253</v>
+        <v>294</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>248</v>
+        <v>289</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>849</v>
@@ -7182,10 +7808,10 @@
         <v>39</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>254</v>
+        <v>295</v>
       </c>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
@@ -7195,16 +7821,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>236</v>
+        <v>277</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>255</v>
+        <v>296</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>256</v>
+        <v>297</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>248</v>
+        <v>289</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>649</v>
@@ -7213,10 +7839,10 @@
         <v>149</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>257</v>
+        <v>298</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>250</v>
+        <v>291</v>
       </c>
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
@@ -7226,16 +7852,16 @@
         <v>24</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>236</v>
+        <v>277</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>258</v>
+        <v>299</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>248</v>
+        <v>289</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>699</v>
@@ -7244,10 +7870,10 @@
         <v>129</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>254</v>
+        <v>295</v>
       </c>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
@@ -7257,16 +7883,16 @@
         <v>24</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>236</v>
+        <v>277</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>260</v>
+        <v>301</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>261</v>
+        <v>302</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>248</v>
+        <v>289</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>749</v>
@@ -7275,10 +7901,10 @@
         <v>39</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>257</v>
+        <v>298</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>250</v>
+        <v>291</v>
       </c>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
@@ -7288,16 +7914,16 @@
         <v>24</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>237</v>
+        <v>278</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>246</v>
+        <v>287</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>262</v>
+        <v>303</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>248</v>
+        <v>289</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>1199</v>
@@ -7306,10 +7932,10 @@
         <v>49</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>249</v>
+        <v>290</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>250</v>
+        <v>291</v>
       </c>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
@@ -7319,16 +7945,16 @@
         <v>24</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>238</v>
+        <v>279</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>260</v>
+        <v>301</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>263</v>
+        <v>304</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>248</v>
+        <v>289</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>999</v>
@@ -7337,10 +7963,10 @@
         <v>39</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>257</v>
+        <v>298</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>250</v>
+        <v>291</v>
       </c>
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
@@ -7412,12 +8038,12 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>264</v>
+        <v>305</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7439,7 +8065,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
-        <v>265</v>
+        <v>306</v>
       </c>
       <c r="B39" s="9" t="n">
         <v>39</v>
@@ -7450,7 +8076,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>266</v>
+        <v>307</v>
       </c>
       <c r="B40" s="9" t="n">
         <v>25</v>
@@ -7461,28 +8087,28 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="s">
-        <v>267</v>
+        <v>308</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>268</v>
+        <v>309</v>
       </c>
       <c r="C41" s="8"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="s">
-        <v>269</v>
+        <v>310</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>270</v>
+        <v>311</v>
       </c>
       <c r="C42" s="8"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>271</v>
+        <v>312</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>272</v>
+        <v>313</v>
       </c>
       <c r="C43" s="8"/>
     </row>
@@ -7558,7 +8184,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>273</v>
+        <v>314</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7580,7 +8206,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>274</v>
+        <v>315</v>
       </c>
       <c r="B8" s="9" t="n">
         <v>42</v>
@@ -7595,13 +8221,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>275</v>
+        <v>316</v>
       </c>
       <c r="B9" s="12" t="n">
         <v>0.75</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D9" s="6" t="n">
         <f aca="false">B9*Allgemein!$B$17</f>
@@ -7614,7 +8240,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>276</v>
+        <v>317</v>
       </c>
       <c r="B10" s="9" t="n">
         <v>52</v>
@@ -7629,13 +8255,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>277</v>
+        <v>318</v>
       </c>
       <c r="B11" s="12" t="n">
         <v>1.2</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D11" s="6" t="n">
         <f aca="false">B11*Allgemein!$B$17</f>
@@ -7648,7 +8274,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>278</v>
+        <v>319</v>
       </c>
       <c r="B12" s="9" t="n">
         <v>30</v>
@@ -7663,13 +8289,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>279</v>
+        <v>320</v>
       </c>
       <c r="B13" s="12" t="n">
         <v>0.6</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D13" s="6" t="n">
         <f aca="false">B13*Allgemein!$B$17</f>
@@ -7682,7 +8308,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>280</v>
+        <v>321</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7704,7 +8330,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>281</v>
+        <v>322</v>
       </c>
       <c r="B17" s="9" t="n">
         <v>1650</v>
@@ -7719,13 +8345,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>282</v>
+        <v>323</v>
       </c>
       <c r="B18" s="12" t="n">
         <v>18</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D18" s="6" t="n">
         <f aca="false">B18*Allgemein!$B$17</f>
@@ -7738,7 +8364,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>283</v>
+        <v>324</v>
       </c>
       <c r="B19" s="9" t="n">
         <v>55</v>
@@ -7753,13 +8379,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>284</v>
+        <v>325</v>
       </c>
       <c r="B20" s="12" t="n">
         <v>1.4</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D20" s="6" t="n">
         <f aca="false">B20*Allgemein!$B$17</f>
@@ -7772,7 +8398,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>285</v>
+        <v>326</v>
       </c>
       <c r="B21" s="9" t="n">
         <v>330</v>
@@ -7787,13 +8413,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>286</v>
+        <v>327</v>
       </c>
       <c r="B22" s="12" t="n">
         <v>2.5</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D22" s="6" t="n">
         <f aca="false">B22*Allgemein!$B$17</f>
@@ -7806,7 +8432,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>287</v>
+        <v>328</v>
       </c>
       <c r="B23" s="9" t="n">
         <v>0</v>
@@ -7821,13 +8447,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>288</v>
+        <v>329</v>
       </c>
       <c r="B24" s="12" t="n">
         <v>2.75</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D24" s="6" t="n">
         <f aca="false">B24*Allgemein!$B$17</f>
@@ -7840,12 +8466,12 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>289</v>
+        <v>330</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>290</v>
+        <v>331</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7873,10 +8499,10 @@
         <v>24</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>182</v>
+        <v>223</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>291</v>
+        <v>332</v>
       </c>
       <c r="D29" s="12" t="n">
         <v>11</v>
@@ -7894,10 +8520,10 @@
         <v>24</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>292</v>
+        <v>333</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>293</v>
+        <v>334</v>
       </c>
       <c r="D30" s="12" t="n">
         <v>11</v>
@@ -7915,10 +8541,10 @@
         <v>24</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>294</v>
+        <v>335</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>295</v>
+        <v>336</v>
       </c>
       <c r="D31" s="12" t="n">
         <v>11</v>
@@ -7936,10 +8562,10 @@
         <v>24</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>296</v>
+        <v>337</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>297</v>
+        <v>338</v>
       </c>
       <c r="D32" s="12" t="n">
         <v>11</v>
@@ -8009,12 +8635,12 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>298</v>
+        <v>339</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8036,13 +8662,13 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="s">
-        <v>299</v>
+        <v>340</v>
       </c>
       <c r="B42" s="12" t="n">
         <v>7</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D42" s="6" t="n">
         <f aca="false">B42*Allgemein!$B$17</f>
@@ -8084,2190 +8710,2190 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>301</v>
+        <v>342</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>302</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>303</v>
+        <v>344</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>304</v>
+        <v>345</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>305</v>
+        <v>346</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>306</v>
+        <v>347</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>307</v>
+        <v>348</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>308</v>
+        <v>349</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>309</v>
+        <v>350</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>310</v>
+        <v>351</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>311</v>
+        <v>352</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>312</v>
+        <v>353</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>313</v>
+        <v>354</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>314</v>
+        <v>355</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>316</v>
+        <v>357</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>317</v>
+        <v>358</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>319</v>
+        <v>360</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>320</v>
+        <v>361</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>321</v>
+        <v>362</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>322</v>
+        <v>363</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>323</v>
+        <v>364</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>324</v>
+        <v>365</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>325</v>
+        <v>366</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>323</v>
+        <v>364</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>326</v>
+        <v>367</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>327</v>
+        <v>368</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>328</v>
+        <v>369</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>329</v>
+        <v>370</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>323</v>
+        <v>364</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>330</v>
+        <v>371</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>331</v>
+        <v>372</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>323</v>
+        <v>364</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>332</v>
+        <v>373</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>333</v>
+        <v>374</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>323</v>
+        <v>364</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B16" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>334</v>
+        <v>375</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>335</v>
+        <v>376</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>323</v>
+        <v>364</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B17" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>336</v>
+        <v>377</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>337</v>
+        <v>378</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="B18" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>338</v>
+        <v>379</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>306</v>
+        <v>347</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>339</v>
+        <v>380</v>
       </c>
       <c r="B19" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>340</v>
+        <v>381</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>341</v>
+        <v>382</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>342</v>
+        <v>383</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>339</v>
+        <v>380</v>
       </c>
       <c r="B20" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>343</v>
+        <v>384</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>344</v>
+        <v>385</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>345</v>
+        <v>386</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>339</v>
+        <v>380</v>
       </c>
       <c r="B21" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>346</v>
+        <v>387</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>347</v>
+        <v>388</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>348</v>
+        <v>389</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B22" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>349</v>
+        <v>390</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>350</v>
+        <v>391</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B23" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>351</v>
+        <v>392</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>352</v>
+        <v>393</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B24" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>353</v>
+        <v>394</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>354</v>
+        <v>395</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B25" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>355</v>
+        <v>396</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>356</v>
+        <v>397</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B26" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>357</v>
+        <v>398</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>358</v>
+        <v>399</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B27" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C27" s="14" t="s">
+        <v>400</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>401</v>
+      </c>
+      <c r="E27" s="14" t="s">
         <v>359</v>
-      </c>
-      <c r="D27" s="14" t="s">
-        <v>360</v>
-      </c>
-      <c r="E27" s="14" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B28" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>361</v>
+        <v>402</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>362</v>
+        <v>403</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B29" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>363</v>
+        <v>404</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>364</v>
+        <v>405</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B30" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>365</v>
+        <v>406</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>366</v>
+        <v>407</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B31" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>367</v>
+        <v>408</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>368</v>
+        <v>409</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B32" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>369</v>
+        <v>410</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>370</v>
+        <v>411</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B33" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>371</v>
+        <v>412</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>372</v>
+        <v>413</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B34" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>373</v>
+        <v>414</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>374</v>
+        <v>415</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B35" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>375</v>
+        <v>416</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>376</v>
+        <v>417</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B36" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>377</v>
+        <v>418</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>378</v>
+        <v>419</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B37" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>379</v>
+        <v>420</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>380</v>
+        <v>421</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B38" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>381</v>
+        <v>422</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>382</v>
+        <v>423</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B39" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>383</v>
+        <v>424</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>384</v>
+        <v>425</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="B40" s="14" t="s">
         <v>23</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>338</v>
+        <v>379</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>302</v>
+        <v>343</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="14" t="s">
-        <v>339</v>
+        <v>380</v>
       </c>
       <c r="B41" s="14" t="s">
         <v>23</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>387</v>
+        <v>428</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B42" s="14" t="s">
         <v>23</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>388</v>
+        <v>429</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>389</v>
+        <v>430</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B43" s="14" t="s">
         <v>23</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>390</v>
+        <v>431</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>391</v>
+        <v>432</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B44" s="14" t="s">
         <v>23</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>392</v>
+        <v>433</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B45" s="14" t="s">
         <v>23</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>328</v>
+        <v>369</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>394</v>
+        <v>435</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B46" s="14" t="s">
         <v>23</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>330</v>
+        <v>371</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>395</v>
+        <v>436</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B47" s="14" t="s">
         <v>23</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>332</v>
+        <v>373</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>396</v>
+        <v>437</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B48" s="14" t="s">
         <v>23</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>397</v>
+        <v>438</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>398</v>
+        <v>439</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B49" s="14" t="s">
         <v>23</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>399</v>
+        <v>440</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>400</v>
+        <v>441</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B50" s="14" t="s">
         <v>23</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>401</v>
+        <v>442</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>402</v>
+        <v>443</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B51" s="14" t="s">
         <v>23</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>403</v>
+        <v>444</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>404</v>
+        <v>445</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B52" s="14" t="s">
         <v>23</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>405</v>
+        <v>446</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>406</v>
+        <v>447</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B53" s="14" t="s">
         <v>23</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>407</v>
+        <v>448</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>408</v>
+        <v>449</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B54" s="14" t="s">
         <v>23</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>409</v>
+        <v>450</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>410</v>
+        <v>451</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="14" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="B55" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>338</v>
+        <v>379</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>304</v>
+        <v>345</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="14" t="s">
-        <v>339</v>
+        <v>380</v>
       </c>
       <c r="B56" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>411</v>
+        <v>452</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>412</v>
+        <v>453</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>413</v>
+        <v>454</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="14" t="s">
-        <v>339</v>
+        <v>380</v>
       </c>
       <c r="B57" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>414</v>
+        <v>455</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>415</v>
+        <v>456</v>
       </c>
       <c r="E57" s="14" t="s">
-        <v>416</v>
+        <v>457</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="14" t="s">
-        <v>339</v>
+        <v>380</v>
       </c>
       <c r="B58" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>417</v>
+        <v>458</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>418</v>
+        <v>459</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>419</v>
+        <v>460</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B59" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>420</v>
+        <v>461</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>421</v>
+        <v>462</v>
       </c>
       <c r="E59" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B60" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>422</v>
+        <v>463</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>423</v>
+        <v>464</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B61" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>424</v>
+        <v>465</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>425</v>
+        <v>466</v>
       </c>
       <c r="E61" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B62" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>426</v>
+        <v>467</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>427</v>
+        <v>468</v>
       </c>
       <c r="E62" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B63" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C63" s="14" t="s">
-        <v>428</v>
+        <v>469</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>429</v>
+        <v>470</v>
       </c>
       <c r="E63" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B64" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>430</v>
+        <v>471</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>431</v>
+        <v>472</v>
       </c>
       <c r="E64" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B65" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C65" s="14" t="s">
-        <v>432</v>
+        <v>473</v>
       </c>
       <c r="D65" s="14" t="s">
-        <v>433</v>
+        <v>474</v>
       </c>
       <c r="E65" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B66" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>434</v>
+        <v>475</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>435</v>
+        <v>476</v>
       </c>
       <c r="E66" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B67" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C67" s="14" t="s">
-        <v>436</v>
+        <v>477</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>437</v>
+        <v>478</v>
       </c>
       <c r="E67" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B68" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>438</v>
+        <v>479</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>439</v>
+        <v>480</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B69" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C69" s="14" t="s">
-        <v>440</v>
+        <v>481</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>441</v>
+        <v>482</v>
       </c>
       <c r="E69" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B70" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C70" s="14" t="s">
-        <v>442</v>
+        <v>483</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>443</v>
+        <v>484</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B71" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C71" s="14" t="s">
-        <v>444</v>
+        <v>485</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>445</v>
+        <v>486</v>
       </c>
       <c r="E71" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B72" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>446</v>
+        <v>487</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>447</v>
+        <v>488</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="14" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="B73" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C73" s="14" t="s">
-        <v>338</v>
+        <v>379</v>
       </c>
       <c r="D73" s="14" t="s">
-        <v>308</v>
+        <v>349</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B74" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C74" s="14" t="s">
-        <v>303</v>
+        <v>344</v>
       </c>
       <c r="D74" s="14" t="s">
-        <v>448</v>
+        <v>489</v>
       </c>
       <c r="E74" s="14" t="s">
-        <v>449</v>
+        <v>490</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B75" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C75" s="14" t="s">
-        <v>305</v>
+        <v>346</v>
       </c>
       <c r="D75" s="14" t="s">
-        <v>450</v>
+        <v>491</v>
       </c>
       <c r="E75" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B76" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C76" s="14" t="s">
-        <v>307</v>
+        <v>348</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>451</v>
+        <v>492</v>
       </c>
       <c r="E76" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B77" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C77" s="14" t="s">
-        <v>309</v>
+        <v>350</v>
       </c>
       <c r="D77" s="14" t="s">
-        <v>452</v>
+        <v>493</v>
       </c>
       <c r="E77" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B78" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C78" s="14" t="s">
-        <v>311</v>
+        <v>352</v>
       </c>
       <c r="D78" s="14" t="s">
-        <v>453</v>
+        <v>494</v>
       </c>
       <c r="E78" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B79" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C79" s="14" t="s">
-        <v>313</v>
+        <v>354</v>
       </c>
       <c r="D79" s="14" t="s">
-        <v>454</v>
+        <v>495</v>
       </c>
       <c r="E79" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B80" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>455</v>
+        <v>496</v>
       </c>
       <c r="D80" s="14" t="s">
-        <v>456</v>
+        <v>497</v>
       </c>
       <c r="E80" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B81" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C81" s="14" t="s">
-        <v>457</v>
+        <v>498</v>
       </c>
       <c r="D81" s="14" t="s">
-        <v>458</v>
+        <v>499</v>
       </c>
       <c r="E81" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B82" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C82" s="14" t="s">
-        <v>459</v>
+        <v>500</v>
       </c>
       <c r="D82" s="14" t="s">
-        <v>460</v>
+        <v>501</v>
       </c>
       <c r="E82" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B83" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C83" s="14" t="s">
-        <v>316</v>
+        <v>357</v>
       </c>
       <c r="D83" s="14" t="s">
-        <v>461</v>
+        <v>502</v>
       </c>
       <c r="E83" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B84" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C84" s="14" t="s">
-        <v>319</v>
+        <v>360</v>
       </c>
       <c r="D84" s="14" t="s">
-        <v>462</v>
+        <v>503</v>
       </c>
       <c r="E84" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B85" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C85" s="14" t="s">
-        <v>463</v>
+        <v>504</v>
       </c>
       <c r="D85" s="14" t="s">
-        <v>464</v>
+        <v>505</v>
       </c>
       <c r="E85" s="14" t="s">
-        <v>449</v>
+        <v>490</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B86" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C86" s="14" t="s">
-        <v>388</v>
+        <v>429</v>
       </c>
       <c r="D86" s="14" t="s">
-        <v>465</v>
+        <v>506</v>
       </c>
       <c r="E86" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B87" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C87" s="14" t="s">
-        <v>390</v>
+        <v>431</v>
       </c>
       <c r="D87" s="14" t="s">
-        <v>466</v>
+        <v>507</v>
       </c>
       <c r="E87" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B88" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C88" s="14" t="s">
-        <v>392</v>
+        <v>433</v>
       </c>
       <c r="D88" s="14" t="s">
-        <v>467</v>
+        <v>508</v>
       </c>
       <c r="E88" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B89" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C89" s="14" t="s">
-        <v>328</v>
+        <v>369</v>
       </c>
       <c r="D89" s="14" t="s">
-        <v>468</v>
+        <v>509</v>
       </c>
       <c r="E89" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B90" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C90" s="14" t="s">
-        <v>330</v>
+        <v>371</v>
       </c>
       <c r="D90" s="14" t="s">
-        <v>469</v>
+        <v>510</v>
       </c>
       <c r="E90" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B91" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C91" s="14" t="s">
-        <v>332</v>
+        <v>373</v>
       </c>
       <c r="D91" s="14" t="s">
-        <v>470</v>
+        <v>511</v>
       </c>
       <c r="E91" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B92" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C92" s="14" t="s">
-        <v>334</v>
+        <v>375</v>
       </c>
       <c r="D92" s="14" t="s">
-        <v>471</v>
+        <v>512</v>
       </c>
       <c r="E92" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B93" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C93" s="14" t="s">
-        <v>336</v>
+        <v>377</v>
       </c>
       <c r="D93" s="14" t="s">
-        <v>472</v>
+        <v>513</v>
       </c>
       <c r="E93" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B94" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C94" s="14" t="s">
-        <v>473</v>
+        <v>514</v>
       </c>
       <c r="D94" s="14" t="s">
-        <v>474</v>
+        <v>515</v>
       </c>
       <c r="E94" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B95" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C95" s="14" t="s">
-        <v>397</v>
+        <v>438</v>
       </c>
       <c r="D95" s="14" t="s">
-        <v>475</v>
+        <v>516</v>
       </c>
       <c r="E95" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B96" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C96" s="14" t="s">
-        <v>405</v>
+        <v>446</v>
       </c>
       <c r="D96" s="14" t="s">
-        <v>476</v>
+        <v>517</v>
       </c>
       <c r="E96" s="14" t="s">
-        <v>449</v>
+        <v>490</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B97" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C97" s="14" t="s">
-        <v>407</v>
+        <v>448</v>
       </c>
       <c r="D97" s="14" t="s">
-        <v>477</v>
+        <v>518</v>
       </c>
       <c r="E97" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B98" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C98" s="14" t="s">
-        <v>478</v>
+        <v>519</v>
       </c>
       <c r="D98" s="14" t="s">
-        <v>479</v>
+        <v>520</v>
       </c>
       <c r="E98" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B99" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C99" s="14" t="s">
-        <v>480</v>
+        <v>521</v>
       </c>
       <c r="D99" s="14" t="s">
-        <v>481</v>
+        <v>522</v>
       </c>
       <c r="E99" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B100" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C100" s="14" t="s">
-        <v>482</v>
+        <v>523</v>
       </c>
       <c r="D100" s="14" t="s">
-        <v>483</v>
+        <v>524</v>
       </c>
       <c r="E100" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B101" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C101" s="14" t="s">
-        <v>409</v>
+        <v>450</v>
       </c>
       <c r="D101" s="14" t="s">
-        <v>484</v>
+        <v>525</v>
       </c>
       <c r="E101" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B102" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C102" s="14" t="s">
-        <v>485</v>
+        <v>526</v>
       </c>
       <c r="D102" s="14" t="s">
-        <v>486</v>
+        <v>527</v>
       </c>
       <c r="E102" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B103" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C103" s="14" t="s">
-        <v>487</v>
+        <v>528</v>
       </c>
       <c r="D103" s="14" t="s">
-        <v>488</v>
+        <v>529</v>
       </c>
       <c r="E103" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B104" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C104" s="14" t="s">
-        <v>489</v>
+        <v>530</v>
       </c>
       <c r="D104" s="14" t="s">
-        <v>490</v>
+        <v>531</v>
       </c>
       <c r="E104" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B105" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C105" s="14" t="s">
-        <v>491</v>
+        <v>532</v>
       </c>
       <c r="D105" s="14" t="s">
-        <v>492</v>
+        <v>533</v>
       </c>
       <c r="E105" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B106" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C106" s="14" t="s">
-        <v>493</v>
+        <v>534</v>
       </c>
       <c r="D106" s="14" t="s">
-        <v>494</v>
+        <v>535</v>
       </c>
       <c r="E106" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="14" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="B107" s="14" t="s">
-        <v>231</v>
+        <v>272</v>
       </c>
       <c r="C107" s="14" t="s">
-        <v>338</v>
+        <v>379</v>
       </c>
       <c r="D107" s="14" t="s">
-        <v>312</v>
+        <v>353</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="14" t="s">
-        <v>339</v>
+        <v>380</v>
       </c>
       <c r="B108" s="14" t="s">
-        <v>231</v>
+        <v>272</v>
       </c>
       <c r="C108" s="14" t="s">
-        <v>495</v>
+        <v>536</v>
       </c>
       <c r="D108" s="14" t="s">
-        <v>496</v>
+        <v>537</v>
       </c>
       <c r="E108" s="14" t="s">
-        <v>497</v>
+        <v>538</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="14" t="s">
-        <v>339</v>
+        <v>380</v>
       </c>
       <c r="B109" s="14" t="s">
-        <v>231</v>
+        <v>272</v>
       </c>
       <c r="C109" s="14" t="s">
-        <v>498</v>
+        <v>539</v>
       </c>
       <c r="D109" s="14" t="s">
-        <v>499</v>
+        <v>540</v>
       </c>
       <c r="E109" s="14" t="s">
-        <v>500</v>
+        <v>541</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B110" s="14" t="s">
-        <v>231</v>
+        <v>272</v>
       </c>
       <c r="C110" s="14" t="s">
-        <v>480</v>
+        <v>521</v>
       </c>
       <c r="D110" s="14" t="s">
-        <v>501</v>
+        <v>542</v>
       </c>
       <c r="E110" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B111" s="14" t="s">
-        <v>231</v>
+        <v>272</v>
       </c>
       <c r="C111" s="14" t="s">
-        <v>482</v>
+        <v>523</v>
       </c>
       <c r="D111" s="14" t="s">
-        <v>502</v>
+        <v>543</v>
       </c>
       <c r="E111" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B112" s="14" t="s">
-        <v>231</v>
+        <v>272</v>
       </c>
       <c r="C112" s="14" t="s">
-        <v>409</v>
+        <v>450</v>
       </c>
       <c r="D112" s="14" t="s">
-        <v>503</v>
+        <v>544</v>
       </c>
       <c r="E112" s="14" t="s">
-        <v>449</v>
+        <v>490</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B113" s="14" t="s">
-        <v>231</v>
+        <v>272</v>
       </c>
       <c r="C113" s="14" t="s">
-        <v>485</v>
+        <v>526</v>
       </c>
       <c r="D113" s="14" t="s">
-        <v>504</v>
+        <v>545</v>
       </c>
       <c r="E113" s="14" t="s">
-        <v>449</v>
+        <v>490</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B114" s="14" t="s">
-        <v>231</v>
+        <v>272</v>
       </c>
       <c r="C114" s="14" t="s">
-        <v>487</v>
+        <v>528</v>
       </c>
       <c r="D114" s="14" t="s">
-        <v>505</v>
+        <v>546</v>
       </c>
       <c r="E114" s="14" t="s">
-        <v>449</v>
+        <v>490</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="14" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="B115" s="14" t="s">
         <v>28</v>
       </c>
       <c r="C115" s="14" t="s">
-        <v>338</v>
+        <v>379</v>
       </c>
       <c r="D115" s="14" t="s">
-        <v>310</v>
+        <v>351</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B116" s="14" t="s">
         <v>28</v>
       </c>
       <c r="C116" s="14" t="s">
-        <v>303</v>
+        <v>344</v>
       </c>
       <c r="D116" s="14" t="s">
-        <v>506</v>
+        <v>547</v>
       </c>
       <c r="E116" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B117" s="14" t="s">
         <v>28</v>
       </c>
       <c r="C117" s="14" t="s">
-        <v>305</v>
+        <v>346</v>
       </c>
       <c r="D117" s="14" t="s">
-        <v>507</v>
+        <v>548</v>
       </c>
       <c r="E117" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B118" s="14" t="s">
         <v>28</v>
       </c>
       <c r="C118" s="14" t="s">
-        <v>307</v>
+        <v>348</v>
       </c>
       <c r="D118" s="14" t="s">
-        <v>508</v>
+        <v>549</v>
       </c>
       <c r="E118" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B119" s="14" t="s">
         <v>28</v>
       </c>
       <c r="C119" s="14" t="s">
-        <v>309</v>
+        <v>350</v>
       </c>
       <c r="D119" s="14" t="s">
-        <v>509</v>
+        <v>550</v>
       </c>
       <c r="E119" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B120" s="14" t="s">
         <v>28</v>
       </c>
       <c r="C120" s="14" t="s">
-        <v>311</v>
+        <v>352</v>
       </c>
       <c r="D120" s="14" t="s">
-        <v>510</v>
+        <v>551</v>
       </c>
       <c r="E120" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B121" s="14" t="s">
         <v>28</v>
       </c>
       <c r="C121" s="14" t="s">
-        <v>313</v>
+        <v>354</v>
       </c>
       <c r="D121" s="14" t="s">
-        <v>511</v>
+        <v>552</v>
       </c>
       <c r="E121" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B122" s="14" t="s">
         <v>28</v>
       </c>
       <c r="C122" s="14" t="s">
-        <v>316</v>
+        <v>357</v>
       </c>
       <c r="D122" s="14" t="s">
-        <v>512</v>
+        <v>553</v>
       </c>
       <c r="E122" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B123" s="14" t="s">
         <v>28</v>
       </c>
       <c r="C123" s="14" t="s">
-        <v>319</v>
+        <v>360</v>
       </c>
       <c r="D123" s="14" t="s">
-        <v>513</v>
+        <v>554</v>
       </c>
       <c r="E123" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B124" s="14" t="s">
         <v>28</v>
       </c>
       <c r="C124" s="14" t="s">
-        <v>321</v>
+        <v>362</v>
       </c>
       <c r="D124" s="14" t="s">
-        <v>514</v>
+        <v>555</v>
       </c>
       <c r="E124" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B125" s="14" t="s">
         <v>28</v>
       </c>
       <c r="C125" s="14" t="s">
-        <v>324</v>
+        <v>365</v>
       </c>
       <c r="D125" s="14" t="s">
-        <v>515</v>
+        <v>556</v>
       </c>
       <c r="E125" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B126" s="14" t="s">
         <v>28</v>
       </c>
       <c r="C126" s="14" t="s">
-        <v>326</v>
+        <v>367</v>
       </c>
       <c r="D126" s="14" t="s">
-        <v>516</v>
+        <v>557</v>
       </c>
       <c r="E126" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B127" s="14" t="s">
         <v>28</v>
       </c>
       <c r="C127" s="14" t="s">
-        <v>463</v>
+        <v>504</v>
       </c>
       <c r="D127" s="14" t="s">
-        <v>517</v>
+        <v>558</v>
       </c>
       <c r="E127" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B128" s="14" t="s">
         <v>28</v>
       </c>
       <c r="C128" s="14" t="s">
-        <v>388</v>
+        <v>429</v>
       </c>
       <c r="D128" s="14" t="s">
-        <v>518</v>
+        <v>559</v>
       </c>
       <c r="E128" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B129" s="14" t="s">
         <v>28</v>
       </c>
       <c r="C129" s="14" t="s">
-        <v>390</v>
+        <v>431</v>
       </c>
       <c r="D129" s="14" t="s">
-        <v>519</v>
+        <v>560</v>
       </c>
       <c r="E129" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="14" t="s">
-        <v>339</v>
+        <v>380</v>
       </c>
       <c r="B130" s="14" t="s">
         <v>28</v>
       </c>
       <c r="C130" s="14" t="s">
-        <v>520</v>
+        <v>561</v>
       </c>
       <c r="D130" s="14" t="s">
-        <v>521</v>
+        <v>562</v>
       </c>
       <c r="E130" s="14" t="s">
-        <v>416</v>
+        <v>457</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="14" t="s">
-        <v>315</v>
+        <v>356</v>
       </c>
       <c r="B131" s="14" t="s">
         <v>28</v>
       </c>
       <c r="C131" s="14" t="s">
-        <v>485</v>
+        <v>526</v>
       </c>
       <c r="D131" s="14" t="s">
-        <v>522</v>
+        <v>563</v>
       </c>
       <c r="E131" s="14" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>

--- a/Ulshoefer-Preisliste-Angebotsrechner.xlsx
+++ b/Ulshoefer-Preisliste-Angebotsrechner.xlsx
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="B190" s="9">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="C190" t="inlineStr" s="5">
         <is>
